--- a/actual_df_filtered.xlsx
+++ b/actual_df_filtered.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CM120"/>
+  <dimension ref="A1:CP120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -884,17 +884,32 @@
           <t>Pset_Enrichment.Mindesthöhe [m]</t>
         </is>
       </c>
+      <c r="CN1" s="1" t="inlineStr">
+        <is>
+          <t>Pset_Enrichment.Minimale Höhe</t>
+        </is>
+      </c>
+      <c r="CO1" s="1" t="inlineStr">
+        <is>
+          <t>Pset_Enrichment.Minimale Breite</t>
+        </is>
+      </c>
+      <c r="CP1" s="1" t="inlineStr">
+        <is>
+          <t>Pset_Enrichment.Minimale Länge</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
         <v>1215</v>
       </c>
       <c r="B2" t="n">
-        <v>1211</v>
+        <v>1209</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>18j2PWjBz3nhKzSkJrvM7d</t>
+          <t>1R$FLavrj8G9Rxnz3lVckG</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -914,7 +929,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>LUF:343164</t>
+          <t>LUF:342799</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -946,11 +961,11 @@
       <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>OG2</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>7.939</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="inlineStr"/>
@@ -1057,37 +1072,40 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>0b93QOWH141xpbKCpGEr8x</t>
+          <t>3$FY_ljDfBsweJfZwnfjOk</t>
         </is>
       </c>
       <c r="CE2" t="n">
-        <v>4.008</v>
+        <v>3</v>
       </c>
       <c r="CF2" t="n">
-        <v>7.38232192035912</v>
+        <v>58.6046173021893</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.3140405</v>
+        <v>29.7644175</v>
       </c>
       <c r="CH2" t="n">
-        <v>9.274674323999999</v>
+        <v>89.29325249999999</v>
       </c>
       <c r="CI2" t="inlineStr"/>
       <c r="CJ2" t="inlineStr"/>
       <c r="CK2" t="inlineStr"/>
       <c r="CL2" t="inlineStr"/>
       <c r="CM2" t="inlineStr"/>
+      <c r="CN2" t="inlineStr"/>
+      <c r="CO2" t="inlineStr"/>
+      <c r="CP2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>1216</v>
       </c>
       <c r="B3" t="n">
-        <v>1212</v>
+        <v>1210</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0wtQ7wfjD5FPd24jrI75yq</t>
+          <t>0CIMZOOqj8GukY8gSKgU97</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1107,7 +1125,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>LUF:343294</t>
+          <t>LUF:342961</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -1139,11 +1157,11 @@
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>OG3</t>
+          <t>OG1</t>
         </is>
       </c>
       <c r="AD3" t="n">
-        <v>11.947</v>
+        <v>2.998</v>
       </c>
       <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="inlineStr"/>
@@ -1250,37 +1268,40 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>3ol_0stLL7q8pSNseENpkb</t>
+          <t>0b93QOWH141xpbKCpGErNs</t>
         </is>
       </c>
       <c r="CE3" t="n">
-        <v>2.523</v>
+        <v>4.941</v>
       </c>
       <c r="CF3" t="n">
-        <v>7.49144557435166</v>
+        <v>7.38232192035912</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.357719</v>
+        <v>2.3140405</v>
       </c>
       <c r="CH3" t="n">
-        <v>5.948525037</v>
+        <v>11.4336741105</v>
       </c>
       <c r="CI3" t="inlineStr"/>
       <c r="CJ3" t="inlineStr"/>
       <c r="CK3" t="inlineStr"/>
       <c r="CL3" t="inlineStr"/>
       <c r="CM3" t="inlineStr"/>
+      <c r="CN3" t="inlineStr"/>
+      <c r="CO3" t="inlineStr"/>
+      <c r="CP3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>1217</v>
       </c>
       <c r="B4" t="n">
-        <v>1207</v>
+        <v>1211</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>34G_SBUtD7Bx_aSDXbyBOH</t>
+          <t>18j2PWjBz3nhKzSkJrvM7d</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1300,7 +1321,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>TRH:341685</t>
+          <t>LUF:343164</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -1332,11 +1353,11 @@
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>UG2</t>
+          <t>OG2</t>
         </is>
       </c>
       <c r="AD4" t="n">
-        <v>-8.199999999999999</v>
+        <v>7.939</v>
       </c>
       <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="inlineStr"/>
@@ -1392,7 +1413,7 @@
       <c r="BR4" t="inlineStr"/>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>TRH</t>
+          <t>LUF</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -1407,7 +1428,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>Treppenhaus</t>
+          <t>Luftraum</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -1417,7 +1438,7 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>TRH  -  Treppenhaus</t>
+          <t>LUF  -  Luftraum</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
@@ -1426,7 +1447,7 @@
         </is>
       </c>
       <c r="BZ4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CA4" t="n">
         <v>1</v>
@@ -1443,41 +1464,40 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>3VbCMl1_928hbAKPG5Knl6</t>
+          <t>0b93QOWH141xpbKCpGEr8x</t>
         </is>
       </c>
       <c r="CE4" t="n">
-        <v>4.121</v>
+        <v>4.008</v>
       </c>
       <c r="CF4" t="n">
-        <v>30.404276140697</v>
+        <v>7.38232192035912</v>
       </c>
       <c r="CG4" t="n">
-        <v>32.270022</v>
+        <v>2.3140405</v>
       </c>
       <c r="CH4" t="n">
-        <v>132.984760662</v>
-      </c>
-      <c r="CI4" t="inlineStr">
-        <is>
-          <t>VF</t>
-        </is>
-      </c>
+        <v>9.274674323999999</v>
+      </c>
+      <c r="CI4" t="inlineStr"/>
       <c r="CJ4" t="inlineStr"/>
       <c r="CK4" t="inlineStr"/>
       <c r="CL4" t="inlineStr"/>
       <c r="CM4" t="inlineStr"/>
+      <c r="CN4" t="inlineStr"/>
+      <c r="CO4" t="inlineStr"/>
+      <c r="CP4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
         <v>1218</v>
       </c>
       <c r="B5" t="n">
-        <v>1208</v>
+        <v>1212</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>11GLlly7bCgPkVa3553rnS</t>
+          <t>0wtQ7wfjD5FPd24jrI75yq</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1497,7 +1517,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>TRH:342381</t>
+          <t>LUF:343294</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -1529,11 +1549,11 @@
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>UG1</t>
+          <t>OG3</t>
         </is>
       </c>
       <c r="AD5" t="n">
-        <v>-3.78</v>
+        <v>11.947</v>
       </c>
       <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="inlineStr"/>
@@ -1589,7 +1609,7 @@
       <c r="BR5" t="inlineStr"/>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>TRH</t>
+          <t>LUF</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -1604,7 +1624,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>Treppenhaus</t>
+          <t>Luftraum</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -1614,7 +1634,7 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>TRH  -  Treppenhaus</t>
+          <t>LUF  -  Luftraum</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
@@ -1623,7 +1643,7 @@
         </is>
       </c>
       <c r="BZ5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CA5" t="n">
         <v>1</v>
@@ -1640,41 +1660,40 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>1QH5Axl111J9SJj2E3W4w1</t>
+          <t>3ol_0stLL7q8pSNseENpkb</t>
         </is>
       </c>
       <c r="CE5" t="n">
-        <v>3.421</v>
+        <v>2.523</v>
       </c>
       <c r="CF5" t="n">
-        <v>30.8427134126076</v>
+        <v>7.49144557435166</v>
       </c>
       <c r="CG5" t="n">
-        <v>58.7912815</v>
+        <v>2.357719</v>
       </c>
       <c r="CH5" t="n">
-        <v>201.1249740115</v>
-      </c>
-      <c r="CI5" t="inlineStr">
-        <is>
-          <t>VF</t>
-        </is>
-      </c>
+        <v>5.948525037</v>
+      </c>
+      <c r="CI5" t="inlineStr"/>
       <c r="CJ5" t="inlineStr"/>
       <c r="CK5" t="inlineStr"/>
       <c r="CL5" t="inlineStr"/>
       <c r="CM5" t="inlineStr"/>
+      <c r="CN5" t="inlineStr"/>
+      <c r="CO5" t="inlineStr"/>
+      <c r="CP5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
         <v>1219</v>
       </c>
       <c r="B6" t="n">
-        <v>1207</v>
+        <v>1212</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>13LOp07jD0lfjp1Ds2xiaX</t>
+          <t>2Ru4iRmYDDDfo5eLHGZ8RE</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1694,7 +1713,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>LUF:340252</t>
+          <t>KOR:343282</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -1726,11 +1745,11 @@
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>UG2</t>
+          <t>OG3</t>
         </is>
       </c>
       <c r="AD6" t="n">
-        <v>-8.199999999999999</v>
+        <v>11.947</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1786,7 +1805,7 @@
       <c r="BR6" t="inlineStr"/>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>LUF</t>
+          <t>KOR</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -1801,7 +1820,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>Luftraum</t>
+          <t>Korridor</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -1811,7 +1830,7 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>LUF  -  Luftraum</t>
+          <t>KOR  -  Korridor</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
@@ -1820,7 +1839,7 @@
         </is>
       </c>
       <c r="BZ6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CA6" t="n">
         <v>1</v>
@@ -1837,37 +1856,44 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>3VbCMl1_928hbAKPG5Knnl</t>
+          <t>3ol_0stLL7q8pSNseENpkf</t>
         </is>
       </c>
       <c r="CE6" t="n">
-        <v>4.42</v>
+        <v>2.522</v>
       </c>
       <c r="CF6" t="n">
-        <v>7.38232192035912</v>
+        <v>24.6411125862649</v>
       </c>
       <c r="CG6" t="n">
-        <v>2.3140405</v>
+        <v>13.547317</v>
       </c>
       <c r="CH6" t="n">
-        <v>10.22805901</v>
-      </c>
-      <c r="CI6" t="inlineStr"/>
+        <v>34.166333474</v>
+      </c>
+      <c r="CI6" t="inlineStr">
+        <is>
+          <t>VF</t>
+        </is>
+      </c>
       <c r="CJ6" t="inlineStr"/>
       <c r="CK6" t="inlineStr"/>
       <c r="CL6" t="inlineStr"/>
       <c r="CM6" t="inlineStr"/>
+      <c r="CN6" t="inlineStr"/>
+      <c r="CO6" t="inlineStr"/>
+      <c r="CP6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
         <v>1220</v>
       </c>
       <c r="B7" t="n">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3BN76u7jD8SONfck_e054E</t>
+          <t>3Q30KcAwrFjgFId43DWY8P</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1887,7 +1913,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>LUF:342420</t>
+          <t>TRH:341682</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -1919,11 +1945,11 @@
       <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>UG1</t>
+          <t>UG2</t>
         </is>
       </c>
       <c r="AD7" t="n">
-        <v>-3.78</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1979,7 +2005,7 @@
       <c r="BR7" t="inlineStr"/>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>LUF</t>
+          <t>TRH</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -1994,7 +2020,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>Luftraum</t>
+          <t>Treppenhaus</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -2004,7 +2030,7 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>LUF  -  Luftraum</t>
+          <t>TRH  -  Treppenhaus</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
@@ -2013,7 +2039,7 @@
         </is>
       </c>
       <c r="BZ7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CA7" t="n">
         <v>1</v>
@@ -2030,37 +2056,44 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>1QH5Axl111J9SJj2E3W4vu</t>
+          <t>3VbCMl1_928hbAKPG5Knl1</t>
         </is>
       </c>
       <c r="CE7" t="n">
-        <v>3.421</v>
+        <v>4.121</v>
       </c>
       <c r="CF7" t="n">
-        <v>7.38098313865425</v>
+        <v>10.4407453756904</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.312567</v>
+        <v>6.8130725</v>
       </c>
       <c r="CH7" t="n">
-        <v>7.911291707</v>
-      </c>
-      <c r="CI7" t="inlineStr"/>
+        <v>28.0766717725</v>
+      </c>
+      <c r="CI7" t="inlineStr">
+        <is>
+          <t>VF</t>
+        </is>
+      </c>
       <c r="CJ7" t="inlineStr"/>
       <c r="CK7" t="inlineStr"/>
       <c r="CL7" t="inlineStr"/>
       <c r="CM7" t="inlineStr"/>
+      <c r="CN7" t="inlineStr"/>
+      <c r="CO7" t="inlineStr"/>
+      <c r="CP7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
         <v>1221</v>
       </c>
       <c r="B8" t="n">
-        <v>1209</v>
+        <v>1207</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1R$FLavrj8G9Rxnz3lVckG</t>
+          <t>34G_SBUtD7Bx_aSDXbyBOH</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2080,7 +2113,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>LUF:342799</t>
+          <t>TRH:341685</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -2112,11 +2145,11 @@
       <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>UG2</t>
         </is>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
@@ -2172,7 +2205,7 @@
       <c r="BR8" t="inlineStr"/>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>LUF</t>
+          <t>TRH</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -2187,7 +2220,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>Luftraum</t>
+          <t>Treppenhaus</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -2197,7 +2230,7 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>LUF  -  Luftraum</t>
+          <t>TRH  -  Treppenhaus</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
@@ -2206,7 +2239,7 @@
         </is>
       </c>
       <c r="BZ8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CA8" t="n">
         <v>1</v>
@@ -2223,37 +2256,44 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>3$FY_ljDfBsweJfZwnfjOk</t>
+          <t>3VbCMl1_928hbAKPG5Knl6</t>
         </is>
       </c>
       <c r="CE8" t="n">
-        <v>3</v>
+        <v>4.121</v>
       </c>
       <c r="CF8" t="n">
-        <v>58.6046173021893</v>
+        <v>30.404276140697</v>
       </c>
       <c r="CG8" t="n">
-        <v>29.7644175</v>
+        <v>32.270022</v>
       </c>
       <c r="CH8" t="n">
-        <v>89.29325249999999</v>
-      </c>
-      <c r="CI8" t="inlineStr"/>
+        <v>132.984760662</v>
+      </c>
+      <c r="CI8" t="inlineStr">
+        <is>
+          <t>VF</t>
+        </is>
+      </c>
       <c r="CJ8" t="inlineStr"/>
       <c r="CK8" t="inlineStr"/>
       <c r="CL8" t="inlineStr"/>
       <c r="CM8" t="inlineStr"/>
+      <c r="CN8" t="inlineStr"/>
+      <c r="CO8" t="inlineStr"/>
+      <c r="CP8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
         <v>1222</v>
       </c>
       <c r="B9" t="n">
-        <v>1210</v>
+        <v>1208</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0CIMZOOqj8GukY8gSKgU97</t>
+          <t>11GLlly7bCgPkVa3553rnS</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2273,7 +2313,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>LUF:342961</t>
+          <t>TRH:342381</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -2305,11 +2345,11 @@
       <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>OG1</t>
+          <t>UG1</t>
         </is>
       </c>
       <c r="AD9" t="n">
-        <v>2.998</v>
+        <v>-3.78</v>
       </c>
       <c r="AE9" t="inlineStr"/>
       <c r="AF9" t="inlineStr"/>
@@ -2365,7 +2405,7 @@
       <c r="BR9" t="inlineStr"/>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>LUF</t>
+          <t>TRH</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -2380,7 +2420,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>Luftraum</t>
+          <t>Treppenhaus</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -2390,7 +2430,7 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>LUF  -  Luftraum</t>
+          <t>TRH  -  Treppenhaus</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
@@ -2399,7 +2439,7 @@
         </is>
       </c>
       <c r="BZ9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CA9" t="n">
         <v>1</v>
@@ -2416,37 +2456,44 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>0b93QOWH141xpbKCpGErNs</t>
+          <t>1QH5Axl111J9SJj2E3W4w1</t>
         </is>
       </c>
       <c r="CE9" t="n">
-        <v>4.941</v>
+        <v>3.421</v>
       </c>
       <c r="CF9" t="n">
-        <v>7.38232192035912</v>
+        <v>30.8427134126076</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.3140405</v>
+        <v>58.7912815</v>
       </c>
       <c r="CH9" t="n">
-        <v>11.4336741105</v>
-      </c>
-      <c r="CI9" t="inlineStr"/>
+        <v>201.1249740115</v>
+      </c>
+      <c r="CI9" t="inlineStr">
+        <is>
+          <t>VF</t>
+        </is>
+      </c>
       <c r="CJ9" t="inlineStr"/>
       <c r="CK9" t="inlineStr"/>
       <c r="CL9" t="inlineStr"/>
       <c r="CM9" t="inlineStr"/>
+      <c r="CN9" t="inlineStr"/>
+      <c r="CO9" t="inlineStr"/>
+      <c r="CP9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
         <v>1223</v>
       </c>
       <c r="B10" t="n">
-        <v>1209</v>
+        <v>1207</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1830E3dHD5f9qhMIKx9HB6</t>
+          <t>13LOp07jD0lfjp1Ds2xiaX</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2466,7 +2513,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>VRF:342790</t>
+          <t>LUF:340252</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -2498,11 +2545,11 @@
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>UG2</t>
         </is>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="AE10" t="inlineStr"/>
       <c r="AF10" t="inlineStr"/>
@@ -2558,7 +2605,7 @@
       <c r="BR10" t="inlineStr"/>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>VRF</t>
+          <t>LUF</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -2573,7 +2620,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>Verkehrsfläche</t>
+          <t>Luftraum</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -2583,7 +2630,7 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>VRF  -  Verkehrsfläche</t>
+          <t>LUF  -  Luftraum</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
@@ -2592,7 +2639,7 @@
         </is>
       </c>
       <c r="BZ10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CA10" t="n">
         <v>1</v>
@@ -2609,41 +2656,40 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>3$FY_ljDfBsweJfZwnfjOd</t>
+          <t>3VbCMl1_928hbAKPG5Knnl</t>
         </is>
       </c>
       <c r="CE10" t="n">
-        <v>3</v>
+        <v>4.42</v>
       </c>
       <c r="CF10" t="n">
-        <v>8.511555999555499</v>
+        <v>7.38232192035912</v>
       </c>
       <c r="CG10" t="n">
-        <v>4.141197</v>
+        <v>2.3140405</v>
       </c>
       <c r="CH10" t="n">
-        <v>12.423591</v>
-      </c>
-      <c r="CI10" t="inlineStr">
-        <is>
-          <t>VF</t>
-        </is>
-      </c>
+        <v>10.22805901</v>
+      </c>
+      <c r="CI10" t="inlineStr"/>
       <c r="CJ10" t="inlineStr"/>
       <c r="CK10" t="inlineStr"/>
       <c r="CL10" t="inlineStr"/>
       <c r="CM10" t="inlineStr"/>
+      <c r="CN10" t="inlineStr"/>
+      <c r="CO10" t="inlineStr"/>
+      <c r="CP10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
         <v>1224</v>
       </c>
       <c r="B11" t="n">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0emPRSOwnDOOTgYleM3B_A</t>
+          <t>3BN76u7jD8SONfck_e054E</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2663,7 +2709,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>KOR:340508</t>
+          <t>LUF:342420</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -2695,11 +2741,11 @@
       <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>UG2</t>
+          <t>UG1</t>
         </is>
       </c>
       <c r="AD11" t="n">
-        <v>-8.199999999999999</v>
+        <v>-3.78</v>
       </c>
       <c r="AE11" t="inlineStr"/>
       <c r="AF11" t="inlineStr"/>
@@ -2755,7 +2801,7 @@
       <c r="BR11" t="inlineStr"/>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>KOR</t>
+          <t>LUF</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -2770,7 +2816,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>Korridor</t>
+          <t>Luftraum</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -2780,7 +2826,7 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>KOR  -  Korridor</t>
+          <t>LUF  -  Luftraum</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
@@ -2789,7 +2835,7 @@
         </is>
       </c>
       <c r="BZ11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CA11" t="n">
         <v>1</v>
@@ -2806,41 +2852,40 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>3VbCMl1_928hbAKPG5Knzl</t>
+          <t>1QH5Axl111J9SJj2E3W4vu</t>
         </is>
       </c>
       <c r="CE11" t="n">
-        <v>4.121</v>
+        <v>3.421</v>
       </c>
       <c r="CF11" t="n">
-        <v>20.2968268134622</v>
+        <v>7.38098313865425</v>
       </c>
       <c r="CG11" t="n">
-        <v>10.7493655</v>
+        <v>2.312567</v>
       </c>
       <c r="CH11" t="n">
-        <v>44.2981352255</v>
-      </c>
-      <c r="CI11" t="inlineStr">
-        <is>
-          <t>VF</t>
-        </is>
-      </c>
+        <v>7.911291707</v>
+      </c>
+      <c r="CI11" t="inlineStr"/>
       <c r="CJ11" t="inlineStr"/>
       <c r="CK11" t="inlineStr"/>
       <c r="CL11" t="inlineStr"/>
       <c r="CM11" t="inlineStr"/>
+      <c r="CN11" t="inlineStr"/>
+      <c r="CO11" t="inlineStr"/>
+      <c r="CP11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
         <v>1225</v>
       </c>
       <c r="B12" t="n">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2g6H0ojnvDdueYpZ_5Zux8</t>
+          <t>0jRMZ$SnH9ouX0ZQEwstxo</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2860,7 +2905,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>KOR:342423</t>
+          <t>VRF:342787</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -2892,11 +2937,11 @@
       <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>UG1</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="AD12" t="n">
-        <v>-3.78</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="inlineStr"/>
       <c r="AF12" t="inlineStr"/>
@@ -2952,7 +2997,7 @@
       <c r="BR12" t="inlineStr"/>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>KOR</t>
+          <t>VRF</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -2967,7 +3012,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>Korridor</t>
+          <t>Verkehrsfläche</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -2977,7 +3022,7 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>KOR  -  Korridor</t>
+          <t>VRF  -  Verkehrsfläche</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
@@ -3003,20 +3048,20 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>1QH5Axl111J9SJj2E3W4vx</t>
+          <t>3$FY_ljDfBsweJfZwnfjOY</t>
         </is>
       </c>
       <c r="CE12" t="n">
-        <v>3.421</v>
+        <v>3</v>
       </c>
       <c r="CF12" t="n">
-        <v>26.887076979177</v>
+        <v>7.99949280466301</v>
       </c>
       <c r="CG12" t="n">
-        <v>18.0784765</v>
+        <v>3.4365005</v>
       </c>
       <c r="CH12" t="n">
-        <v>61.8464681065</v>
+        <v>10.3095015</v>
       </c>
       <c r="CI12" t="inlineStr">
         <is>
@@ -3027,17 +3072,20 @@
       <c r="CK12" t="inlineStr"/>
       <c r="CL12" t="inlineStr"/>
       <c r="CM12" t="inlineStr"/>
+      <c r="CN12" t="inlineStr"/>
+      <c r="CO12" t="inlineStr"/>
+      <c r="CP12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
         <v>1226</v>
       </c>
       <c r="B13" t="n">
-        <v>1211</v>
+        <v>1209</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1rOBySJhH5b9YWwDU_guK1</t>
+          <t>1830E3dHD5f9qhMIKx9HB6</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -3057,7 +3105,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>KOR:343102</t>
+          <t>VRF:342790</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -3089,11 +3137,11 @@
       <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>OG2</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="AD13" t="n">
-        <v>7.939</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="inlineStr"/>
       <c r="AF13" t="inlineStr"/>
@@ -3149,7 +3197,7 @@
       <c r="BR13" t="inlineStr"/>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>KOR</t>
+          <t>VRF</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -3164,7 +3212,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>Korridor</t>
+          <t>Verkehrsfläche</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -3174,7 +3222,7 @@
       </c>
       <c r="BX13" t="inlineStr">
         <is>
-          <t>KOR  -  Korridor</t>
+          <t>VRF  -  Verkehrsfläche</t>
         </is>
       </c>
       <c r="BY13" t="inlineStr">
@@ -3200,20 +3248,20 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>0b93QOWH141xpbKCpGEr9v</t>
+          <t>3$FY_ljDfBsweJfZwnfjOd</t>
         </is>
       </c>
       <c r="CE13" t="n">
-        <v>3.579</v>
+        <v>3</v>
       </c>
       <c r="CF13" t="n">
-        <v>22.2995095258837</v>
+        <v>8.511555999555499</v>
       </c>
       <c r="CG13" t="n">
-        <v>13.6486625</v>
+        <v>4.141197</v>
       </c>
       <c r="CH13" t="n">
-        <v>48.8485630875</v>
+        <v>12.423591</v>
       </c>
       <c r="CI13" t="inlineStr">
         <is>
@@ -3224,17 +3272,20 @@
       <c r="CK13" t="inlineStr"/>
       <c r="CL13" t="inlineStr"/>
       <c r="CM13" t="inlineStr"/>
+      <c r="CN13" t="inlineStr"/>
+      <c r="CO13" t="inlineStr"/>
+      <c r="CP13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
         <v>1227</v>
       </c>
       <c r="B14" t="n">
-        <v>1212</v>
+        <v>1207</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2Ru4iRmYDDDfo5eLHGZ8RE</t>
+          <t>0emPRSOwnDOOTgYleM3B_A</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3254,7 +3305,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>KOR:343282</t>
+          <t>KOR:340508</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -3286,11 +3337,11 @@
       <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>OG3</t>
+          <t>UG2</t>
         </is>
       </c>
       <c r="AD14" t="n">
-        <v>11.947</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="AE14" t="inlineStr"/>
       <c r="AF14" t="inlineStr"/>
@@ -3397,20 +3448,20 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>3ol_0stLL7q8pSNseENpkf</t>
+          <t>3VbCMl1_928hbAKPG5Knzl</t>
         </is>
       </c>
       <c r="CE14" t="n">
-        <v>2.522</v>
+        <v>4.121</v>
       </c>
       <c r="CF14" t="n">
-        <v>24.6411125862649</v>
+        <v>20.2968268134622</v>
       </c>
       <c r="CG14" t="n">
-        <v>13.547317</v>
+        <v>10.7493655</v>
       </c>
       <c r="CH14" t="n">
-        <v>34.166333474</v>
+        <v>44.2981352255</v>
       </c>
       <c r="CI14" t="inlineStr">
         <is>
@@ -3421,17 +3472,20 @@
       <c r="CK14" t="inlineStr"/>
       <c r="CL14" t="inlineStr"/>
       <c r="CM14" t="inlineStr"/>
+      <c r="CN14" t="inlineStr"/>
+      <c r="CO14" t="inlineStr"/>
+      <c r="CP14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
         <v>1228</v>
       </c>
       <c r="B15" t="n">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>3Q30KcAwrFjgFId43DWY8P</t>
+          <t>2g6H0ojnvDdueYpZ_5Zux8</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3451,7 +3505,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>TRH:341682</t>
+          <t>KOR:342423</t>
         </is>
       </c>
       <c r="H15" t="n">
@@ -3483,11 +3537,11 @@
       <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>UG2</t>
+          <t>UG1</t>
         </is>
       </c>
       <c r="AD15" t="n">
-        <v>-8.199999999999999</v>
+        <v>-3.78</v>
       </c>
       <c r="AE15" t="inlineStr"/>
       <c r="AF15" t="inlineStr"/>
@@ -3543,7 +3597,7 @@
       <c r="BR15" t="inlineStr"/>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>TRH</t>
+          <t>KOR</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -3558,7 +3612,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>Treppenhaus</t>
+          <t>Korridor</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -3568,7 +3622,7 @@
       </c>
       <c r="BX15" t="inlineStr">
         <is>
-          <t>TRH  -  Treppenhaus</t>
+          <t>KOR  -  Korridor</t>
         </is>
       </c>
       <c r="BY15" t="inlineStr">
@@ -3594,20 +3648,20 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>3VbCMl1_928hbAKPG5Knl1</t>
+          <t>1QH5Axl111J9SJj2E3W4vx</t>
         </is>
       </c>
       <c r="CE15" t="n">
-        <v>4.121</v>
+        <v>3.421</v>
       </c>
       <c r="CF15" t="n">
-        <v>10.4407453756904</v>
+        <v>26.887076979177</v>
       </c>
       <c r="CG15" t="n">
-        <v>6.8130725</v>
+        <v>18.0784765</v>
       </c>
       <c r="CH15" t="n">
-        <v>28.0766717725</v>
+        <v>61.8464681065</v>
       </c>
       <c r="CI15" t="inlineStr">
         <is>
@@ -3618,17 +3672,20 @@
       <c r="CK15" t="inlineStr"/>
       <c r="CL15" t="inlineStr"/>
       <c r="CM15" t="inlineStr"/>
+      <c r="CN15" t="inlineStr"/>
+      <c r="CO15" t="inlineStr"/>
+      <c r="CP15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
         <v>1229</v>
       </c>
       <c r="B16" t="n">
-        <v>1209</v>
+        <v>1211</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2vZ$D3URf34vJnBMMHx9xX</t>
+          <t>1rOBySJhH5b9YWwDU_guK1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3648,7 +3705,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>UUF:343919</t>
+          <t>KOR:343102</t>
         </is>
       </c>
       <c r="H16" t="n">
@@ -3667,7 +3724,7 @@
       <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr">
         <is>
-          <t>EXTERNAL</t>
+          <t>INTERNAL</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
@@ -3680,11 +3737,11 @@
       <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>OG2</t>
         </is>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>7.939</v>
       </c>
       <c r="AE16" t="inlineStr"/>
       <c r="AF16" t="inlineStr"/>
@@ -3740,41 +3797,41 @@
       <c r="BR16" t="inlineStr"/>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>UUF</t>
+          <t>KOR</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>Aussenbereich</t>
+          <t>Allgemein</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>Aussenanlagen</t>
+          <t>Allgemein</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>Unbearbeitete Umgebungsflächen</t>
+          <t>Korridor</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
         <is>
-          <t>Alle restlichen unbearbeiteten Aussenanlagenflächen bis zur Grundstücksgrenze</t>
+          <t>nach Bedarf</t>
         </is>
       </c>
       <c r="BX16" t="inlineStr">
         <is>
-          <t>UUF  -  Unbearbeitete Umgebungsflächen</t>
+          <t>KOR  -  Korridor</t>
         </is>
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>EXTERNAL</t>
+          <t>INTERNAL</t>
         </is>
       </c>
       <c r="BZ16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CA16" t="n">
         <v>1</v>
@@ -3791,34 +3848,33 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>3qJ9B5zvT7$hh913fcAFEM</t>
+          <t>0b93QOWH141xpbKCpGEr9v</t>
         </is>
       </c>
       <c r="CE16" t="n">
-        <v>1</v>
+        <v>3.579</v>
       </c>
       <c r="CF16" t="n">
-        <v>27.1971243796257</v>
+        <v>22.2995095258837</v>
       </c>
       <c r="CG16" t="n">
-        <v>35.7954435</v>
+        <v>13.6486625</v>
       </c>
       <c r="CH16" t="n">
-        <v>35.7954435</v>
+        <v>48.8485630875</v>
       </c>
       <c r="CI16" t="inlineStr">
         <is>
-          <t>BUF</t>
-        </is>
-      </c>
-      <c r="CJ16" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
+          <t>VF</t>
+        </is>
+      </c>
+      <c r="CJ16" t="inlineStr"/>
       <c r="CK16" t="inlineStr"/>
       <c r="CL16" t="inlineStr"/>
       <c r="CM16" t="inlineStr"/>
+      <c r="CN16" t="inlineStr"/>
+      <c r="CO16" t="inlineStr"/>
+      <c r="CP16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -3829,7 +3885,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1D6v$lAcHDiAsIdGYCYrg4</t>
+          <t>3vSADXkCf9CehgpLlu0Bds</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3849,7 +3905,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>UUF:344049</t>
+          <t>UUF:343913</t>
         </is>
       </c>
       <c r="H17" t="n">
@@ -3992,20 +4048,20 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>3qJ9B5zvT7$hh913fcAFC8</t>
+          <t>3qJ9B5zvT7$hh913fcAFEG</t>
         </is>
       </c>
       <c r="CE17" t="n">
         <v>1</v>
       </c>
       <c r="CF17" t="n">
-        <v>165.175783539062</v>
+        <v>28.3650362774305</v>
       </c>
       <c r="CG17" t="n">
-        <v>258.794827</v>
+        <v>13.032036</v>
       </c>
       <c r="CH17" t="n">
-        <v>258.794827</v>
+        <v>13.032036</v>
       </c>
       <c r="CI17" t="inlineStr">
         <is>
@@ -4020,6 +4076,9 @@
       <c r="CK17" t="inlineStr"/>
       <c r="CL17" t="inlineStr"/>
       <c r="CM17" t="inlineStr"/>
+      <c r="CN17" t="inlineStr"/>
+      <c r="CO17" t="inlineStr"/>
+      <c r="CP17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -4030,7 +4089,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>14Y66SGP5Fm8iYaOLsp2V8</t>
+          <t>2vZ$D3URf34vJnBMMHx9xX</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -4050,7 +4109,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>UUF:344052</t>
+          <t>UUF:343919</t>
         </is>
       </c>
       <c r="H18" t="n">
@@ -4193,20 +4252,20 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>3qJ9B5zvT7$hh913fcAFCD</t>
+          <t>3qJ9B5zvT7$hh913fcAFEM</t>
         </is>
       </c>
       <c r="CE18" t="n">
         <v>1</v>
       </c>
       <c r="CF18" t="n">
-        <v>32.1979140750708</v>
+        <v>27.1971243796257</v>
       </c>
       <c r="CG18" t="n">
-        <v>56.537983</v>
+        <v>35.7954435</v>
       </c>
       <c r="CH18" t="n">
-        <v>56.537983</v>
+        <v>35.7954435</v>
       </c>
       <c r="CI18" t="inlineStr">
         <is>
@@ -4221,17 +4280,20 @@
       <c r="CK18" t="inlineStr"/>
       <c r="CL18" t="inlineStr"/>
       <c r="CM18" t="inlineStr"/>
+      <c r="CN18" t="inlineStr"/>
+      <c r="CO18" t="inlineStr"/>
+      <c r="CP18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
         <v>1232</v>
       </c>
       <c r="B19" t="n">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>14zTAK7eDFxu25AGckILdY</t>
+          <t>1D6v$lAcHDiAsIdGYCYrg4</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4251,7 +4313,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>VRF:342387</t>
+          <t>UUF:344049</t>
         </is>
       </c>
       <c r="H19" t="n">
@@ -4270,7 +4332,7 @@
       <c r="S19" t="inlineStr"/>
       <c r="T19" t="inlineStr">
         <is>
-          <t>INTERNAL</t>
+          <t>EXTERNAL</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -4283,11 +4345,11 @@
       <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>UG1</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="AD19" t="n">
-        <v>-3.78</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="inlineStr"/>
       <c r="AF19" t="inlineStr"/>
@@ -4343,41 +4405,41 @@
       <c r="BR19" t="inlineStr"/>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>VRF</t>
+          <t>UUF</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>Allgemein</t>
+          <t>Aussenbereich</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>Allgemein</t>
+          <t>Aussenanlagen</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>Verkehrsfläche</t>
+          <t>Unbearbeitete Umgebungsflächen</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
         <is>
-          <t>nach Bedarf</t>
+          <t>Alle restlichen unbearbeiteten Aussenanlagenflächen bis zur Grundstücksgrenze</t>
         </is>
       </c>
       <c r="BX19" t="inlineStr">
         <is>
-          <t>VRF  -  Verkehrsfläche</t>
+          <t>UUF  -  Unbearbeitete Umgebungsflächen</t>
         </is>
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>INTERNAL</t>
+          <t>EXTERNAL</t>
         </is>
       </c>
       <c r="BZ19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CA19" t="n">
         <v>1</v>
@@ -4394,41 +4456,48 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>1QH5Axl111J9SJj2E3W4wV</t>
+          <t>3qJ9B5zvT7$hh913fcAFC8</t>
         </is>
       </c>
       <c r="CE19" t="n">
-        <v>3.421</v>
+        <v>1</v>
       </c>
       <c r="CF19" t="n">
-        <v>64.01776445924619</v>
+        <v>165.175783539062</v>
       </c>
       <c r="CG19" t="n">
-        <v>50.4801045</v>
+        <v>258.794827</v>
       </c>
       <c r="CH19" t="n">
-        <v>172.6924374945</v>
+        <v>258.794827</v>
       </c>
       <c r="CI19" t="inlineStr">
         <is>
-          <t>VF</t>
-        </is>
-      </c>
-      <c r="CJ19" t="inlineStr"/>
+          <t>BUF</t>
+        </is>
+      </c>
+      <c r="CJ19" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
       <c r="CK19" t="inlineStr"/>
       <c r="CL19" t="inlineStr"/>
       <c r="CM19" t="inlineStr"/>
+      <c r="CN19" t="inlineStr"/>
+      <c r="CO19" t="inlineStr"/>
+      <c r="CP19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
         <v>1233</v>
       </c>
       <c r="B20" t="n">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>3_49$ldkHAGOZei44e_8FY</t>
+          <t>14Y66SGP5Fm8iYaOLsp2V8</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4448,7 +4517,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>VRF:342402</t>
+          <t>UUF:344052</t>
         </is>
       </c>
       <c r="H20" t="n">
@@ -4467,7 +4536,7 @@
       <c r="S20" t="inlineStr"/>
       <c r="T20" t="inlineStr">
         <is>
-          <t>INTERNAL</t>
+          <t>EXTERNAL</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
@@ -4480,11 +4549,11 @@
       <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>UG1</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="AD20" t="n">
-        <v>-3.78</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="inlineStr"/>
       <c r="AF20" t="inlineStr"/>
@@ -4540,41 +4609,41 @@
       <c r="BR20" t="inlineStr"/>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>VRF</t>
+          <t>UUF</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>Allgemein</t>
+          <t>Aussenbereich</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>Allgemein</t>
+          <t>Aussenanlagen</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>Verkehrsfläche</t>
+          <t>Unbearbeitete Umgebungsflächen</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
         <is>
-          <t>nach Bedarf</t>
+          <t>Alle restlichen unbearbeiteten Aussenanlagenflächen bis zur Grundstücksgrenze</t>
         </is>
       </c>
       <c r="BX20" t="inlineStr">
         <is>
-          <t>VRF  -  Verkehrsfläche</t>
+          <t>UUF  -  Unbearbeitete Umgebungsflächen</t>
         </is>
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>INTERNAL</t>
+          <t>EXTERNAL</t>
         </is>
       </c>
       <c r="BZ20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CA20" t="n">
         <v>1</v>
@@ -4591,41 +4660,48 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>1QH5Axl111J9SJj2E3W4vk</t>
+          <t>3qJ9B5zvT7$hh913fcAFCD</t>
         </is>
       </c>
       <c r="CE20" t="n">
-        <v>3.421</v>
+        <v>1</v>
       </c>
       <c r="CF20" t="n">
-        <v>8.247282695482101</v>
+        <v>32.1979140750708</v>
       </c>
       <c r="CG20" t="n">
-        <v>4.2125125</v>
+        <v>56.537983</v>
       </c>
       <c r="CH20" t="n">
-        <v>14.4110052625</v>
+        <v>56.537983</v>
       </c>
       <c r="CI20" t="inlineStr">
         <is>
-          <t>VF</t>
-        </is>
-      </c>
-      <c r="CJ20" t="inlineStr"/>
+          <t>BUF</t>
+        </is>
+      </c>
+      <c r="CJ20" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
       <c r="CK20" t="inlineStr"/>
       <c r="CL20" t="inlineStr"/>
       <c r="CM20" t="inlineStr"/>
+      <c r="CN20" t="inlineStr"/>
+      <c r="CO20" t="inlineStr"/>
+      <c r="CP20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
         <v>1234</v>
       </c>
       <c r="B21" t="n">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0jRMZ$SnH9ouX0ZQEwstxo</t>
+          <t>14zTAK7eDFxu25AGckILdY</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4645,7 +4721,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>VRF:342787</t>
+          <t>VRF:342387</t>
         </is>
       </c>
       <c r="H21" t="n">
@@ -4677,11 +4753,11 @@
       <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>UG1</t>
         </is>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>-3.78</v>
       </c>
       <c r="AE21" t="inlineStr"/>
       <c r="AF21" t="inlineStr"/>
@@ -4788,20 +4864,20 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>3$FY_ljDfBsweJfZwnfjOY</t>
+          <t>1QH5Axl111J9SJj2E3W4wV</t>
         </is>
       </c>
       <c r="CE21" t="n">
-        <v>3</v>
+        <v>3.421</v>
       </c>
       <c r="CF21" t="n">
-        <v>7.99949280466301</v>
+        <v>64.01776445924619</v>
       </c>
       <c r="CG21" t="n">
-        <v>3.4365005</v>
+        <v>50.4801045</v>
       </c>
       <c r="CH21" t="n">
-        <v>10.3095015</v>
+        <v>172.6924374945</v>
       </c>
       <c r="CI21" t="inlineStr">
         <is>
@@ -4812,17 +4888,20 @@
       <c r="CK21" t="inlineStr"/>
       <c r="CL21" t="inlineStr"/>
       <c r="CM21" t="inlineStr"/>
+      <c r="CN21" t="inlineStr"/>
+      <c r="CO21" t="inlineStr"/>
+      <c r="CP21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
         <v>1235</v>
       </c>
       <c r="B22" t="n">
-        <v>1212</v>
+        <v>1208</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2VPJztHKzE5eU2jmaJhVnb</t>
+          <t>3_49$ldkHAGOZei44e_8FY</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4842,7 +4921,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>BUF:345410</t>
+          <t>VRF:342402</t>
         </is>
       </c>
       <c r="H22" t="n">
@@ -4861,7 +4940,7 @@
       <c r="S22" t="inlineStr"/>
       <c r="T22" t="inlineStr">
         <is>
-          <t>EXTERNAL</t>
+          <t>INTERNAL</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
@@ -4874,11 +4953,11 @@
       <c r="AB22" t="inlineStr"/>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>OG3</t>
+          <t>UG1</t>
         </is>
       </c>
       <c r="AD22" t="n">
-        <v>11.947</v>
+        <v>-3.78</v>
       </c>
       <c r="AE22" t="inlineStr"/>
       <c r="AF22" t="inlineStr"/>
@@ -4934,41 +5013,41 @@
       <c r="BR22" t="inlineStr"/>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>BUF</t>
+          <t>VRF</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>Aussenbereich</t>
+          <t>Allgemein</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>Aussenanlagen</t>
+          <t>Allgemein</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>Bearbeitet Umgebungsflächen</t>
+          <t>Verkehrsfläche</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
         <is>
-          <t>Alle restlichen bearbeiteten Aussenanlagenflächen bis zur Grundstücksgrenze</t>
+          <t>nach Bedarf</t>
         </is>
       </c>
       <c r="BX22" t="inlineStr">
         <is>
-          <t>BUF  -  Bearbeitet Umgebungsflächen</t>
+          <t>VRF  -  Verkehrsfläche</t>
         </is>
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>EXTERNAL</t>
+          <t>INTERNAL</t>
         </is>
       </c>
       <c r="BZ22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CA22" t="n">
         <v>1</v>
@@ -4985,45 +5064,44 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>2VFBkNPLX5hxPkFzLFhskz</t>
+          <t>1QH5Axl111J9SJj2E3W4vk</t>
         </is>
       </c>
       <c r="CE22" t="n">
-        <v>1.001</v>
+        <v>3.421</v>
       </c>
       <c r="CF22" t="n">
-        <v>26.6148846931745</v>
+        <v>8.247282695482101</v>
       </c>
       <c r="CG22" t="n">
-        <v>29.418831</v>
+        <v>4.2125125</v>
       </c>
       <c r="CH22" t="n">
-        <v>29.448249831</v>
+        <v>14.4110052625</v>
       </c>
       <c r="CI22" t="inlineStr">
         <is>
-          <t>BUF</t>
-        </is>
-      </c>
-      <c r="CJ22" t="inlineStr">
-        <is>
-          <t>???</t>
-        </is>
-      </c>
+          <t>VF</t>
+        </is>
+      </c>
+      <c r="CJ22" t="inlineStr"/>
       <c r="CK22" t="inlineStr"/>
       <c r="CL22" t="inlineStr"/>
       <c r="CM22" t="inlineStr"/>
+      <c r="CN22" t="inlineStr"/>
+      <c r="CO22" t="inlineStr"/>
+      <c r="CP22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
         <v>1236</v>
       </c>
       <c r="B23" t="n">
-        <v>1212</v>
+        <v>1209</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>360G1aSpvFCuurfPO7oVVK</t>
+          <t>2smUqi2i10zRE_diOVjJhu</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -5043,7 +5121,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>BUF:345413</t>
+          <t>BUF:345808</t>
         </is>
       </c>
       <c r="H23" t="n">
@@ -5075,11 +5153,11 @@
       <c r="AB23" t="inlineStr"/>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>OG3</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="AD23" t="n">
-        <v>11.947</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="inlineStr"/>
       <c r="AF23" t="inlineStr"/>
@@ -5186,20 +5264,20 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>2VFBkNPLX5hxPkFzLFhskw</t>
+          <t>3EjVH2xK16fxVS2$WCt57y</t>
         </is>
       </c>
       <c r="CE23" t="n">
-        <v>1.001</v>
+        <v>1</v>
       </c>
       <c r="CF23" t="n">
-        <v>22.6274169979695</v>
+        <v>93.1053783306551</v>
       </c>
       <c r="CG23" t="n">
-        <v>32</v>
+        <v>330.8825295</v>
       </c>
       <c r="CH23" t="n">
-        <v>32.032</v>
+        <v>330.8825295</v>
       </c>
       <c r="CI23" t="inlineStr">
         <is>
@@ -5214,6 +5292,9 @@
       <c r="CK23" t="inlineStr"/>
       <c r="CL23" t="inlineStr"/>
       <c r="CM23" t="inlineStr"/>
+      <c r="CN23" t="inlineStr"/>
+      <c r="CO23" t="inlineStr"/>
+      <c r="CP23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -5224,7 +5305,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2gK95MKEPE$O83dwER37Qp</t>
+          <t>2VPJztHKzE5eU2jmaJhVnb</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5244,7 +5325,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>BUF:345445</t>
+          <t>BUF:345410</t>
         </is>
       </c>
       <c r="H24" t="n">
@@ -5387,20 +5468,20 @@
       </c>
       <c r="CD24" t="inlineStr">
         <is>
-          <t>2VFBkNPLX5hxPkFzLFhskQ</t>
+          <t>2VFBkNPLX5hxPkFzLFhskz</t>
         </is>
       </c>
       <c r="CE24" t="n">
         <v>1.001</v>
       </c>
       <c r="CF24" t="n">
-        <v>26.6132231953422</v>
+        <v>26.6148846931745</v>
       </c>
       <c r="CG24" t="n">
-        <v>29.4185435</v>
+        <v>29.418831</v>
       </c>
       <c r="CH24" t="n">
-        <v>29.4479620435</v>
+        <v>29.448249831</v>
       </c>
       <c r="CI24" t="inlineStr">
         <is>
@@ -5415,17 +5496,20 @@
       <c r="CK24" t="inlineStr"/>
       <c r="CL24" t="inlineStr"/>
       <c r="CM24" t="inlineStr"/>
+      <c r="CN24" t="inlineStr"/>
+      <c r="CO24" t="inlineStr"/>
+      <c r="CP24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
         <v>1238</v>
       </c>
       <c r="B25" t="n">
-        <v>1209</v>
+        <v>1212</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0XbzWrb4P70RH_r69FZvNC</t>
+          <t>360G1aSpvFCuurfPO7oVVK</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5445,7 +5529,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>UUF:343895</t>
+          <t>BUF:345413</t>
         </is>
       </c>
       <c r="H25" t="n">
@@ -5477,11 +5561,11 @@
       <c r="AB25" t="inlineStr"/>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>OG3</t>
         </is>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>11.947</v>
       </c>
       <c r="AE25" t="inlineStr"/>
       <c r="AF25" t="inlineStr"/>
@@ -5537,7 +5621,7 @@
       <c r="BR25" t="inlineStr"/>
       <c r="BS25" t="inlineStr">
         <is>
-          <t>UUF</t>
+          <t>BUF</t>
         </is>
       </c>
       <c r="BT25" t="inlineStr">
@@ -5552,17 +5636,17 @@
       </c>
       <c r="BV25" t="inlineStr">
         <is>
-          <t>Unbearbeitete Umgebungsflächen</t>
+          <t>Bearbeitet Umgebungsflächen</t>
         </is>
       </c>
       <c r="BW25" t="inlineStr">
         <is>
-          <t>Alle restlichen unbearbeiteten Aussenanlagenflächen bis zur Grundstücksgrenze</t>
+          <t>Alle restlichen bearbeiteten Aussenanlagenflächen bis zur Grundstücksgrenze</t>
         </is>
       </c>
       <c r="BX25" t="inlineStr">
         <is>
-          <t>UUF  -  Unbearbeitete Umgebungsflächen</t>
+          <t>BUF  -  Bearbeitet Umgebungsflächen</t>
         </is>
       </c>
       <c r="BY25" t="inlineStr">
@@ -5588,20 +5672,20 @@
       </c>
       <c r="CD25" t="inlineStr">
         <is>
-          <t>3qJ9B5zvT7$hh913fcAFEk</t>
+          <t>2VFBkNPLX5hxPkFzLFhskw</t>
         </is>
       </c>
       <c r="CE25" t="n">
-        <v>1</v>
+        <v>1.001</v>
       </c>
       <c r="CF25" t="n">
-        <v>71.8572432719856</v>
+        <v>22.6274169979695</v>
       </c>
       <c r="CG25" t="n">
-        <v>24.9312215</v>
+        <v>32</v>
       </c>
       <c r="CH25" t="n">
-        <v>24.9312215</v>
+        <v>32.032</v>
       </c>
       <c r="CI25" t="inlineStr">
         <is>
@@ -5610,23 +5694,26 @@
       </c>
       <c r="CJ25" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>???</t>
         </is>
       </c>
       <c r="CK25" t="inlineStr"/>
       <c r="CL25" t="inlineStr"/>
       <c r="CM25" t="inlineStr"/>
+      <c r="CN25" t="inlineStr"/>
+      <c r="CO25" t="inlineStr"/>
+      <c r="CP25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
         <v>1239</v>
       </c>
       <c r="B26" t="n">
-        <v>1209</v>
+        <v>1212</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>3vSADXkCf9CehgpLlu0Bds</t>
+          <t>2gK95MKEPE$O83dwER37Qp</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5646,7 +5733,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>UUF:343913</t>
+          <t>BUF:345445</t>
         </is>
       </c>
       <c r="H26" t="n">
@@ -5678,11 +5765,11 @@
       <c r="AB26" t="inlineStr"/>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>OG3</t>
         </is>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>11.947</v>
       </c>
       <c r="AE26" t="inlineStr"/>
       <c r="AF26" t="inlineStr"/>
@@ -5738,7 +5825,7 @@
       <c r="BR26" t="inlineStr"/>
       <c r="BS26" t="inlineStr">
         <is>
-          <t>UUF</t>
+          <t>BUF</t>
         </is>
       </c>
       <c r="BT26" t="inlineStr">
@@ -5753,17 +5840,17 @@
       </c>
       <c r="BV26" t="inlineStr">
         <is>
-          <t>Unbearbeitete Umgebungsflächen</t>
+          <t>Bearbeitet Umgebungsflächen</t>
         </is>
       </c>
       <c r="BW26" t="inlineStr">
         <is>
-          <t>Alle restlichen unbearbeiteten Aussenanlagenflächen bis zur Grundstücksgrenze</t>
+          <t>Alle restlichen bearbeiteten Aussenanlagenflächen bis zur Grundstücksgrenze</t>
         </is>
       </c>
       <c r="BX26" t="inlineStr">
         <is>
-          <t>UUF  -  Unbearbeitete Umgebungsflächen</t>
+          <t>BUF  -  Bearbeitet Umgebungsflächen</t>
         </is>
       </c>
       <c r="BY26" t="inlineStr">
@@ -5789,20 +5876,20 @@
       </c>
       <c r="CD26" t="inlineStr">
         <is>
-          <t>3qJ9B5zvT7$hh913fcAFEG</t>
+          <t>2VFBkNPLX5hxPkFzLFhskQ</t>
         </is>
       </c>
       <c r="CE26" t="n">
-        <v>1</v>
+        <v>1.001</v>
       </c>
       <c r="CF26" t="n">
-        <v>28.3650362774305</v>
+        <v>26.6132231953422</v>
       </c>
       <c r="CG26" t="n">
-        <v>13.032036</v>
+        <v>29.4185435</v>
       </c>
       <c r="CH26" t="n">
-        <v>13.032036</v>
+        <v>29.4479620435</v>
       </c>
       <c r="CI26" t="inlineStr">
         <is>
@@ -5811,12 +5898,15 @@
       </c>
       <c r="CJ26" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>???</t>
         </is>
       </c>
       <c r="CK26" t="inlineStr"/>
       <c r="CL26" t="inlineStr"/>
       <c r="CM26" t="inlineStr"/>
+      <c r="CN26" t="inlineStr"/>
+      <c r="CO26" t="inlineStr"/>
+      <c r="CP26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -5827,7 +5917,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2u0jNhx4PBahQiA_Mn0fAT</t>
+          <t>0XbzWrb4P70RH_r69FZvNC</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5847,7 +5937,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>BUF:343916</t>
+          <t>UUF:343895</t>
         </is>
       </c>
       <c r="H27" t="n">
@@ -5939,7 +6029,7 @@
       <c r="BR27" t="inlineStr"/>
       <c r="BS27" t="inlineStr">
         <is>
-          <t>BUF</t>
+          <t>UUF</t>
         </is>
       </c>
       <c r="BT27" t="inlineStr">
@@ -5954,17 +6044,17 @@
       </c>
       <c r="BV27" t="inlineStr">
         <is>
-          <t>Bearbeitet Umgebungsflächen</t>
+          <t>Unbearbeitete Umgebungsflächen</t>
         </is>
       </c>
       <c r="BW27" t="inlineStr">
         <is>
-          <t>Alle restlichen bearbeiteten Aussenanlagenflächen bis zur Grundstücksgrenze</t>
+          <t>Alle restlichen unbearbeiteten Aussenanlagenflächen bis zur Grundstücksgrenze</t>
         </is>
       </c>
       <c r="BX27" t="inlineStr">
         <is>
-          <t>BUF  -  Bearbeitet Umgebungsflächen</t>
+          <t>UUF  -  Unbearbeitete Umgebungsflächen</t>
         </is>
       </c>
       <c r="BY27" t="inlineStr">
@@ -5990,20 +6080,20 @@
       </c>
       <c r="CD27" t="inlineStr">
         <is>
-          <t>3qJ9B5zvT7$hh913fcAFEL</t>
+          <t>3qJ9B5zvT7$hh913fcAFEk</t>
         </is>
       </c>
       <c r="CE27" t="n">
         <v>1</v>
       </c>
       <c r="CF27" t="n">
-        <v>46.5550926093682</v>
+        <v>71.8572432719856</v>
       </c>
       <c r="CG27" t="n">
-        <v>136.0412375</v>
+        <v>24.9312215</v>
       </c>
       <c r="CH27" t="n">
-        <v>136.0412375</v>
+        <v>24.9312215</v>
       </c>
       <c r="CI27" t="inlineStr">
         <is>
@@ -6012,12 +6102,15 @@
       </c>
       <c r="CJ27" t="inlineStr">
         <is>
-          <t>???</t>
+          <t>true</t>
         </is>
       </c>
       <c r="CK27" t="inlineStr"/>
       <c r="CL27" t="inlineStr"/>
       <c r="CM27" t="inlineStr"/>
+      <c r="CN27" t="inlineStr"/>
+      <c r="CO27" t="inlineStr"/>
+      <c r="CP27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -6028,7 +6121,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1XvgrEk2L7Sf0_v9d5iT66</t>
+          <t>0WtOOP9cn9MBUnf0AHUQfJ</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -6048,7 +6141,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>BUF:343928</t>
+          <t>BUF:343910</t>
         </is>
       </c>
       <c r="H28" t="n">
@@ -6191,20 +6284,20 @@
       </c>
       <c r="CD28" t="inlineStr">
         <is>
-          <t>3qJ9B5zvT7$hh913fcAFE1</t>
+          <t>3qJ9B5zvT7$hh913fcAFEV</t>
         </is>
       </c>
       <c r="CE28" t="n">
         <v>1</v>
       </c>
       <c r="CF28" t="n">
-        <v>10.2950212176134</v>
+        <v>18.0302029491287</v>
       </c>
       <c r="CG28" t="n">
-        <v>6.29499</v>
+        <v>7.9934815</v>
       </c>
       <c r="CH28" t="n">
-        <v>6.29499</v>
+        <v>7.9934815</v>
       </c>
       <c r="CI28" t="inlineStr">
         <is>
@@ -6219,6 +6312,9 @@
       <c r="CK28" t="inlineStr"/>
       <c r="CL28" t="inlineStr"/>
       <c r="CM28" t="inlineStr"/>
+      <c r="CN28" t="inlineStr"/>
+      <c r="CO28" t="inlineStr"/>
+      <c r="CP28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -6229,7 +6325,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>02z0dETOLCdvSjB6spGLDD</t>
+          <t>2u0jNhx4PBahQiA_Mn0fAT</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6249,7 +6345,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>BUF:343937</t>
+          <t>BUF:343916</t>
         </is>
       </c>
       <c r="H29" t="n">
@@ -6392,20 +6488,20 @@
       </c>
       <c r="CD29" t="inlineStr">
         <is>
-          <t>3qJ9B5zvT7$hh913fcAFDu</t>
+          <t>3qJ9B5zvT7$hh913fcAFEL</t>
         </is>
       </c>
       <c r="CE29" t="n">
         <v>1</v>
       </c>
       <c r="CF29" t="n">
-        <v>5.40536512706288</v>
+        <v>46.5550926093682</v>
       </c>
       <c r="CG29" t="n">
-        <v>1.4047875</v>
+        <v>136.0412375</v>
       </c>
       <c r="CH29" t="n">
-        <v>1.4047875</v>
+        <v>136.0412375</v>
       </c>
       <c r="CI29" t="inlineStr">
         <is>
@@ -6420,6 +6516,9 @@
       <c r="CK29" t="inlineStr"/>
       <c r="CL29" t="inlineStr"/>
       <c r="CM29" t="inlineStr"/>
+      <c r="CN29" t="inlineStr"/>
+      <c r="CO29" t="inlineStr"/>
+      <c r="CP29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -6430,7 +6529,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2dWGfk8A5FP9hGnKCxZb2t</t>
+          <t>1XvgrEk2L7Sf0_v9d5iT66</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6450,7 +6549,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>BUF:344088</t>
+          <t>BUF:343928</t>
         </is>
       </c>
       <c r="H30" t="n">
@@ -6593,20 +6692,20 @@
       </c>
       <c r="CD30" t="inlineStr">
         <is>
-          <t>3qJ9B5zvT7$hh913fcA8pX</t>
+          <t>3qJ9B5zvT7$hh913fcAFE1</t>
         </is>
       </c>
       <c r="CE30" t="n">
         <v>1</v>
       </c>
       <c r="CF30" t="n">
-        <v>51.1635370017265</v>
+        <v>10.2950212176134</v>
       </c>
       <c r="CG30" t="n">
-        <v>17.796225</v>
+        <v>6.29499</v>
       </c>
       <c r="CH30" t="n">
-        <v>17.796225</v>
+        <v>6.29499</v>
       </c>
       <c r="CI30" t="inlineStr">
         <is>
@@ -6621,6 +6720,9 @@
       <c r="CK30" t="inlineStr"/>
       <c r="CL30" t="inlineStr"/>
       <c r="CM30" t="inlineStr"/>
+      <c r="CN30" t="inlineStr"/>
+      <c r="CO30" t="inlineStr"/>
+      <c r="CP30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -6631,7 +6733,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2smUqi2i10zRE_diOVjJhu</t>
+          <t>02z0dETOLCdvSjB6spGLDD</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6651,7 +6753,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>BUF:345808</t>
+          <t>BUF:343937</t>
         </is>
       </c>
       <c r="H31" t="n">
@@ -6794,20 +6896,20 @@
       </c>
       <c r="CD31" t="inlineStr">
         <is>
-          <t>3EjVH2xK16fxVS2$WCt57y</t>
+          <t>3qJ9B5zvT7$hh913fcAFDu</t>
         </is>
       </c>
       <c r="CE31" t="n">
         <v>1</v>
       </c>
       <c r="CF31" t="n">
-        <v>93.1053783306551</v>
+        <v>5.40536512706288</v>
       </c>
       <c r="CG31" t="n">
-        <v>330.8825295</v>
+        <v>1.4047875</v>
       </c>
       <c r="CH31" t="n">
-        <v>330.8825295</v>
+        <v>1.4047875</v>
       </c>
       <c r="CI31" t="inlineStr">
         <is>
@@ -6822,6 +6924,9 @@
       <c r="CK31" t="inlineStr"/>
       <c r="CL31" t="inlineStr"/>
       <c r="CM31" t="inlineStr"/>
+      <c r="CN31" t="inlineStr"/>
+      <c r="CO31" t="inlineStr"/>
+      <c r="CP31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -6832,7 +6937,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>3eJReeN3j08hoB6uk90Meh</t>
+          <t>2dWGfk8A5FP9hGnKCxZb2t</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6852,7 +6957,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>VEL_S:343931</t>
+          <t>BUF:344088</t>
         </is>
       </c>
       <c r="H32" t="n">
@@ -6944,7 +7049,7 @@
       <c r="BR32" t="inlineStr"/>
       <c r="BS32" t="inlineStr">
         <is>
-          <t>VEL_S</t>
+          <t>BUF</t>
         </is>
       </c>
       <c r="BT32" t="inlineStr">
@@ -6959,17 +7064,17 @@
       </c>
       <c r="BV32" t="inlineStr">
         <is>
-          <t>Velo- Abstellplätze Schulkinder</t>
+          <t>Bearbeitet Umgebungsflächen</t>
         </is>
       </c>
       <c r="BW32" t="inlineStr">
         <is>
-          <t>13 Stück, davon mind 1/3 überdacht, idealerweise alle</t>
+          <t>Alle restlichen bearbeiteten Aussenanlagenflächen bis zur Grundstücksgrenze</t>
         </is>
       </c>
       <c r="BX32" t="inlineStr">
         <is>
-          <t>VEL_S  -  Velo- Abstellplätze Schulkinder</t>
+          <t>BUF  -  Bearbeitet Umgebungsflächen</t>
         </is>
       </c>
       <c r="BY32" t="inlineStr">
@@ -6995,20 +7100,20 @@
       </c>
       <c r="CD32" t="inlineStr">
         <is>
-          <t>3qJ9B5zvT7$hh913fcAFE2</t>
+          <t>3qJ9B5zvT7$hh913fcA8pX</t>
         </is>
       </c>
       <c r="CE32" t="n">
-        <v>0.999999999999999</v>
+        <v>1</v>
       </c>
       <c r="CF32" t="n">
-        <v>22.2049630491981</v>
+        <v>51.1635370017265</v>
       </c>
       <c r="CG32" t="n">
-        <v>18.206341</v>
+        <v>17.796225</v>
       </c>
       <c r="CH32" t="n">
-        <v>18.206341</v>
+        <v>17.796225</v>
       </c>
       <c r="CI32" t="inlineStr">
         <is>
@@ -7017,14 +7122,15 @@
       </c>
       <c r="CJ32" t="inlineStr">
         <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="CK32" t="n">
-        <v>10.1</v>
-      </c>
+          <t>???</t>
+        </is>
+      </c>
+      <c r="CK32" t="inlineStr"/>
       <c r="CL32" t="inlineStr"/>
       <c r="CM32" t="inlineStr"/>
+      <c r="CN32" t="inlineStr"/>
+      <c r="CO32" t="inlineStr"/>
+      <c r="CP32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -7035,7 +7141,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>3OwC$bqnH8HPMox51VeeVy</t>
+          <t>1MqvEZmU539xzlBdmFG0Gt</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -7055,7 +7161,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>AVF:343904</t>
+          <t>VEL_L:343934</t>
         </is>
       </c>
       <c r="H33" t="n">
@@ -7147,7 +7253,7 @@
       <c r="BR33" t="inlineStr"/>
       <c r="BS33" t="inlineStr">
         <is>
-          <t>AVF</t>
+          <t>VEL_L</t>
         </is>
       </c>
       <c r="BT33" t="inlineStr">
@@ -7162,17 +7268,17 @@
       </c>
       <c r="BV33" t="inlineStr">
         <is>
-          <t>Zufahrt, Abstandsfläche, Umschwung</t>
+          <t>Velo- Abstellplätze Schulpersonal</t>
         </is>
       </c>
       <c r="BW33" t="inlineStr">
         <is>
-          <t>nach Bedarf</t>
+          <t>8 Stück, Gedeckt und gegen Diebstahl und Vanalismus geschützt</t>
         </is>
       </c>
       <c r="BX33" t="inlineStr">
         <is>
-          <t>AVF  -  Zufahrt, Abstandsfläche, Umschwung</t>
+          <t>VEL_L  -  Velo- Abstellplätze Schulpersonal</t>
         </is>
       </c>
       <c r="BY33" t="inlineStr">
@@ -7198,20 +7304,20 @@
       </c>
       <c r="CD33" t="inlineStr">
         <is>
-          <t>3qJ9B5zvT7$hh913fcAFEP</t>
+          <t>3qJ9B5zvT7$hh913fcAFE7</t>
         </is>
       </c>
       <c r="CE33" t="n">
         <v>1</v>
       </c>
       <c r="CF33" t="n">
-        <v>14.5215458021443</v>
+        <v>9.201563573455161</v>
       </c>
       <c r="CG33" t="n">
-        <v>12.9937485</v>
+        <v>5.20168</v>
       </c>
       <c r="CH33" t="n">
-        <v>12.9937485</v>
+        <v>5.20168</v>
       </c>
       <c r="CI33" t="inlineStr">
         <is>
@@ -7223,9 +7329,14 @@
           <t>false</t>
         </is>
       </c>
-      <c r="CK33" t="inlineStr"/>
+      <c r="CK33" t="n">
+        <v>10.1</v>
+      </c>
       <c r="CL33" t="inlineStr"/>
       <c r="CM33" t="inlineStr"/>
+      <c r="CN33" t="inlineStr"/>
+      <c r="CO33" t="inlineStr"/>
+      <c r="CP33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -7236,7 +7347,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>3Dk2HhiCr35RYXuSaVOvs6</t>
+          <t>3eJReeN3j08hoB6uk90Meh</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7256,7 +7367,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>BUF:343892</t>
+          <t>VEL_S:343931</t>
         </is>
       </c>
       <c r="H34" t="n">
@@ -7348,7 +7459,7 @@
       <c r="BR34" t="inlineStr"/>
       <c r="BS34" t="inlineStr">
         <is>
-          <t>BUF</t>
+          <t>VEL_S</t>
         </is>
       </c>
       <c r="BT34" t="inlineStr">
@@ -7363,17 +7474,17 @@
       </c>
       <c r="BV34" t="inlineStr">
         <is>
-          <t>Bearbeitet Umgebungsflächen</t>
+          <t>Velo- Abstellplätze Schulkinder</t>
         </is>
       </c>
       <c r="BW34" t="inlineStr">
         <is>
-          <t>Alle restlichen bearbeiteten Aussenanlagenflächen bis zur Grundstücksgrenze</t>
+          <t>13 Stück, davon mind 1/3 überdacht, idealerweise alle</t>
         </is>
       </c>
       <c r="BX34" t="inlineStr">
         <is>
-          <t>BUF  -  Bearbeitet Umgebungsflächen</t>
+          <t>VEL_S  -  Velo- Abstellplätze Schulkinder</t>
         </is>
       </c>
       <c r="BY34" t="inlineStr">
@@ -7399,20 +7510,20 @@
       </c>
       <c r="CD34" t="inlineStr">
         <is>
-          <t>3qJ9B5zvT7$hh913fcAFEj</t>
+          <t>3qJ9B5zvT7$hh913fcAFE2</t>
         </is>
       </c>
       <c r="CE34" t="n">
-        <v>1</v>
+        <v>0.999999999999999</v>
       </c>
       <c r="CF34" t="n">
-        <v>118.876854433513</v>
+        <v>22.2049630491981</v>
       </c>
       <c r="CG34" t="n">
-        <v>162.444519</v>
+        <v>18.206341</v>
       </c>
       <c r="CH34" t="n">
-        <v>162.444519</v>
+        <v>18.206341</v>
       </c>
       <c r="CI34" t="inlineStr">
         <is>
@@ -7421,12 +7532,17 @@
       </c>
       <c r="CJ34" t="inlineStr">
         <is>
-          <t>???</t>
-        </is>
-      </c>
-      <c r="CK34" t="inlineStr"/>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="CK34" t="n">
+        <v>10.1</v>
+      </c>
       <c r="CL34" t="inlineStr"/>
       <c r="CM34" t="inlineStr"/>
+      <c r="CN34" t="inlineStr"/>
+      <c r="CO34" t="inlineStr"/>
+      <c r="CP34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -7437,7 +7553,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>3AGSwy4Cv9YOBE5MpdNLQt</t>
+          <t>3OwC$bqnH8HPMox51VeeVy</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7457,7 +7573,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>BUF:343901</t>
+          <t>AVF:343904</t>
         </is>
       </c>
       <c r="H35" t="n">
@@ -7549,7 +7665,7 @@
       <c r="BR35" t="inlineStr"/>
       <c r="BS35" t="inlineStr">
         <is>
-          <t>BUF</t>
+          <t>AVF</t>
         </is>
       </c>
       <c r="BT35" t="inlineStr">
@@ -7564,17 +7680,17 @@
       </c>
       <c r="BV35" t="inlineStr">
         <is>
-          <t>Bearbeitet Umgebungsflächen</t>
+          <t>Zufahrt, Abstandsfläche, Umschwung</t>
         </is>
       </c>
       <c r="BW35" t="inlineStr">
         <is>
-          <t>Alle restlichen bearbeiteten Aussenanlagenflächen bis zur Grundstücksgrenze</t>
+          <t>nach Bedarf</t>
         </is>
       </c>
       <c r="BX35" t="inlineStr">
         <is>
-          <t>BUF  -  Bearbeitet Umgebungsflächen</t>
+          <t>AVF  -  Zufahrt, Abstandsfläche, Umschwung</t>
         </is>
       </c>
       <c r="BY35" t="inlineStr">
@@ -7600,20 +7716,20 @@
       </c>
       <c r="CD35" t="inlineStr">
         <is>
-          <t>3qJ9B5zvT7$hh913fcAFEa</t>
+          <t>3qJ9B5zvT7$hh913fcAFEP</t>
         </is>
       </c>
       <c r="CE35" t="n">
         <v>1</v>
       </c>
       <c r="CF35" t="n">
-        <v>36.0606998520392</v>
+        <v>14.5215458021443</v>
       </c>
       <c r="CG35" t="n">
-        <v>25.4851555</v>
+        <v>12.9937485</v>
       </c>
       <c r="CH35" t="n">
-        <v>25.4851555</v>
+        <v>12.9937485</v>
       </c>
       <c r="CI35" t="inlineStr">
         <is>
@@ -7622,12 +7738,15 @@
       </c>
       <c r="CJ35" t="inlineStr">
         <is>
-          <t>???</t>
+          <t>false</t>
         </is>
       </c>
       <c r="CK35" t="inlineStr"/>
       <c r="CL35" t="inlineStr"/>
       <c r="CM35" t="inlineStr"/>
+      <c r="CN35" t="inlineStr"/>
+      <c r="CO35" t="inlineStr"/>
+      <c r="CP35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -7638,7 +7757,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>0E4QXUam15QfaVaTAymHn2</t>
+          <t>3Dk2HhiCr35RYXuSaVOvs6</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7658,7 +7777,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>BUF:343907</t>
+          <t>BUF:343892</t>
         </is>
       </c>
       <c r="H36" t="n">
@@ -7801,20 +7920,20 @@
       </c>
       <c r="CD36" t="inlineStr">
         <is>
-          <t>3qJ9B5zvT7$hh913fcAFEQ</t>
+          <t>3qJ9B5zvT7$hh913fcAFEj</t>
         </is>
       </c>
       <c r="CE36" t="n">
         <v>1</v>
       </c>
       <c r="CF36" t="n">
-        <v>12.0248764381316</v>
+        <v>118.876854433513</v>
       </c>
       <c r="CG36" t="n">
-        <v>4.922164</v>
+        <v>162.444519</v>
       </c>
       <c r="CH36" t="n">
-        <v>4.922164</v>
+        <v>162.444519</v>
       </c>
       <c r="CI36" t="inlineStr">
         <is>
@@ -7829,6 +7948,9 @@
       <c r="CK36" t="inlineStr"/>
       <c r="CL36" t="inlineStr"/>
       <c r="CM36" t="inlineStr"/>
+      <c r="CN36" t="inlineStr"/>
+      <c r="CO36" t="inlineStr"/>
+      <c r="CP36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -7839,7 +7961,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>0WtOOP9cn9MBUnf0AHUQfJ</t>
+          <t>3AGSwy4Cv9YOBE5MpdNLQt</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7859,7 +7981,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>BUF:343910</t>
+          <t>BUF:343901</t>
         </is>
       </c>
       <c r="H37" t="n">
@@ -8002,20 +8124,20 @@
       </c>
       <c r="CD37" t="inlineStr">
         <is>
-          <t>3qJ9B5zvT7$hh913fcAFEV</t>
+          <t>3qJ9B5zvT7$hh913fcAFEa</t>
         </is>
       </c>
       <c r="CE37" t="n">
         <v>1</v>
       </c>
       <c r="CF37" t="n">
-        <v>18.0302029491287</v>
+        <v>36.0606998520392</v>
       </c>
       <c r="CG37" t="n">
-        <v>7.9934815</v>
+        <v>25.4851555</v>
       </c>
       <c r="CH37" t="n">
-        <v>7.9934815</v>
+        <v>25.4851555</v>
       </c>
       <c r="CI37" t="inlineStr">
         <is>
@@ -8030,17 +8152,20 @@
       <c r="CK37" t="inlineStr"/>
       <c r="CL37" t="inlineStr"/>
       <c r="CM37" t="inlineStr"/>
+      <c r="CN37" t="inlineStr"/>
+      <c r="CO37" t="inlineStr"/>
+      <c r="CP37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
         <v>1251</v>
       </c>
       <c r="B38" t="n">
-        <v>1212</v>
+        <v>1209</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2VPSmwn8f80wlwsZLQwj7f</t>
+          <t>0E4QXUam15QfaVaTAymHn2</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -8060,7 +8185,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>PAA:345416</t>
+          <t>BUF:343907</t>
         </is>
       </c>
       <c r="H38" t="n">
@@ -8092,11 +8217,11 @@
       <c r="AB38" t="inlineStr"/>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>OG3</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="AD38" t="n">
-        <v>11.947</v>
+        <v>0</v>
       </c>
       <c r="AE38" t="inlineStr"/>
       <c r="AF38" t="inlineStr"/>
@@ -8152,7 +8277,7 @@
       <c r="BR38" t="inlineStr"/>
       <c r="BS38" t="inlineStr">
         <is>
-          <t>PAA</t>
+          <t>BUF</t>
         </is>
       </c>
       <c r="BT38" t="inlineStr">
@@ -8167,17 +8292,17 @@
       </c>
       <c r="BV38" t="inlineStr">
         <is>
-          <t>Pausenfläche PS</t>
+          <t>Bearbeitet Umgebungsflächen</t>
         </is>
       </c>
       <c r="BW38" t="inlineStr">
         <is>
-          <t>Pausenfläche (Hartplatz) für ges.Schulanlage. Auf Erweiterungsbau sollen auch Dachflächen als Pausenplatz nutzbar sein</t>
+          <t>Alle restlichen bearbeiteten Aussenanlagenflächen bis zur Grundstücksgrenze</t>
         </is>
       </c>
       <c r="BX38" t="inlineStr">
         <is>
-          <t>PAA  -  Pausenfläche PS</t>
+          <t>BUF  -  Bearbeitet Umgebungsflächen</t>
         </is>
       </c>
       <c r="BY38" t="inlineStr">
@@ -8203,20 +8328,20 @@
       </c>
       <c r="CD38" t="inlineStr">
         <is>
-          <t>2VFBkNPLX5hxPkFzLFhskt</t>
+          <t>3qJ9B5zvT7$hh913fcAFEQ</t>
         </is>
       </c>
       <c r="CE38" t="n">
-        <v>1.001</v>
+        <v>1</v>
       </c>
       <c r="CF38" t="n">
-        <v>61.8374883969868</v>
+        <v>12.0248764381316</v>
       </c>
       <c r="CG38" t="n">
-        <v>126.246645</v>
+        <v>4.922164</v>
       </c>
       <c r="CH38" t="n">
-        <v>126.372891645</v>
+        <v>4.922164</v>
       </c>
       <c r="CI38" t="inlineStr">
         <is>
@@ -8225,27 +8350,26 @@
       </c>
       <c r="CJ38" t="inlineStr">
         <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="CK38" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="CL38" t="n">
-        <v>400</v>
-      </c>
+          <t>???</t>
+        </is>
+      </c>
+      <c r="CK38" t="inlineStr"/>
+      <c r="CL38" t="inlineStr"/>
       <c r="CM38" t="inlineStr"/>
+      <c r="CN38" t="inlineStr"/>
+      <c r="CO38" t="inlineStr"/>
+      <c r="CP38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
         <v>1252</v>
       </c>
       <c r="B39" t="n">
-        <v>1209</v>
+        <v>1212</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2VcirkfBf6ahuppLqfjuCo</t>
+          <t>2MZESDDfb379fB261rIbnR</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8265,7 +8389,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>ALL:343925</t>
+          <t>PAA:345416</t>
         </is>
       </c>
       <c r="H39" t="n">
@@ -8297,11 +8421,11 @@
       <c r="AB39" t="inlineStr"/>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>OG3</t>
         </is>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>11.947</v>
       </c>
       <c r="AE39" t="inlineStr"/>
       <c r="AF39" t="inlineStr"/>
@@ -8357,7 +8481,7 @@
       <c r="BR39" t="inlineStr"/>
       <c r="BS39" t="inlineStr">
         <is>
-          <t>ALL</t>
+          <t>PAA</t>
         </is>
       </c>
       <c r="BT39" t="inlineStr">
@@ -8372,17 +8496,17 @@
       </c>
       <c r="BV39" t="inlineStr">
         <is>
-          <t>Allwetterplatz mit Sportbelag</t>
+          <t>Pausenfläche PS</t>
         </is>
       </c>
       <c r="BW39" t="inlineStr">
         <is>
-          <t>idealerweise 26 x 40m - ebenerdiger sportfunktionaler Allwetterplatz (EPDM-Belag, Ballfang) mit minimalen Spielfeld-Abmessungen 24 x 13m plus Sicherheitsraum umlaufend b=1m zwingend nachzuweisen</t>
+          <t>Pausenfläche (Hartplatz) für ges.Schulanlage. Auf Erweiterungsbau sollen auch Dachflächen als Pausenplatz nutzbar sein</t>
         </is>
       </c>
       <c r="BX39" t="inlineStr">
         <is>
-          <t>ALL  -  Allwetterplatz mit Sportbelag</t>
+          <t>PAA  -  Pausenfläche PS</t>
         </is>
       </c>
       <c r="BY39" t="inlineStr">
@@ -8408,20 +8532,20 @@
       </c>
       <c r="CD39" t="inlineStr">
         <is>
-          <t>3qJ9B5zvT7$hh913fcAFEC</t>
+          <t>2VFBkNPLX5hxPkFzLFhskt</t>
         </is>
       </c>
       <c r="CE39" t="n">
-        <v>1</v>
+        <v>1.001</v>
       </c>
       <c r="CF39" t="n">
-        <v>82.51586312796729</v>
+        <v>61.8367587494543</v>
       </c>
       <c r="CG39" t="n">
-        <v>396.6236325</v>
+        <v>126.1984585</v>
       </c>
       <c r="CH39" t="n">
-        <v>396.6236325</v>
+        <v>126.3246569585</v>
       </c>
       <c r="CI39" t="inlineStr">
         <is>
@@ -8434,23 +8558,26 @@
         </is>
       </c>
       <c r="CK39" t="n">
-        <v>10.4</v>
+        <v>10.8</v>
       </c>
       <c r="CL39" t="n">
-        <v>390</v>
+        <v>400</v>
       </c>
       <c r="CM39" t="inlineStr"/>
+      <c r="CN39" t="inlineStr"/>
+      <c r="CO39" t="inlineStr"/>
+      <c r="CP39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
         <v>1253</v>
       </c>
       <c r="B40" t="n">
-        <v>1209</v>
+        <v>1212</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>07p_i19HfFMxUYszLXHx0R</t>
+          <t>2VPSmwn8f80wlwsZLQwj7f</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8470,7 +8597,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>PPA:343898</t>
+          <t>PAA:345416</t>
         </is>
       </c>
       <c r="H40" t="n">
@@ -8502,11 +8629,11 @@
       <c r="AB40" t="inlineStr"/>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>OG3</t>
         </is>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>11.947</v>
       </c>
       <c r="AE40" t="inlineStr"/>
       <c r="AF40" t="inlineStr"/>
@@ -8562,7 +8689,7 @@
       <c r="BR40" t="inlineStr"/>
       <c r="BS40" t="inlineStr">
         <is>
-          <t>PPA</t>
+          <t>PAA</t>
         </is>
       </c>
       <c r="BT40" t="inlineStr">
@@ -8577,17 +8704,17 @@
       </c>
       <c r="BV40" t="inlineStr">
         <is>
-          <t>Parkplätze PW (Normbedarf)</t>
+          <t>Pausenfläche PS</t>
         </is>
       </c>
       <c r="BW40" t="inlineStr">
         <is>
-          <t>Gesamtangebot für Schulpersonal, Besuchende, Anlieferung, IV-Transport usw. Reduktionsfaktor nicht berücksichtigt&amp;#10;1 PP-IV auf Anlage, 5 PP ausgelagert in TG vom GFA Wildbach, Wildbachstr. 11</t>
+          <t>Pausenfläche (Hartplatz) für ges.Schulanlage. Auf Erweiterungsbau sollen auch Dachflächen als Pausenplatz nutzbar sein</t>
         </is>
       </c>
       <c r="BX40" t="inlineStr">
         <is>
-          <t>PPA  -  Parkplätze PW (Normbedarf)</t>
+          <t>PAA  -  Pausenfläche PS</t>
         </is>
       </c>
       <c r="BY40" t="inlineStr">
@@ -8613,20 +8740,20 @@
       </c>
       <c r="CD40" t="inlineStr">
         <is>
-          <t>3qJ9B5zvT7$hh913fcAFEZ</t>
+          <t>2VFBkNPLX5hxPkFzLFhskt</t>
         </is>
       </c>
       <c r="CE40" t="n">
-        <v>1</v>
+        <v>1.001</v>
       </c>
       <c r="CF40" t="n">
-        <v>20.3229188998477</v>
+        <v>61.8374883969868</v>
       </c>
       <c r="CG40" t="n">
-        <v>17.289957</v>
+        <v>126.246645</v>
       </c>
       <c r="CH40" t="n">
-        <v>17.289957</v>
+        <v>126.372891645</v>
       </c>
       <c r="CI40" t="inlineStr">
         <is>
@@ -8639,12 +8766,15 @@
         </is>
       </c>
       <c r="CK40" t="n">
-        <v>10.1</v>
+        <v>10.8</v>
       </c>
       <c r="CL40" t="n">
-        <v>12</v>
+        <v>400</v>
       </c>
       <c r="CM40" t="inlineStr"/>
+      <c r="CN40" t="inlineStr"/>
+      <c r="CO40" t="inlineStr"/>
+      <c r="CP40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -8655,7 +8785,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>1MqvEZmU539xzlBdmFG0Gt</t>
+          <t>2VcirkfBf6ahuppLqfjuCo</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8675,7 +8805,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>VEL_L:343934</t>
+          <t>ALL:343925</t>
         </is>
       </c>
       <c r="H41" t="n">
@@ -8767,7 +8897,7 @@
       <c r="BR41" t="inlineStr"/>
       <c r="BS41" t="inlineStr">
         <is>
-          <t>VEL_L</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="BT41" t="inlineStr">
@@ -8782,17 +8912,17 @@
       </c>
       <c r="BV41" t="inlineStr">
         <is>
-          <t>Velo- Abstellplätze Schulpersonal</t>
+          <t>Allwetterplatz mit Sportbelag</t>
         </is>
       </c>
       <c r="BW41" t="inlineStr">
         <is>
-          <t>8 Stück, Gedeckt und gegen Diebstahl und Vanalismus geschützt</t>
+          <t>idealerweise 26 x 40m - ebenerdiger sportfunktionaler Allwetterplatz (EPDM-Belag, Ballfang) mit minimalen Spielfeld-Abmessungen 24 x 13m plus Sicherheitsraum umlaufend b=1m zwingend nachzuweisen</t>
         </is>
       </c>
       <c r="BX41" t="inlineStr">
         <is>
-          <t>VEL_L  -  Velo- Abstellplätze Schulpersonal</t>
+          <t>ALL  -  Allwetterplatz mit Sportbelag</t>
         </is>
       </c>
       <c r="BY41" t="inlineStr">
@@ -8818,20 +8948,20 @@
       </c>
       <c r="CD41" t="inlineStr">
         <is>
-          <t>3qJ9B5zvT7$hh913fcAFE7</t>
+          <t>3qJ9B5zvT7$hh913fcAFEC</t>
         </is>
       </c>
       <c r="CE41" t="n">
         <v>1</v>
       </c>
       <c r="CF41" t="n">
-        <v>9.201563573455161</v>
+        <v>82.51586312796729</v>
       </c>
       <c r="CG41" t="n">
-        <v>5.20168</v>
+        <v>396.6236325</v>
       </c>
       <c r="CH41" t="n">
-        <v>5.20168</v>
+        <v>396.6236325</v>
       </c>
       <c r="CI41" t="inlineStr">
         <is>
@@ -8840,14 +8970,19 @@
       </c>
       <c r="CJ41" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="CK41" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="CL41" t="inlineStr"/>
+        <v>10.4</v>
+      </c>
+      <c r="CL41" t="n">
+        <v>390</v>
+      </c>
       <c r="CM41" t="inlineStr"/>
+      <c r="CN41" t="inlineStr"/>
+      <c r="CO41" t="inlineStr"/>
+      <c r="CP41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -8858,7 +8993,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>3WAjbS9Tz63fT8SRxhsEgW</t>
+          <t>07p_i19HfFMxUYszLXHx0R</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8878,7 +9013,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>ASP:345271</t>
+          <t>PPA:343898</t>
         </is>
       </c>
       <c r="H42" t="n">
@@ -8970,7 +9105,7 @@
       <c r="BR42" t="inlineStr"/>
       <c r="BS42" t="inlineStr">
         <is>
-          <t>ASP</t>
+          <t>PPA</t>
         </is>
       </c>
       <c r="BT42" t="inlineStr">
@@ -8985,17 +9120,17 @@
       </c>
       <c r="BV42" t="inlineStr">
         <is>
-          <t>Aussensitzplatz Mensa/Verpflegung</t>
+          <t>Parkplätze PW (Normbedarf)</t>
         </is>
       </c>
       <c r="BW42" t="inlineStr">
         <is>
-          <t>Teil der Pausenfläche PS</t>
+          <t>Gesamtangebot für Schulpersonal, Besuchende, Anlieferung, IV-Transport usw. Reduktionsfaktor nicht berücksichtigt&amp;#10;1 PP-IV auf Anlage, 5 PP ausgelagert in TG vom GFA Wildbach, Wildbachstr. 11</t>
         </is>
       </c>
       <c r="BX42" t="inlineStr">
         <is>
-          <t>ASP  -  Aussensitzplatz Mensa/Verpflegung</t>
+          <t>PPA  -  Parkplätze PW (Normbedarf)</t>
         </is>
       </c>
       <c r="BY42" t="inlineStr">
@@ -9021,24 +9156,24 @@
       </c>
       <c r="CD42" t="inlineStr">
         <is>
-          <t>035uX0PqXCW8$9o28UaoyD</t>
+          <t>3qJ9B5zvT7$hh913fcAFEZ</t>
         </is>
       </c>
       <c r="CE42" t="n">
         <v>1</v>
       </c>
       <c r="CF42" t="n">
-        <v>33.8501433189163</v>
+        <v>20.3229188998477</v>
       </c>
       <c r="CG42" t="n">
-        <v>29.849794</v>
+        <v>17.289957</v>
       </c>
       <c r="CH42" t="n">
-        <v>29.849794</v>
+        <v>17.289957</v>
       </c>
       <c r="CI42" t="inlineStr">
         <is>
-          <t>ANF</t>
+          <t>BUF</t>
         </is>
       </c>
       <c r="CJ42" t="inlineStr">
@@ -9047,12 +9182,15 @@
         </is>
       </c>
       <c r="CK42" t="n">
-        <v>10.4</v>
+        <v>10.1</v>
       </c>
       <c r="CL42" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="CM42" t="inlineStr"/>
+      <c r="CN42" t="inlineStr"/>
+      <c r="CO42" t="inlineStr"/>
+      <c r="CP42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -9063,7 +9201,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2F9RWBhUfEZ8$cJ_kTeVpx</t>
+          <t>3dUr5q39zEXBCsj4PLV405</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -9083,7 +9221,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>PAK:343886</t>
+          <t>PAG:329111</t>
         </is>
       </c>
       <c r="H43" t="n">
@@ -9175,7 +9313,7 @@
       <c r="BR43" t="inlineStr"/>
       <c r="BS43" t="inlineStr">
         <is>
-          <t>PAK</t>
+          <t>PAG</t>
         </is>
       </c>
       <c r="BT43" t="inlineStr">
@@ -9190,13 +9328,17 @@
       </c>
       <c r="BV43" t="inlineStr">
         <is>
-          <t>Aussenraum Kindergarten</t>
-        </is>
-      </c>
-      <c r="BW43" t="inlineStr"/>
+          <t xml:space="preserve">Gedeckter Aussenbereich </t>
+        </is>
+      </c>
+      <c r="BW43" t="inlineStr">
+        <is>
+          <t>Vordach, freistehender Unterstand oder Auskragung Gebäude</t>
+        </is>
+      </c>
       <c r="BX43" t="inlineStr">
         <is>
-          <t>PAK  -  Aussenraum Kindergarten</t>
+          <t xml:space="preserve">PAG  -  Gedeckter Aussenbereich </t>
         </is>
       </c>
       <c r="BY43" t="inlineStr">
@@ -9208,7 +9350,7 @@
         <v>0</v>
       </c>
       <c r="CA43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CB43" t="inlineStr">
         <is>
@@ -9222,38 +9364,39 @@
       </c>
       <c r="CD43" t="inlineStr">
         <is>
-          <t>3qJ9B5zvT7$hh913fcAFEt</t>
+          <t>1QkPwOj9z05w845KZPzMyj</t>
         </is>
       </c>
       <c r="CE43" t="n">
         <v>1</v>
       </c>
       <c r="CF43" t="n">
-        <v>70.7275988525333</v>
+        <v>36.5379660958738</v>
       </c>
       <c r="CG43" t="n">
-        <v>295.86007</v>
+        <v>73.566976</v>
       </c>
       <c r="CH43" t="n">
-        <v>295.86007</v>
+        <v>73.566976</v>
       </c>
       <c r="CI43" t="inlineStr">
         <is>
-          <t>BUF</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="CJ43" t="inlineStr">
         <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="CK43" t="n">
-        <v>10.8</v>
-      </c>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="CK43" t="inlineStr"/>
       <c r="CL43" t="n">
-        <v>150</v>
+        <v>54</v>
       </c>
       <c r="CM43" t="inlineStr"/>
+      <c r="CN43" t="inlineStr"/>
+      <c r="CO43" t="inlineStr"/>
+      <c r="CP43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -9264,7 +9407,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>3vBeHUwhfB5OcVQruWBfzN</t>
+          <t>3WAjbS9Tz63fT8SRxhsEgW</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9284,7 +9427,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>PAA:329291</t>
+          <t>ASP:345271</t>
         </is>
       </c>
       <c r="H44" t="n">
@@ -9376,7 +9519,7 @@
       <c r="BR44" t="inlineStr"/>
       <c r="BS44" t="inlineStr">
         <is>
-          <t>PAA</t>
+          <t>ASP</t>
         </is>
       </c>
       <c r="BT44" t="inlineStr">
@@ -9391,17 +9534,17 @@
       </c>
       <c r="BV44" t="inlineStr">
         <is>
-          <t>Pausenfläche PS</t>
+          <t>Aussensitzplatz Mensa/Verpflegung</t>
         </is>
       </c>
       <c r="BW44" t="inlineStr">
         <is>
-          <t>Pausenfläche (Hartplatz) für ges.Schulanlage. Auf Erweiterungsbau sollen auch Dachflächen als Pausenplatz nutzbar sein</t>
+          <t>Teil der Pausenfläche PS</t>
         </is>
       </c>
       <c r="BX44" t="inlineStr">
         <is>
-          <t>PAA  -  Pausenfläche PS</t>
+          <t>ASP  -  Aussensitzplatz Mensa/Verpflegung</t>
         </is>
       </c>
       <c r="BY44" t="inlineStr">
@@ -9427,24 +9570,24 @@
       </c>
       <c r="CD44" t="inlineStr">
         <is>
-          <t>1QkPwOj9z05w845KZPzMpn</t>
+          <t>035uX0PqXCW8$9o28UaoyD</t>
         </is>
       </c>
       <c r="CE44" t="n">
         <v>1</v>
       </c>
       <c r="CF44" t="n">
-        <v>228.018781084836</v>
+        <v>33.8501433189163</v>
       </c>
       <c r="CG44" t="n">
-        <v>627.669683</v>
+        <v>29.849794</v>
       </c>
       <c r="CH44" t="n">
-        <v>627.669683</v>
+        <v>29.849794</v>
       </c>
       <c r="CI44" t="inlineStr">
         <is>
-          <t>BUF</t>
+          <t>ANF</t>
         </is>
       </c>
       <c r="CJ44" t="inlineStr">
@@ -9453,23 +9596,26 @@
         </is>
       </c>
       <c r="CK44" t="n">
-        <v>10.8</v>
+        <v>10.4</v>
       </c>
       <c r="CL44" t="n">
-        <v>400</v>
+        <v>16</v>
       </c>
       <c r="CM44" t="inlineStr"/>
+      <c r="CN44" t="inlineStr"/>
+      <c r="CO44" t="inlineStr"/>
+      <c r="CP44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
         <v>1258</v>
       </c>
       <c r="B45" t="n">
-        <v>1212</v>
+        <v>1209</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2MZESDDfb379fB261rIbnR</t>
+          <t>2F9RWBhUfEZ8$cJ_kTeVpx</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9489,7 +9635,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>PAA:345416</t>
+          <t>PAK:343886</t>
         </is>
       </c>
       <c r="H45" t="n">
@@ -9521,11 +9667,11 @@
       <c r="AB45" t="inlineStr"/>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>OG3</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="AD45" t="n">
-        <v>11.947</v>
+        <v>0</v>
       </c>
       <c r="AE45" t="inlineStr"/>
       <c r="AF45" t="inlineStr"/>
@@ -9581,7 +9727,7 @@
       <c r="BR45" t="inlineStr"/>
       <c r="BS45" t="inlineStr">
         <is>
-          <t>PAA</t>
+          <t>PAK</t>
         </is>
       </c>
       <c r="BT45" t="inlineStr">
@@ -9596,17 +9742,13 @@
       </c>
       <c r="BV45" t="inlineStr">
         <is>
-          <t>Pausenfläche PS</t>
-        </is>
-      </c>
-      <c r="BW45" t="inlineStr">
-        <is>
-          <t>Pausenfläche (Hartplatz) für ges.Schulanlage. Auf Erweiterungsbau sollen auch Dachflächen als Pausenplatz nutzbar sein</t>
-        </is>
-      </c>
+          <t>Aussenraum Kindergarten</t>
+        </is>
+      </c>
+      <c r="BW45" t="inlineStr"/>
       <c r="BX45" t="inlineStr">
         <is>
-          <t>PAA  -  Pausenfläche PS</t>
+          <t>PAK  -  Aussenraum Kindergarten</t>
         </is>
       </c>
       <c r="BY45" t="inlineStr">
@@ -9618,34 +9760,34 @@
         <v>0</v>
       </c>
       <c r="CA45" t="n">
+        <v>2</v>
+      </c>
+      <c r="CB45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="CC45" t="inlineStr">
+        <is>
+          <t>Rooms</t>
+        </is>
+      </c>
+      <c r="CD45" t="inlineStr">
+        <is>
+          <t>3qJ9B5zvT7$hh913fcAFEt</t>
+        </is>
+      </c>
+      <c r="CE45" t="n">
         <v>1</v>
       </c>
-      <c r="CB45" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="CC45" t="inlineStr">
-        <is>
-          <t>Rooms</t>
-        </is>
-      </c>
-      <c r="CD45" t="inlineStr">
-        <is>
-          <t>2VFBkNPLX5hxPkFzLFhskt</t>
-        </is>
-      </c>
-      <c r="CE45" t="n">
-        <v>1.001</v>
-      </c>
       <c r="CF45" t="n">
-        <v>61.8367587494543</v>
+        <v>70.7275988525333</v>
       </c>
       <c r="CG45" t="n">
-        <v>126.1984585</v>
+        <v>295.86007</v>
       </c>
       <c r="CH45" t="n">
-        <v>126.3246569585</v>
+        <v>295.86007</v>
       </c>
       <c r="CI45" t="inlineStr">
         <is>
@@ -9654,27 +9796,30 @@
       </c>
       <c r="CJ45" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="CK45" t="n">
         <v>10.8</v>
       </c>
       <c r="CL45" t="n">
-        <v>400</v>
+        <v>150</v>
       </c>
       <c r="CM45" t="inlineStr"/>
+      <c r="CN45" t="inlineStr"/>
+      <c r="CO45" t="inlineStr"/>
+      <c r="CP45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
         <v>1259</v>
       </c>
       <c r="B46" t="n">
-        <v>1207</v>
+        <v>1209</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>0ZrdVUR4b0zxBrw6VrPmpy</t>
+          <t>3vBeHUwhfB5OcVQruWBfzN</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9694,7 +9839,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>HTR_S:340473</t>
+          <t>PAA:329291</t>
         </is>
       </c>
       <c r="H46" t="n">
@@ -9713,7 +9858,7 @@
       <c r="S46" t="inlineStr"/>
       <c r="T46" t="inlineStr">
         <is>
-          <t>INTERNAL</t>
+          <t>EXTERNAL</t>
         </is>
       </c>
       <c r="U46" t="inlineStr"/>
@@ -9726,11 +9871,11 @@
       <c r="AB46" t="inlineStr"/>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>UG2</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="AD46" t="n">
-        <v>-8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AE46" t="inlineStr"/>
       <c r="AF46" t="inlineStr"/>
@@ -9786,41 +9931,41 @@
       <c r="BR46" t="inlineStr"/>
       <c r="BS46" t="inlineStr">
         <is>
-          <t>HTR_S</t>
+          <t>PAA</t>
         </is>
       </c>
       <c r="BT46" t="inlineStr">
         <is>
-          <t>Funktionsfläche</t>
+          <t>Aussenbereich</t>
         </is>
       </c>
       <c r="BU46" t="inlineStr">
         <is>
-          <t>Haustechnik</t>
+          <t>Aussenanlagen</t>
         </is>
       </c>
       <c r="BV46" t="inlineStr">
         <is>
-          <t>Sanitär</t>
+          <t>Pausenfläche PS</t>
         </is>
       </c>
       <c r="BW46" t="inlineStr">
         <is>
-          <t>Raumhöhe mind. 3.5m im Licht</t>
+          <t>Pausenfläche (Hartplatz) für ges.Schulanlage. Auf Erweiterungsbau sollen auch Dachflächen als Pausenplatz nutzbar sein</t>
         </is>
       </c>
       <c r="BX46" t="inlineStr">
         <is>
-          <t>HTR_S  -  Sanitär</t>
+          <t>PAA  -  Pausenfläche PS</t>
         </is>
       </c>
       <c r="BY46" t="inlineStr">
         <is>
-          <t>INTERNAL</t>
+          <t>EXTERNAL</t>
         </is>
       </c>
       <c r="BZ46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CA46" t="n">
         <v>1</v>
@@ -9837,47 +9982,52 @@
       </c>
       <c r="CD46" t="inlineStr">
         <is>
-          <t>3VbCMl1_928hbAKPG5KnoA</t>
+          <t>1QkPwOj9z05w845KZPzMpn</t>
         </is>
       </c>
       <c r="CE46" t="n">
-        <v>4.121</v>
+        <v>1</v>
       </c>
       <c r="CF46" t="n">
-        <v>29.2296306506672</v>
+        <v>228.018781084836</v>
       </c>
       <c r="CG46" t="n">
-        <v>38.861445</v>
+        <v>627.669683</v>
       </c>
       <c r="CH46" t="n">
-        <v>160.148014845</v>
+        <v>627.669683</v>
       </c>
       <c r="CI46" t="inlineStr">
         <is>
-          <t>FF</t>
-        </is>
-      </c>
-      <c r="CJ46" t="inlineStr"/>
+          <t>BUF</t>
+        </is>
+      </c>
+      <c r="CJ46" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
       <c r="CK46" t="n">
-        <v>8.300000000000001</v>
+        <v>10.8</v>
       </c>
       <c r="CL46" t="n">
-        <v>40</v>
-      </c>
-      <c r="CM46" t="n">
-        <v>3.5</v>
-      </c>
+        <v>400</v>
+      </c>
+      <c r="CM46" t="inlineStr"/>
+      <c r="CN46" t="inlineStr"/>
+      <c r="CO46" t="inlineStr"/>
+      <c r="CP46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
         <v>1260</v>
       </c>
       <c r="B47" t="n">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>1R9Imo_5167B$XHbYy7aZ6</t>
+          <t>3LuW9jHbHBBAyJit_$Yn3$</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9897,7 +10047,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>HTR_E:342390</t>
+          <t>HTR_L:340296</t>
         </is>
       </c>
       <c r="H47" t="n">
@@ -9929,11 +10079,11 @@
       <c r="AB47" t="inlineStr"/>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>UG1</t>
+          <t>UG2</t>
         </is>
       </c>
       <c r="AD47" t="n">
-        <v>-3.78</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="AE47" t="inlineStr"/>
       <c r="AF47" t="inlineStr"/>
@@ -9989,7 +10139,7 @@
       <c r="BR47" t="inlineStr"/>
       <c r="BS47" t="inlineStr">
         <is>
-          <t>HTR_E</t>
+          <t>HTR_L</t>
         </is>
       </c>
       <c r="BT47" t="inlineStr">
@@ -10004,17 +10154,17 @@
       </c>
       <c r="BV47" t="inlineStr">
         <is>
-          <t>Elektohauptverteilung</t>
+          <t>Lüftung</t>
         </is>
       </c>
       <c r="BW47" t="inlineStr">
         <is>
-          <t>Raumhöhe mind. 3.0m im Licht</t>
+          <t>Raumhöhe mind. 3.5m im Licht</t>
         </is>
       </c>
       <c r="BX47" t="inlineStr">
         <is>
-          <t>HTR_E  -  Elektohauptverteilung</t>
+          <t>HTR_L  -  Lüftung</t>
         </is>
       </c>
       <c r="BY47" t="inlineStr">
@@ -10040,20 +10190,20 @@
       </c>
       <c r="CD47" t="inlineStr">
         <is>
-          <t>1QH5Axl111J9SJj2E3W4wQ</t>
+          <t>3VbCMl1_928hbAKPG5Knmx</t>
         </is>
       </c>
       <c r="CE47" t="n">
-        <v>3.421</v>
+        <v>4.121</v>
       </c>
       <c r="CF47" t="n">
-        <v>21.5722949304711</v>
+        <v>57.8747961939876</v>
       </c>
       <c r="CG47" t="n">
-        <v>25.280915</v>
+        <v>130.4597315</v>
       </c>
       <c r="CH47" t="n">
-        <v>86.48601021499999</v>
+        <v>537.6245535115</v>
       </c>
       <c r="CI47" t="inlineStr">
         <is>
@@ -10062,25 +10212,28 @@
       </c>
       <c r="CJ47" t="inlineStr"/>
       <c r="CK47" t="n">
-        <v>8.300000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="CL47" t="n">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="CM47" t="n">
         <v>3.5</v>
       </c>
+      <c r="CN47" t="inlineStr"/>
+      <c r="CO47" t="inlineStr"/>
+      <c r="CP47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
         <v>1261</v>
       </c>
       <c r="B48" t="n">
-        <v>1209</v>
+        <v>1207</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>3dUr5q39zEXBCsj4PLV405</t>
+          <t>0ZrdVUR4b0zxBrw6VrPmpy</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -10100,7 +10253,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>PAG:329111</t>
+          <t>HTR_S:340473</t>
         </is>
       </c>
       <c r="H48" t="n">
@@ -10119,7 +10272,7 @@
       <c r="S48" t="inlineStr"/>
       <c r="T48" t="inlineStr">
         <is>
-          <t>EXTERNAL</t>
+          <t>INTERNAL</t>
         </is>
       </c>
       <c r="U48" t="inlineStr"/>
@@ -10132,11 +10285,11 @@
       <c r="AB48" t="inlineStr"/>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>UG2</t>
         </is>
       </c>
       <c r="AD48" t="n">
-        <v>0</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="AE48" t="inlineStr"/>
       <c r="AF48" t="inlineStr"/>
@@ -10192,41 +10345,41 @@
       <c r="BR48" t="inlineStr"/>
       <c r="BS48" t="inlineStr">
         <is>
-          <t>PAG</t>
+          <t>HTR_S</t>
         </is>
       </c>
       <c r="BT48" t="inlineStr">
         <is>
-          <t>Aussenbereich</t>
+          <t>Funktionsfläche</t>
         </is>
       </c>
       <c r="BU48" t="inlineStr">
         <is>
-          <t>Aussenanlagen</t>
+          <t>Haustechnik</t>
         </is>
       </c>
       <c r="BV48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gedeckter Aussenbereich </t>
+          <t>Sanitär</t>
         </is>
       </c>
       <c r="BW48" t="inlineStr">
         <is>
-          <t>Vordach, freistehender Unterstand oder Auskragung Gebäude</t>
+          <t>Raumhöhe mind. 3.5m im Licht</t>
         </is>
       </c>
       <c r="BX48" t="inlineStr">
         <is>
-          <t xml:space="preserve">PAG  -  Gedeckter Aussenbereich </t>
+          <t>HTR_S  -  Sanitär</t>
         </is>
       </c>
       <c r="BY48" t="inlineStr">
         <is>
-          <t>EXTERNAL</t>
+          <t>INTERNAL</t>
         </is>
       </c>
       <c r="BZ48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CA48" t="n">
         <v>1</v>
@@ -10243,47 +10396,50 @@
       </c>
       <c r="CD48" t="inlineStr">
         <is>
-          <t>1QkPwOj9z05w845KZPzMyj</t>
+          <t>3VbCMl1_928hbAKPG5KnoA</t>
         </is>
       </c>
       <c r="CE48" t="n">
-        <v>1</v>
+        <v>4.121</v>
       </c>
       <c r="CF48" t="n">
-        <v>36.5379660958738</v>
+        <v>29.2296306506672</v>
       </c>
       <c r="CG48" t="n">
-        <v>73.566976</v>
+        <v>38.861445</v>
       </c>
       <c r="CH48" t="n">
-        <v>73.566976</v>
+        <v>160.148014845</v>
       </c>
       <c r="CI48" t="inlineStr">
         <is>
-          <t>AGF</t>
-        </is>
-      </c>
-      <c r="CJ48" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="CK48" t="inlineStr"/>
+          <t>FF</t>
+        </is>
+      </c>
+      <c r="CJ48" t="inlineStr"/>
+      <c r="CK48" t="n">
+        <v>8.300000000000001</v>
+      </c>
       <c r="CL48" t="n">
-        <v>54</v>
-      </c>
-      <c r="CM48" t="inlineStr"/>
+        <v>40</v>
+      </c>
+      <c r="CM48" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="CN48" t="inlineStr"/>
+      <c r="CO48" t="inlineStr"/>
+      <c r="CP48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
         <v>1262</v>
       </c>
       <c r="B49" t="n">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>0teRCO0lj5OQYpPkvQztRq</t>
+          <t>1R9Imo_5167B$XHbYy7aZ6</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10303,7 +10459,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>ESP:329276</t>
+          <t>HTR_E:342390</t>
         </is>
       </c>
       <c r="H49" t="n">
@@ -10322,7 +10478,7 @@
       <c r="S49" t="inlineStr"/>
       <c r="T49" t="inlineStr">
         <is>
-          <t>EXTERNAL</t>
+          <t>INTERNAL</t>
         </is>
       </c>
       <c r="U49" t="inlineStr"/>
@@ -10335,11 +10491,11 @@
       <c r="AB49" t="inlineStr"/>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>UG1</t>
         </is>
       </c>
       <c r="AD49" t="n">
-        <v>0</v>
+        <v>-3.78</v>
       </c>
       <c r="AE49" t="inlineStr"/>
       <c r="AF49" t="inlineStr"/>
@@ -10395,28 +10551,32 @@
       <c r="BR49" t="inlineStr"/>
       <c r="BS49" t="inlineStr">
         <is>
-          <t>ESP</t>
+          <t>HTR_E</t>
         </is>
       </c>
       <c r="BT49" t="inlineStr">
         <is>
-          <t>Sportbereich</t>
+          <t>Funktionsfläche</t>
         </is>
       </c>
       <c r="BU49" t="inlineStr">
         <is>
-          <t>Sporthallen</t>
+          <t>Haustechnik</t>
         </is>
       </c>
       <c r="BV49" t="inlineStr">
         <is>
-          <t>Eingangshalle Sporthalle</t>
-        </is>
-      </c>
-      <c r="BW49" t="inlineStr"/>
+          <t>Elektohauptverteilung</t>
+        </is>
+      </c>
+      <c r="BW49" t="inlineStr">
+        <is>
+          <t>Raumhöhe mind. 3.0m im Licht</t>
+        </is>
+      </c>
       <c r="BX49" t="inlineStr">
         <is>
-          <t>ESP  -  Eingangshalle Sporthalle</t>
+          <t>HTR_E  -  Elektohauptverteilung</t>
         </is>
       </c>
       <c r="BY49" t="inlineStr">
@@ -10442,34 +10602,39 @@
       </c>
       <c r="CD49" t="inlineStr">
         <is>
-          <t>1QkPwOj9z05w845KZPzMo6</t>
+          <t>1QH5Axl111J9SJj2E3W4wQ</t>
         </is>
       </c>
       <c r="CE49" t="n">
-        <v>1</v>
+        <v>3.421</v>
       </c>
       <c r="CF49" t="n">
-        <v>32.1201520903664</v>
+        <v>21.5722949304711</v>
       </c>
       <c r="CG49" t="n">
-        <v>34.123994</v>
+        <v>25.280915</v>
       </c>
       <c r="CH49" t="n">
-        <v>34.123994</v>
+        <v>86.48601021499999</v>
       </c>
       <c r="CI49" t="inlineStr">
         <is>
-          <t>VF</t>
+          <t>FF</t>
         </is>
       </c>
       <c r="CJ49" t="inlineStr"/>
       <c r="CK49" t="n">
-        <v>9.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="CL49" t="n">
-        <v>30</v>
-      </c>
-      <c r="CM49" t="inlineStr"/>
+        <v>25</v>
+      </c>
+      <c r="CM49" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="CN49" t="inlineStr"/>
+      <c r="CO49" t="inlineStr"/>
+      <c r="CP49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -10480,7 +10645,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>3O5OUxbKP5_PZAUUrtfSgZ</t>
+          <t>0teRCO0lj5OQYpPkvQztRq</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10500,7 +10665,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>RHW:342820</t>
+          <t>ESP:329276</t>
         </is>
       </c>
       <c r="H50" t="n">
@@ -10519,7 +10684,7 @@
       <c r="S50" t="inlineStr"/>
       <c r="T50" t="inlineStr">
         <is>
-          <t>INTERNAL</t>
+          <t>EXTERNAL</t>
         </is>
       </c>
       <c r="U50" t="inlineStr"/>
@@ -10592,7 +10757,7 @@
       <c r="BR50" t="inlineStr"/>
       <c r="BS50" t="inlineStr">
         <is>
-          <t>RHW</t>
+          <t>ESP</t>
         </is>
       </c>
       <c r="BT50" t="inlineStr">
@@ -10607,17 +10772,13 @@
       </c>
       <c r="BV50" t="inlineStr">
         <is>
-          <t>Raum Hallenwart</t>
-        </is>
-      </c>
-      <c r="BW50" t="inlineStr">
-        <is>
-          <t>Betriebszentrale und Büro kombiniert (2 AP) Teilzeitarbeitsplatz mit Arbeitssims, bei Eingang Sportanlage</t>
-        </is>
-      </c>
+          <t>Eingangshalle Sporthalle</t>
+        </is>
+      </c>
+      <c r="BW50" t="inlineStr"/>
       <c r="BX50" t="inlineStr">
         <is>
-          <t>RHW  -  Raum Hallenwart</t>
+          <t>ESP  -  Eingangshalle Sporthalle</t>
         </is>
       </c>
       <c r="BY50" t="inlineStr">
@@ -10643,45 +10804,48 @@
       </c>
       <c r="CD50" t="inlineStr">
         <is>
-          <t>3$FY_ljDfBsweJfZwnfjO5</t>
+          <t>1QkPwOj9z05w845KZPzMo6</t>
         </is>
       </c>
       <c r="CE50" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="CF50" t="n">
-        <v>13.0853052853127</v>
+        <v>32.1201520903664</v>
       </c>
       <c r="CG50" t="n">
-        <v>13.396027</v>
+        <v>34.123994</v>
       </c>
       <c r="CH50" t="n">
-        <v>40.188081</v>
+        <v>34.123994</v>
       </c>
       <c r="CI50" t="inlineStr">
         <is>
-          <t>HNF</t>
+          <t>VF</t>
         </is>
       </c>
       <c r="CJ50" t="inlineStr"/>
       <c r="CK50" t="n">
-        <v>2.1</v>
+        <v>9.1</v>
       </c>
       <c r="CL50" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="CM50" t="inlineStr"/>
+      <c r="CN50" t="inlineStr"/>
+      <c r="CO50" t="inlineStr"/>
+      <c r="CP50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
         <v>1264</v>
       </c>
       <c r="B51" t="n">
-        <v>1207</v>
+        <v>1209</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2v3d7GGqDEd8IyrTdRXWWY</t>
+          <t>3O5OUxbKP5_PZAUUrtfSgZ</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10701,7 +10865,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>HTR_K:340479</t>
+          <t>RHW:342820</t>
         </is>
       </c>
       <c r="H51" t="n">
@@ -10733,11 +10897,11 @@
       <c r="AB51" t="inlineStr"/>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>UG2</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="AD51" t="n">
-        <v>-8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AE51" t="inlineStr"/>
       <c r="AF51" t="inlineStr"/>
@@ -10793,32 +10957,32 @@
       <c r="BR51" t="inlineStr"/>
       <c r="BS51" t="inlineStr">
         <is>
-          <t>HTR_K</t>
+          <t>RHW</t>
         </is>
       </c>
       <c r="BT51" t="inlineStr">
         <is>
-          <t>Funktionsfläche</t>
+          <t>Sportbereich</t>
         </is>
       </c>
       <c r="BU51" t="inlineStr">
         <is>
-          <t>Haustechnik</t>
+          <t>Sporthallen</t>
         </is>
       </c>
       <c r="BV51" t="inlineStr">
         <is>
-          <t>Elektro-Unterverteilung / -Kommunikation</t>
+          <t>Raum Hallenwart</t>
         </is>
       </c>
       <c r="BW51" t="inlineStr">
         <is>
-          <t>Raumhöhe mind. 3.0m im Licht, ev. Je Geschoss &gt; 8m2</t>
+          <t>Betriebszentrale und Büro kombiniert (2 AP) Teilzeitarbeitsplatz mit Arbeitssims, bei Eingang Sportanlage</t>
         </is>
       </c>
       <c r="BX51" t="inlineStr">
         <is>
-          <t>HTR_K  -  Elektro-Unterverteilung / -Kommunikation</t>
+          <t>RHW  -  Raum Hallenwart</t>
         </is>
       </c>
       <c r="BY51" t="inlineStr">
@@ -10830,7 +10994,7 @@
         <v>1</v>
       </c>
       <c r="CA51" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CB51" t="inlineStr">
         <is>
@@ -10844,47 +11008,48 @@
       </c>
       <c r="CD51" t="inlineStr">
         <is>
-          <t>3VbCMl1_928hbAKPG5KnoC</t>
+          <t>3$FY_ljDfBsweJfZwnfjO5</t>
         </is>
       </c>
       <c r="CE51" t="n">
-        <v>4.121</v>
+        <v>3</v>
       </c>
       <c r="CF51" t="n">
-        <v>33.6781770938313</v>
+        <v>13.0853052853127</v>
       </c>
       <c r="CG51" t="n">
-        <v>68.07347249999999</v>
+        <v>13.396027</v>
       </c>
       <c r="CH51" t="n">
-        <v>280.5307801725</v>
+        <v>40.188081</v>
       </c>
       <c r="CI51" t="inlineStr">
         <is>
-          <t>FF</t>
+          <t>HNF</t>
         </is>
       </c>
       <c r="CJ51" t="inlineStr"/>
       <c r="CK51" t="n">
-        <v>8.5</v>
+        <v>2.1</v>
       </c>
       <c r="CL51" t="n">
-        <v>20</v>
-      </c>
-      <c r="CM51" t="n">
-        <v>3.5</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="CM51" t="inlineStr"/>
+      <c r="CN51" t="inlineStr"/>
+      <c r="CO51" t="inlineStr"/>
+      <c r="CP51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
         <v>1265</v>
       </c>
       <c r="B52" t="n">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2_kl8xFAvE_Oi0Djmy1jeA</t>
+          <t>2v3d7GGqDEd8IyrTdRXWWY</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10904,7 +11069,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>HTR_K:342393</t>
+          <t>HTR_K:340479</t>
         </is>
       </c>
       <c r="H52" t="n">
@@ -10936,11 +11101,11 @@
       <c r="AB52" t="inlineStr"/>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>UG1</t>
+          <t>UG2</t>
         </is>
       </c>
       <c r="AD52" t="n">
-        <v>-3.78</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="AE52" t="inlineStr"/>
       <c r="AF52" t="inlineStr"/>
@@ -11047,20 +11212,20 @@
       </c>
       <c r="CD52" t="inlineStr">
         <is>
-          <t>1QH5Axl111J9SJj2E3W4wL</t>
+          <t>3VbCMl1_928hbAKPG5KnoC</t>
         </is>
       </c>
       <c r="CE52" t="n">
-        <v>3.421</v>
+        <v>4.121</v>
       </c>
       <c r="CF52" t="n">
-        <v>15.2440637556325</v>
+        <v>33.6781770938313</v>
       </c>
       <c r="CG52" t="n">
-        <v>13.790366</v>
+        <v>68.07347249999999</v>
       </c>
       <c r="CH52" t="n">
-        <v>47.176842086</v>
+        <v>280.5307801725</v>
       </c>
       <c r="CI52" t="inlineStr">
         <is>
@@ -11077,17 +11242,20 @@
       <c r="CM52" t="n">
         <v>3.5</v>
       </c>
+      <c r="CN52" t="inlineStr"/>
+      <c r="CO52" t="inlineStr"/>
+      <c r="CP52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
         <v>1266</v>
       </c>
       <c r="B53" t="n">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>3LuW9jHbHBBAyJit_$Yn3$</t>
+          <t>2_kl8xFAvE_Oi0Djmy1jeA</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -11107,7 +11275,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>HTR_L:340296</t>
+          <t>HTR_K:342393</t>
         </is>
       </c>
       <c r="H53" t="n">
@@ -11139,11 +11307,11 @@
       <c r="AB53" t="inlineStr"/>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>UG2</t>
+          <t>UG1</t>
         </is>
       </c>
       <c r="AD53" t="n">
-        <v>-8.199999999999999</v>
+        <v>-3.78</v>
       </c>
       <c r="AE53" t="inlineStr"/>
       <c r="AF53" t="inlineStr"/>
@@ -11199,7 +11367,7 @@
       <c r="BR53" t="inlineStr"/>
       <c r="BS53" t="inlineStr">
         <is>
-          <t>HTR_L</t>
+          <t>HTR_K</t>
         </is>
       </c>
       <c r="BT53" t="inlineStr">
@@ -11214,17 +11382,17 @@
       </c>
       <c r="BV53" t="inlineStr">
         <is>
-          <t>Lüftung</t>
+          <t>Elektro-Unterverteilung / -Kommunikation</t>
         </is>
       </c>
       <c r="BW53" t="inlineStr">
         <is>
-          <t>Raumhöhe mind. 3.5m im Licht</t>
+          <t>Raumhöhe mind. 3.0m im Licht, ev. Je Geschoss &gt; 8m2</t>
         </is>
       </c>
       <c r="BX53" t="inlineStr">
         <is>
-          <t>HTR_L  -  Lüftung</t>
+          <t>HTR_K  -  Elektro-Unterverteilung / -Kommunikation</t>
         </is>
       </c>
       <c r="BY53" t="inlineStr">
@@ -11236,7 +11404,7 @@
         <v>1</v>
       </c>
       <c r="CA53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CB53" t="inlineStr">
         <is>
@@ -11250,20 +11418,20 @@
       </c>
       <c r="CD53" t="inlineStr">
         <is>
-          <t>3VbCMl1_928hbAKPG5Knmx</t>
+          <t>1QH5Axl111J9SJj2E3W4wL</t>
         </is>
       </c>
       <c r="CE53" t="n">
-        <v>4.121</v>
+        <v>3.421</v>
       </c>
       <c r="CF53" t="n">
-        <v>57.8747961939876</v>
+        <v>15.2440637556325</v>
       </c>
       <c r="CG53" t="n">
-        <v>130.4597315</v>
+        <v>13.790366</v>
       </c>
       <c r="CH53" t="n">
-        <v>537.6245535115</v>
+        <v>47.176842086</v>
       </c>
       <c r="CI53" t="inlineStr">
         <is>
@@ -11272,14 +11440,17 @@
       </c>
       <c r="CJ53" t="inlineStr"/>
       <c r="CK53" t="n">
-        <v>8.1</v>
+        <v>8.5</v>
       </c>
       <c r="CL53" t="n">
-        <v>150</v>
+        <v>20</v>
       </c>
       <c r="CM53" t="n">
         <v>3.5</v>
       </c>
+      <c r="CN53" t="inlineStr"/>
+      <c r="CO53" t="inlineStr"/>
+      <c r="CP53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -11481,6 +11652,9 @@
         <v>5</v>
       </c>
       <c r="CM54" t="inlineStr"/>
+      <c r="CN54" t="inlineStr"/>
+      <c r="CO54" t="inlineStr"/>
+      <c r="CP54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -11682,6 +11856,9 @@
         <v>10</v>
       </c>
       <c r="CM55" t="inlineStr"/>
+      <c r="CN55" t="inlineStr"/>
+      <c r="CO55" t="inlineStr"/>
+      <c r="CP55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -11883,6 +12060,9 @@
         <v>16</v>
       </c>
       <c r="CM56" t="inlineStr"/>
+      <c r="CN56" t="inlineStr"/>
+      <c r="CO56" t="inlineStr"/>
+      <c r="CP56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -12084,6 +12264,9 @@
         <v>16</v>
       </c>
       <c r="CM57" t="inlineStr"/>
+      <c r="CN57" t="inlineStr"/>
+      <c r="CO57" t="inlineStr"/>
+      <c r="CP57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -12094,7 +12277,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2oV52czXD7zAOL8XOUSL78</t>
+          <t>1vDbowLhr7nx5SdmnF8FXc</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -12114,7 +12297,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>GSA:342378</t>
+          <t>GSA:342375</t>
         </is>
       </c>
       <c r="H58" t="n">
@@ -12257,20 +12440,20 @@
       </c>
       <c r="CD58" t="inlineStr">
         <is>
-          <t>1QH5Axl111J9SJj2E3W4w6</t>
+          <t>1QH5Axl111J9SJj2E3W4wB</t>
         </is>
       </c>
       <c r="CE58" t="n">
         <v>3.421</v>
       </c>
       <c r="CF58" t="n">
-        <v>38.5665051072028</v>
+        <v>38.5924363426088</v>
       </c>
       <c r="CG58" t="n">
-        <v>42.0894875</v>
+        <v>42.344828</v>
       </c>
       <c r="CH58" t="n">
-        <v>143.9881367375</v>
+        <v>144.861656588</v>
       </c>
       <c r="CI58" t="inlineStr">
         <is>
@@ -12285,17 +12468,20 @@
         <v>45</v>
       </c>
       <c r="CM58" t="inlineStr"/>
+      <c r="CN58" t="inlineStr"/>
+      <c r="CO58" t="inlineStr"/>
+      <c r="CP58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
         <v>1272</v>
       </c>
       <c r="B59" t="n">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>0qoMVDV8fAzBp8ww__y4Tz</t>
+          <t>2oV52czXD7zAOL8XOUSL78</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -12315,7 +12501,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>AGS:343922</t>
+          <t>GSA:342378</t>
         </is>
       </c>
       <c r="H59" t="n">
@@ -12334,7 +12520,7 @@
       <c r="S59" t="inlineStr"/>
       <c r="T59" t="inlineStr">
         <is>
-          <t>EXTERNAL</t>
+          <t>INTERNAL</t>
         </is>
       </c>
       <c r="U59" t="inlineStr"/>
@@ -12347,11 +12533,11 @@
       <c r="AB59" t="inlineStr"/>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>UG1</t>
         </is>
       </c>
       <c r="AD59" t="n">
-        <v>0</v>
+        <v>-3.78</v>
       </c>
       <c r="AE59" t="inlineStr"/>
       <c r="AF59" t="inlineStr"/>
@@ -12407,7 +12593,7 @@
       <c r="BR59" t="inlineStr"/>
       <c r="BS59" t="inlineStr">
         <is>
-          <t>AGS</t>
+          <t>GSA</t>
         </is>
       </c>
       <c r="BT59" t="inlineStr">
@@ -12422,17 +12608,17 @@
       </c>
       <c r="BV59" t="inlineStr">
         <is>
-          <t>Aussengeräteraum Sport</t>
+          <t>Garderobe inkl. Dusche</t>
         </is>
       </c>
       <c r="BW59" t="inlineStr">
         <is>
-          <t>Direkter Zugang von Aussen,mit Beleuchtung und Ballkompressor</t>
+          <t>Garderoben gem. BASPO 201. Jede Umkleide schliesst direkt an einen Duschraum an. &amp;#10;Inkl. Abtrockungszone, Garderoben gem. BASPO 201. Pro Duschraum ist 1 gehbehindertengerechter Duschplatz vorhanden.</t>
         </is>
       </c>
       <c r="BX59" t="inlineStr">
         <is>
-          <t>AGS  -  Aussengeräteraum Sport</t>
+          <t>GSA  -  Garderobe inkl. Dusche</t>
         </is>
       </c>
       <c r="BY59" t="inlineStr">
@@ -12444,7 +12630,7 @@
         <v>1</v>
       </c>
       <c r="CA59" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="CB59" t="inlineStr">
         <is>
@@ -12458,45 +12644,48 @@
       </c>
       <c r="CD59" t="inlineStr">
         <is>
-          <t>3qJ9B5zvT7$hh913fcAFEB</t>
+          <t>1QH5Axl111J9SJj2E3W4w6</t>
         </is>
       </c>
       <c r="CE59" t="n">
-        <v>1</v>
+        <v>3.421</v>
       </c>
       <c r="CF59" t="n">
-        <v>15.9988743322313</v>
+        <v>38.5665051072028</v>
       </c>
       <c r="CG59" t="n">
-        <v>14.9977755</v>
+        <v>42.0894875</v>
       </c>
       <c r="CH59" t="n">
-        <v>14.9977755</v>
+        <v>143.9881367375</v>
       </c>
       <c r="CI59" t="inlineStr">
         <is>
-          <t>HNF</t>
+          <t>NNF</t>
         </is>
       </c>
       <c r="CJ59" t="inlineStr"/>
       <c r="CK59" t="n">
-        <v>4.1</v>
+        <v>7.2</v>
       </c>
       <c r="CL59" t="n">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="CM59" t="inlineStr"/>
+      <c r="CN59" t="inlineStr"/>
+      <c r="CO59" t="inlineStr"/>
+      <c r="CP59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
         <v>1273</v>
       </c>
       <c r="B60" t="n">
-        <v>1208</v>
+        <v>1210</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>1d_UGp1UD2pfCq6QCu1odj</t>
+          <t>1FDFHpwUH4NB1tapjSpmKb</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12516,7 +12705,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>GSA:342369</t>
+          <t>SGR:342955</t>
         </is>
       </c>
       <c r="H60" t="n">
@@ -12548,11 +12737,11 @@
       <c r="AB60" t="inlineStr"/>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>UG1</t>
+          <t>OG1</t>
         </is>
       </c>
       <c r="AD60" t="n">
-        <v>-3.78</v>
+        <v>2.998</v>
       </c>
       <c r="AE60" t="inlineStr"/>
       <c r="AF60" t="inlineStr"/>
@@ -12608,7 +12797,7 @@
       <c r="BR60" t="inlineStr"/>
       <c r="BS60" t="inlineStr">
         <is>
-          <t>GSA</t>
+          <t>SGR</t>
         </is>
       </c>
       <c r="BT60" t="inlineStr">
@@ -12623,17 +12812,17 @@
       </c>
       <c r="BV60" t="inlineStr">
         <is>
-          <t>Garderobe inkl. Dusche</t>
+          <t>Geräteraum</t>
         </is>
       </c>
       <c r="BW60" t="inlineStr">
         <is>
-          <t>Garderoben gem. BASPO 201. Jede Umkleide schliesst direkt an einen Duschraum an. &amp;#10;Inkl. Abtrockungszone, Garderoben gem. BASPO 201. Pro Duschraum ist 1 gehbehindertengerechter Duschplatz vorhanden.</t>
+          <t>Diekt aus der zugehörigen Sporthalle, stufenlos zugänglich. Inkl. abschliessbarem Kleingeräteraum. Zu beachten: Mind. 6m Raumtiefe und 2.5m Höhe im Licht.</t>
         </is>
       </c>
       <c r="BX60" t="inlineStr">
         <is>
-          <t>GSA  -  Garderobe inkl. Dusche</t>
+          <t>SGR  -  Geräteraum</t>
         </is>
       </c>
       <c r="BY60" t="inlineStr">
@@ -12645,7 +12834,7 @@
         <v>1</v>
       </c>
       <c r="CA60" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="CB60" t="inlineStr">
         <is>
@@ -12659,45 +12848,48 @@
       </c>
       <c r="CD60" t="inlineStr">
         <is>
-          <t>1QH5Axl111J9SJj2E3W4wD</t>
+          <t>0b93QOWH141xpbKCpGErNi</t>
         </is>
       </c>
       <c r="CE60" t="n">
-        <v>3.421</v>
+        <v>3.982</v>
       </c>
       <c r="CF60" t="n">
-        <v>38.597841235775</v>
+        <v>41.7997852969898</v>
       </c>
       <c r="CG60" t="n">
-        <v>42.293608</v>
+        <v>89.581008</v>
       </c>
       <c r="CH60" t="n">
-        <v>144.686432968</v>
+        <v>356.711573856</v>
       </c>
       <c r="CI60" t="inlineStr">
         <is>
-          <t>NNF</t>
+          <t>HNF</t>
         </is>
       </c>
       <c r="CJ60" t="inlineStr"/>
       <c r="CK60" t="n">
-        <v>7.2</v>
+        <v>4.1</v>
       </c>
       <c r="CL60" t="n">
-        <v>45</v>
+        <v>90</v>
       </c>
       <c r="CM60" t="inlineStr"/>
+      <c r="CN60" t="inlineStr"/>
+      <c r="CO60" t="inlineStr"/>
+      <c r="CP60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
         <v>1274</v>
       </c>
       <c r="B61" t="n">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>1DjBk084n8gfRcElXcnhlR</t>
+          <t>0qoMVDV8fAzBp8ww__y4Tz</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12717,7 +12909,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>GSA:342372</t>
+          <t>AGS:343922</t>
         </is>
       </c>
       <c r="H61" t="n">
@@ -12736,7 +12928,7 @@
       <c r="S61" t="inlineStr"/>
       <c r="T61" t="inlineStr">
         <is>
-          <t>INTERNAL</t>
+          <t>EXTERNAL</t>
         </is>
       </c>
       <c r="U61" t="inlineStr"/>
@@ -12749,11 +12941,11 @@
       <c r="AB61" t="inlineStr"/>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>UG1</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="AD61" t="n">
-        <v>-3.78</v>
+        <v>0</v>
       </c>
       <c r="AE61" t="inlineStr"/>
       <c r="AF61" t="inlineStr"/>
@@ -12809,7 +13001,7 @@
       <c r="BR61" t="inlineStr"/>
       <c r="BS61" t="inlineStr">
         <is>
-          <t>GSA</t>
+          <t>AGS</t>
         </is>
       </c>
       <c r="BT61" t="inlineStr">
@@ -12824,17 +13016,17 @@
       </c>
       <c r="BV61" t="inlineStr">
         <is>
-          <t>Garderobe inkl. Dusche</t>
+          <t>Aussengeräteraum Sport</t>
         </is>
       </c>
       <c r="BW61" t="inlineStr">
         <is>
-          <t>Garderoben gem. BASPO 201. Jede Umkleide schliesst direkt an einen Duschraum an. &amp;#10;Inkl. Abtrockungszone, Garderoben gem. BASPO 201. Pro Duschraum ist 1 gehbehindertengerechter Duschplatz vorhanden.</t>
+          <t>Direkter Zugang von Aussen,mit Beleuchtung und Ballkompressor</t>
         </is>
       </c>
       <c r="BX61" t="inlineStr">
         <is>
-          <t>GSA  -  Garderobe inkl. Dusche</t>
+          <t>AGS  -  Aussengeräteraum Sport</t>
         </is>
       </c>
       <c r="BY61" t="inlineStr">
@@ -12846,7 +13038,7 @@
         <v>1</v>
       </c>
       <c r="CA61" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="CB61" t="inlineStr">
         <is>
@@ -12860,34 +13052,37 @@
       </c>
       <c r="CD61" t="inlineStr">
         <is>
-          <t>1QH5Axl111J9SJj2E3W4w8</t>
+          <t>3qJ9B5zvT7$hh913fcAFEB</t>
         </is>
       </c>
       <c r="CE61" t="n">
-        <v>3.421</v>
+        <v>1</v>
       </c>
       <c r="CF61" t="n">
-        <v>38.5011315279237</v>
+        <v>15.9988743322313</v>
       </c>
       <c r="CG61" t="n">
-        <v>41.894542</v>
+        <v>14.9977755</v>
       </c>
       <c r="CH61" t="n">
-        <v>143.321228182</v>
+        <v>14.9977755</v>
       </c>
       <c r="CI61" t="inlineStr">
         <is>
-          <t>NNF</t>
+          <t>HNF</t>
         </is>
       </c>
       <c r="CJ61" t="inlineStr"/>
       <c r="CK61" t="n">
-        <v>7.2</v>
+        <v>4.1</v>
       </c>
       <c r="CL61" t="n">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="CM61" t="inlineStr"/>
+      <c r="CN61" t="inlineStr"/>
+      <c r="CO61" t="inlineStr"/>
+      <c r="CP61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -12898,7 +13093,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>1vDbowLhr7nx5SdmnF8FXc</t>
+          <t>1d_UGp1UD2pfCq6QCu1odj</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12918,7 +13113,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>GSA:342375</t>
+          <t>GSA:342369</t>
         </is>
       </c>
       <c r="H62" t="n">
@@ -13061,20 +13256,20 @@
       </c>
       <c r="CD62" t="inlineStr">
         <is>
-          <t>1QH5Axl111J9SJj2E3W4wB</t>
+          <t>1QH5Axl111J9SJj2E3W4wD</t>
         </is>
       </c>
       <c r="CE62" t="n">
         <v>3.421</v>
       </c>
       <c r="CF62" t="n">
-        <v>38.5924363426088</v>
+        <v>38.597841235775</v>
       </c>
       <c r="CG62" t="n">
-        <v>42.344828</v>
+        <v>42.293608</v>
       </c>
       <c r="CH62" t="n">
-        <v>144.861656588</v>
+        <v>144.686432968</v>
       </c>
       <c r="CI62" t="inlineStr">
         <is>
@@ -13089,17 +13284,20 @@
         <v>45</v>
       </c>
       <c r="CM62" t="inlineStr"/>
+      <c r="CN62" t="inlineStr"/>
+      <c r="CO62" t="inlineStr"/>
+      <c r="CP62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
         <v>1276</v>
       </c>
       <c r="B63" t="n">
-        <v>1210</v>
+        <v>1208</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2qwEpCHpPBQhWqR0aH8a_c</t>
+          <t>1DjBk084n8gfRcElXcnhlR</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -13119,7 +13317,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>SPH:342964</t>
+          <t>GSA:342372</t>
         </is>
       </c>
       <c r="H63" t="n">
@@ -13151,11 +13349,11 @@
       <c r="AB63" t="inlineStr"/>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>OG1</t>
+          <t>UG1</t>
         </is>
       </c>
       <c r="AD63" t="n">
-        <v>2.998</v>
+        <v>-3.78</v>
       </c>
       <c r="AE63" t="inlineStr"/>
       <c r="AF63" t="inlineStr"/>
@@ -13211,7 +13409,7 @@
       <c r="BR63" t="inlineStr"/>
       <c r="BS63" t="inlineStr">
         <is>
-          <t>SPH</t>
+          <t>GSA</t>
         </is>
       </c>
       <c r="BT63" t="inlineStr">
@@ -13226,17 +13424,17 @@
       </c>
       <c r="BV63" t="inlineStr">
         <is>
-          <t>Sporthalle</t>
+          <t>Garderobe inkl. Dusche</t>
         </is>
       </c>
       <c r="BW63" t="inlineStr">
         <is>
-          <t>Einfachhalle 28 x 16 x 7m (frei bespielbare Höhe= 7m, Stauraum für Technik, Tragstruktur, Sportgeräte + ca. 1m)&amp;#10;</t>
+          <t>Garderoben gem. BASPO 201. Jede Umkleide schliesst direkt an einen Duschraum an. &amp;#10;Inkl. Abtrockungszone, Garderoben gem. BASPO 201. Pro Duschraum ist 1 gehbehindertengerechter Duschplatz vorhanden.</t>
         </is>
       </c>
       <c r="BX63" t="inlineStr">
         <is>
-          <t>SPH  -  Sporthalle</t>
+          <t>GSA  -  Garderobe inkl. Dusche</t>
         </is>
       </c>
       <c r="BY63" t="inlineStr">
@@ -13248,7 +13446,7 @@
         <v>1</v>
       </c>
       <c r="CA63" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="CB63" t="inlineStr">
         <is>
@@ -13262,47 +13460,48 @@
       </c>
       <c r="CD63" t="inlineStr">
         <is>
-          <t>0b93QOWH141xpbKCpGErNp</t>
+          <t>1QH5Axl111J9SJj2E3W4w8</t>
         </is>
       </c>
       <c r="CE63" t="n">
-        <v>7.85999999999999</v>
+        <v>3.421</v>
       </c>
       <c r="CF63" t="n">
-        <v>89.09855519173711</v>
+        <v>38.5011315279237</v>
       </c>
       <c r="CG63" t="n">
-        <v>463.384951</v>
+        <v>41.894542</v>
       </c>
       <c r="CH63" t="n">
-        <v>3642.20571486</v>
+        <v>143.321228182</v>
       </c>
       <c r="CI63" t="inlineStr">
         <is>
-          <t>HNF</t>
+          <t>NNF</t>
         </is>
       </c>
       <c r="CJ63" t="inlineStr"/>
       <c r="CK63" t="n">
-        <v>5.5</v>
+        <v>7.2</v>
       </c>
       <c r="CL63" t="n">
-        <v>448</v>
-      </c>
-      <c r="CM63" t="n">
-        <v>7</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="CM63" t="inlineStr"/>
+      <c r="CN63" t="inlineStr"/>
+      <c r="CO63" t="inlineStr"/>
+      <c r="CP63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
         <v>1277</v>
       </c>
       <c r="B64" t="n">
-        <v>1207</v>
+        <v>1210</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>1OOeb7pNP5YhVqjcacSVQj</t>
+          <t>2qwEpCHpPBQhWqR0aH8a_c</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -13322,7 +13521,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>SGR:340482</t>
+          <t>SPH:342964</t>
         </is>
       </c>
       <c r="H64" t="n">
@@ -13354,11 +13553,11 @@
       <c r="AB64" t="inlineStr"/>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>UG2</t>
+          <t>OG1</t>
         </is>
       </c>
       <c r="AD64" t="n">
-        <v>-8.199999999999999</v>
+        <v>2.998</v>
       </c>
       <c r="AE64" t="inlineStr"/>
       <c r="AF64" t="inlineStr"/>
@@ -13414,7 +13613,7 @@
       <c r="BR64" t="inlineStr"/>
       <c r="BS64" t="inlineStr">
         <is>
-          <t>SGR</t>
+          <t>SPH</t>
         </is>
       </c>
       <c r="BT64" t="inlineStr">
@@ -13429,17 +13628,17 @@
       </c>
       <c r="BV64" t="inlineStr">
         <is>
-          <t>Geräteraum</t>
+          <t>Sporthalle</t>
         </is>
       </c>
       <c r="BW64" t="inlineStr">
         <is>
-          <t>Diekt aus der zugehörigen Sporthalle, stufenlos zugänglich. Inkl. abschliessbarem Kleingeräteraum. Zu beachten: Mind. 6m Raumtiefe und 2.5m Höhe im Licht.</t>
+          <t>Einfachhalle 28 x 16 x 7m (frei bespielbare Höhe= 7m, Stauraum für Technik, Tragstruktur, Sportgeräte + ca. 1m)&amp;#10;</t>
         </is>
       </c>
       <c r="BX64" t="inlineStr">
         <is>
-          <t>SGR  -  Geräteraum</t>
+          <t>SPH  -  Sporthalle</t>
         </is>
       </c>
       <c r="BY64" t="inlineStr">
@@ -13465,20 +13664,20 @@
       </c>
       <c r="CD64" t="inlineStr">
         <is>
-          <t>3VbCMl1_928hbAKPG5Knzn</t>
+          <t>0b93QOWH141xpbKCpGErNp</t>
         </is>
       </c>
       <c r="CE64" t="n">
-        <v>4.121</v>
+        <v>7.85999999999999</v>
       </c>
       <c r="CF64" t="n">
-        <v>37.9925325891083</v>
+        <v>89.09855519173711</v>
       </c>
       <c r="CG64" t="n">
-        <v>89.857005</v>
+        <v>463.384951</v>
       </c>
       <c r="CH64" t="n">
-        <v>370.300717605</v>
+        <v>3642.20571486</v>
       </c>
       <c r="CI64" t="inlineStr">
         <is>
@@ -13487,23 +13686,34 @@
       </c>
       <c r="CJ64" t="inlineStr"/>
       <c r="CK64" t="n">
-        <v>4.1</v>
+        <v>5.5</v>
       </c>
       <c r="CL64" t="n">
-        <v>90</v>
-      </c>
-      <c r="CM64" t="inlineStr"/>
+        <v>448</v>
+      </c>
+      <c r="CM64" t="n">
+        <v>7</v>
+      </c>
+      <c r="CN64" t="n">
+        <v>8</v>
+      </c>
+      <c r="CO64" t="n">
+        <v>28</v>
+      </c>
+      <c r="CP64" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
         <v>1278</v>
       </c>
       <c r="B65" t="n">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>1FDFHpwUH4NB1tapjSpmKb</t>
+          <t>1OOeb7pNP5YhVqjcacSVQj</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13523,7 +13733,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>SGR:342955</t>
+          <t>SGR:340482</t>
         </is>
       </c>
       <c r="H65" t="n">
@@ -13555,11 +13765,11 @@
       <c r="AB65" t="inlineStr"/>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>OG1</t>
+          <t>UG2</t>
         </is>
       </c>
       <c r="AD65" t="n">
-        <v>2.998</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="AE65" t="inlineStr"/>
       <c r="AF65" t="inlineStr"/>
@@ -13666,20 +13876,20 @@
       </c>
       <c r="CD65" t="inlineStr">
         <is>
-          <t>0b93QOWH141xpbKCpGErNi</t>
+          <t>3VbCMl1_928hbAKPG5Knzn</t>
         </is>
       </c>
       <c r="CE65" t="n">
-        <v>3.982</v>
+        <v>4.121</v>
       </c>
       <c r="CF65" t="n">
-        <v>41.7997852969898</v>
+        <v>37.9925325891083</v>
       </c>
       <c r="CG65" t="n">
-        <v>89.581008</v>
+        <v>89.857005</v>
       </c>
       <c r="CH65" t="n">
-        <v>356.711573856</v>
+        <v>370.300717605</v>
       </c>
       <c r="CI65" t="inlineStr">
         <is>
@@ -13694,6 +13904,9 @@
         <v>90</v>
       </c>
       <c r="CM65" t="inlineStr"/>
+      <c r="CN65" t="inlineStr"/>
+      <c r="CO65" t="inlineStr"/>
+      <c r="CP65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -13895,6 +14108,9 @@
         <v>25</v>
       </c>
       <c r="CM66" t="inlineStr"/>
+      <c r="CN66" t="inlineStr"/>
+      <c r="CO66" t="inlineStr"/>
+      <c r="CP66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -14096,6 +14312,9 @@
         <v>12</v>
       </c>
       <c r="CM67" t="inlineStr"/>
+      <c r="CN67" t="inlineStr"/>
+      <c r="CO67" t="inlineStr"/>
+      <c r="CP67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -14297,6 +14516,9 @@
         <v>12</v>
       </c>
       <c r="CM68" t="inlineStr"/>
+      <c r="CN68" t="inlineStr"/>
+      <c r="CO68" t="inlineStr"/>
+      <c r="CP68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -14500,6 +14722,15 @@
       <c r="CM69" t="n">
         <v>7</v>
       </c>
+      <c r="CN69" t="n">
+        <v>8</v>
+      </c>
+      <c r="CO69" t="n">
+        <v>28</v>
+      </c>
+      <c r="CP69" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -14701,6 +14932,9 @@
         <v>6</v>
       </c>
       <c r="CM70" t="inlineStr"/>
+      <c r="CN70" t="inlineStr"/>
+      <c r="CO70" t="inlineStr"/>
+      <c r="CP70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -14902,6 +15136,9 @@
         <v>6</v>
       </c>
       <c r="CM71" t="inlineStr"/>
+      <c r="CN71" t="inlineStr"/>
+      <c r="CO71" t="inlineStr"/>
+      <c r="CP71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -15099,6 +15336,9 @@
         <v>7</v>
       </c>
       <c r="CM72" t="inlineStr"/>
+      <c r="CN72" t="inlineStr"/>
+      <c r="CO72" t="inlineStr"/>
+      <c r="CP72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -15296,6 +15536,9 @@
         <v>18</v>
       </c>
       <c r="CM73" t="inlineStr"/>
+      <c r="CN73" t="inlineStr"/>
+      <c r="CO73" t="inlineStr"/>
+      <c r="CP73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -15493,6 +15736,9 @@
         <v>36</v>
       </c>
       <c r="CM74" t="inlineStr"/>
+      <c r="CN74" t="inlineStr"/>
+      <c r="CO74" t="inlineStr"/>
+      <c r="CP74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -15690,6 +15936,9 @@
         <v>54</v>
       </c>
       <c r="CM75" t="inlineStr"/>
+      <c r="CN75" t="inlineStr"/>
+      <c r="CO75" t="inlineStr"/>
+      <c r="CP75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -15887,6 +16136,9 @@
         <v>18</v>
       </c>
       <c r="CM76" t="inlineStr"/>
+      <c r="CN76" t="inlineStr"/>
+      <c r="CO76" t="inlineStr"/>
+      <c r="CP76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -16084,6 +16336,9 @@
         <v>18</v>
       </c>
       <c r="CM77" t="inlineStr"/>
+      <c r="CN77" t="inlineStr"/>
+      <c r="CO77" t="inlineStr"/>
+      <c r="CP77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -16287,6 +16542,9 @@
       <c r="CM78" t="n">
         <v>3</v>
       </c>
+      <c r="CN78" t="inlineStr"/>
+      <c r="CO78" t="inlineStr"/>
+      <c r="CP78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -16488,6 +16746,9 @@
         <v>55</v>
       </c>
       <c r="CM79" t="inlineStr"/>
+      <c r="CN79" t="inlineStr"/>
+      <c r="CO79" t="inlineStr"/>
+      <c r="CP79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -16689,6 +16950,9 @@
         <v>4</v>
       </c>
       <c r="CM80" t="inlineStr"/>
+      <c r="CN80" t="inlineStr"/>
+      <c r="CO80" t="inlineStr"/>
+      <c r="CP80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -16886,6 +17150,9 @@
         <v>7</v>
       </c>
       <c r="CM81" t="inlineStr"/>
+      <c r="CN81" t="inlineStr"/>
+      <c r="CO81" t="inlineStr"/>
+      <c r="CP81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -17087,6 +17354,9 @@
         <v>2.5</v>
       </c>
       <c r="CM82" t="inlineStr"/>
+      <c r="CN82" t="inlineStr"/>
+      <c r="CO82" t="inlineStr"/>
+      <c r="CP82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -17288,6 +17558,9 @@
         <v>2.5</v>
       </c>
       <c r="CM83" t="inlineStr"/>
+      <c r="CN83" t="inlineStr"/>
+      <c r="CO83" t="inlineStr"/>
+      <c r="CP83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -17491,6 +17764,9 @@
       <c r="CM84" t="n">
         <v>3</v>
       </c>
+      <c r="CN84" t="inlineStr"/>
+      <c r="CO84" t="inlineStr"/>
+      <c r="CP84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -17692,6 +17968,9 @@
         <v>20</v>
       </c>
       <c r="CM85" t="inlineStr"/>
+      <c r="CN85" t="inlineStr"/>
+      <c r="CO85" t="inlineStr"/>
+      <c r="CP85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -17893,6 +18172,9 @@
         <v>36</v>
       </c>
       <c r="CM86" t="inlineStr"/>
+      <c r="CN86" t="inlineStr"/>
+      <c r="CO86" t="inlineStr"/>
+      <c r="CP86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -18090,6 +18372,9 @@
         <v>108</v>
       </c>
       <c r="CM87" t="inlineStr"/>
+      <c r="CN87" t="inlineStr"/>
+      <c r="CO87" t="inlineStr"/>
+      <c r="CP87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -18291,6 +18576,9 @@
         <v>2.5</v>
       </c>
       <c r="CM88" t="inlineStr"/>
+      <c r="CN88" t="inlineStr"/>
+      <c r="CO88" t="inlineStr"/>
+      <c r="CP88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -18492,6 +18780,9 @@
         <v>2.5</v>
       </c>
       <c r="CM89" t="inlineStr"/>
+      <c r="CN89" t="inlineStr"/>
+      <c r="CO89" t="inlineStr"/>
+      <c r="CP89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -18693,6 +18984,9 @@
         <v>2.5</v>
       </c>
       <c r="CM90" t="inlineStr"/>
+      <c r="CN90" t="inlineStr"/>
+      <c r="CO90" t="inlineStr"/>
+      <c r="CP90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -18894,6 +19188,9 @@
         <v>2.5</v>
       </c>
       <c r="CM91" t="inlineStr"/>
+      <c r="CN91" t="inlineStr"/>
+      <c r="CO91" t="inlineStr"/>
+      <c r="CP91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -19095,6 +19392,9 @@
         <v>72</v>
       </c>
       <c r="CM92" t="inlineStr"/>
+      <c r="CN92" t="inlineStr"/>
+      <c r="CO92" t="inlineStr"/>
+      <c r="CP92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -19292,6 +19592,9 @@
         <v>54</v>
       </c>
       <c r="CM93" t="inlineStr"/>
+      <c r="CN93" t="inlineStr"/>
+      <c r="CO93" t="inlineStr"/>
+      <c r="CP93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -19449,6 +19752,9 @@
       <c r="CK94" t="inlineStr"/>
       <c r="CL94" t="inlineStr"/>
       <c r="CM94" t="inlineStr"/>
+      <c r="CN94" t="inlineStr"/>
+      <c r="CO94" t="inlineStr"/>
+      <c r="CP94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -19606,6 +19912,9 @@
       <c r="CK95" t="inlineStr"/>
       <c r="CL95" t="inlineStr"/>
       <c r="CM95" t="inlineStr"/>
+      <c r="CN95" t="inlineStr"/>
+      <c r="CO95" t="inlineStr"/>
+      <c r="CP95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -19763,6 +20072,9 @@
       <c r="CK96" t="inlineStr"/>
       <c r="CL96" t="inlineStr"/>
       <c r="CM96" t="inlineStr"/>
+      <c r="CN96" t="inlineStr"/>
+      <c r="CO96" t="inlineStr"/>
+      <c r="CP96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -19920,6 +20232,9 @@
       <c r="CK97" t="inlineStr"/>
       <c r="CL97" t="inlineStr"/>
       <c r="CM97" t="inlineStr"/>
+      <c r="CN97" t="inlineStr"/>
+      <c r="CO97" t="inlineStr"/>
+      <c r="CP97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -20077,6 +20392,9 @@
       <c r="CK98" t="inlineStr"/>
       <c r="CL98" t="inlineStr"/>
       <c r="CM98" t="inlineStr"/>
+      <c r="CN98" t="inlineStr"/>
+      <c r="CO98" t="inlineStr"/>
+      <c r="CP98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -20242,6 +20560,9 @@
       <c r="CK99" t="inlineStr"/>
       <c r="CL99" t="inlineStr"/>
       <c r="CM99" t="inlineStr"/>
+      <c r="CN99" t="inlineStr"/>
+      <c r="CO99" t="inlineStr"/>
+      <c r="CP99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -20407,6 +20728,9 @@
       <c r="CK100" t="inlineStr"/>
       <c r="CL100" t="inlineStr"/>
       <c r="CM100" t="inlineStr"/>
+      <c r="CN100" t="inlineStr"/>
+      <c r="CO100" t="inlineStr"/>
+      <c r="CP100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -20564,6 +20888,9 @@
       <c r="CK101" t="inlineStr"/>
       <c r="CL101" t="inlineStr"/>
       <c r="CM101" t="inlineStr"/>
+      <c r="CN101" t="inlineStr"/>
+      <c r="CO101" t="inlineStr"/>
+      <c r="CP101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -20721,6 +21048,9 @@
       <c r="CK102" t="inlineStr"/>
       <c r="CL102" t="inlineStr"/>
       <c r="CM102" t="inlineStr"/>
+      <c r="CN102" t="inlineStr"/>
+      <c r="CO102" t="inlineStr"/>
+      <c r="CP102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -20878,6 +21208,9 @@
       <c r="CK103" t="inlineStr"/>
       <c r="CL103" t="inlineStr"/>
       <c r="CM103" t="inlineStr"/>
+      <c r="CN103" t="inlineStr"/>
+      <c r="CO103" t="inlineStr"/>
+      <c r="CP103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -21035,6 +21368,9 @@
       <c r="CK104" t="inlineStr"/>
       <c r="CL104" t="inlineStr"/>
       <c r="CM104" t="inlineStr"/>
+      <c r="CN104" t="inlineStr"/>
+      <c r="CO104" t="inlineStr"/>
+      <c r="CP104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -21200,6 +21536,9 @@
       <c r="CK105" t="inlineStr"/>
       <c r="CL105" t="inlineStr"/>
       <c r="CM105" t="inlineStr"/>
+      <c r="CN105" t="inlineStr"/>
+      <c r="CO105" t="inlineStr"/>
+      <c r="CP105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -21365,6 +21704,9 @@
       <c r="CK106" t="inlineStr"/>
       <c r="CL106" t="inlineStr"/>
       <c r="CM106" t="inlineStr"/>
+      <c r="CN106" t="inlineStr"/>
+      <c r="CO106" t="inlineStr"/>
+      <c r="CP106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -21530,6 +21872,9 @@
       <c r="CK107" t="inlineStr"/>
       <c r="CL107" t="inlineStr"/>
       <c r="CM107" t="inlineStr"/>
+      <c r="CN107" t="inlineStr"/>
+      <c r="CO107" t="inlineStr"/>
+      <c r="CP107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -21687,6 +22032,9 @@
       <c r="CK108" t="inlineStr"/>
       <c r="CL108" t="inlineStr"/>
       <c r="CM108" t="inlineStr"/>
+      <c r="CN108" t="inlineStr"/>
+      <c r="CO108" t="inlineStr"/>
+      <c r="CP108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -21844,6 +22192,9 @@
       <c r="CK109" t="inlineStr"/>
       <c r="CL109" t="inlineStr"/>
       <c r="CM109" t="inlineStr"/>
+      <c r="CN109" t="inlineStr"/>
+      <c r="CO109" t="inlineStr"/>
+      <c r="CP109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -22001,6 +22352,9 @@
       <c r="CK110" t="inlineStr"/>
       <c r="CL110" t="inlineStr"/>
       <c r="CM110" t="inlineStr"/>
+      <c r="CN110" t="inlineStr"/>
+      <c r="CO110" t="inlineStr"/>
+      <c r="CP110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -22158,6 +22512,9 @@
       <c r="CK111" t="inlineStr"/>
       <c r="CL111" t="inlineStr"/>
       <c r="CM111" t="inlineStr"/>
+      <c r="CN111" t="inlineStr"/>
+      <c r="CO111" t="inlineStr"/>
+      <c r="CP111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -22323,6 +22680,9 @@
       <c r="CK112" t="inlineStr"/>
       <c r="CL112" t="inlineStr"/>
       <c r="CM112" t="inlineStr"/>
+      <c r="CN112" t="inlineStr"/>
+      <c r="CO112" t="inlineStr"/>
+      <c r="CP112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -22488,6 +22848,9 @@
       <c r="CK113" t="inlineStr"/>
       <c r="CL113" t="inlineStr"/>
       <c r="CM113" t="inlineStr"/>
+      <c r="CN113" t="inlineStr"/>
+      <c r="CO113" t="inlineStr"/>
+      <c r="CP113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -22653,6 +23016,9 @@
       <c r="CK114" t="inlineStr"/>
       <c r="CL114" t="inlineStr"/>
       <c r="CM114" t="inlineStr"/>
+      <c r="CN114" t="inlineStr"/>
+      <c r="CO114" t="inlineStr"/>
+      <c r="CP114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -22810,6 +23176,9 @@
       <c r="CK115" t="inlineStr"/>
       <c r="CL115" t="inlineStr"/>
       <c r="CM115" t="inlineStr"/>
+      <c r="CN115" t="inlineStr"/>
+      <c r="CO115" t="inlineStr"/>
+      <c r="CP115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -22967,6 +23336,9 @@
       <c r="CK116" t="inlineStr"/>
       <c r="CL116" t="inlineStr"/>
       <c r="CM116" t="inlineStr"/>
+      <c r="CN116" t="inlineStr"/>
+      <c r="CO116" t="inlineStr"/>
+      <c r="CP116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -23132,6 +23504,9 @@
       <c r="CK117" t="inlineStr"/>
       <c r="CL117" t="inlineStr"/>
       <c r="CM117" t="inlineStr"/>
+      <c r="CN117" t="inlineStr"/>
+      <c r="CO117" t="inlineStr"/>
+      <c r="CP117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -23297,6 +23672,9 @@
       <c r="CK118" t="inlineStr"/>
       <c r="CL118" t="inlineStr"/>
       <c r="CM118" t="inlineStr"/>
+      <c r="CN118" t="inlineStr"/>
+      <c r="CO118" t="inlineStr"/>
+      <c r="CP118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -23454,6 +23832,9 @@
       <c r="CK119" t="inlineStr"/>
       <c r="CL119" t="inlineStr"/>
       <c r="CM119" t="inlineStr"/>
+      <c r="CN119" t="inlineStr"/>
+      <c r="CO119" t="inlineStr"/>
+      <c r="CP119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -23611,6 +23992,9 @@
       <c r="CK120" t="inlineStr"/>
       <c r="CL120" t="inlineStr"/>
       <c r="CM120" t="inlineStr"/>
+      <c r="CN120" t="inlineStr"/>
+      <c r="CO120" t="inlineStr"/>
+      <c r="CP120" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/actual_df_filtered.xlsx
+++ b/actual_df_filtered.xlsx
@@ -541,32 +541,32 @@
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
+          <t>ePset_abstractBIM.PredefinedType</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>ePset_abstractBIM.IsExternal</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>ePset_abstractBIM.Spaces</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>ePset_abstractBIM.SpacesLongName</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>ePset_abstractBIM.SpacesName</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
           <t>Pset_CoveringCommon.IsExternal</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>ePset_abstractBIM.PredefinedType</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>ePset_abstractBIM.IsExternal</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>ePset_abstractBIM.Spaces</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>ePset_abstractBIM.SpacesLongName</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>ePset_abstractBIM.SpacesName</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
@@ -902,14 +902,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1215</v>
+        <v>1191</v>
       </c>
       <c r="B2" t="n">
-        <v>1209</v>
+        <v>1186</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1R$FLavrj8G9Rxnz3lVckG</t>
+          <t>3Hh_lnoOjFseiPP$fBJdTk</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -929,11 +929,11 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>LUF:342799</t>
+          <t>LUF:342961</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1215</v>
+        <v>1191</v>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
@@ -961,11 +961,11 @@
       <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>OG1</t>
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>2.998</v>
       </c>
       <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="inlineStr"/>
@@ -1072,20 +1072,20 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>3$FY_ljDfBsweJfZwnfjOk</t>
+          <t>0b93QOWH141xpbKCpGErNs</t>
         </is>
       </c>
       <c r="CE2" t="n">
-        <v>3</v>
+        <v>4.942</v>
       </c>
       <c r="CF2" t="n">
-        <v>58.6046173021893</v>
+        <v>7.38232192035912</v>
       </c>
       <c r="CG2" t="n">
-        <v>29.7644175</v>
+        <v>2.3140405</v>
       </c>
       <c r="CH2" t="n">
-        <v>89.29325249999999</v>
+        <v>11.435988151</v>
       </c>
       <c r="CI2" t="inlineStr"/>
       <c r="CJ2" t="inlineStr"/>
@@ -1098,14 +1098,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1216</v>
+        <v>1192</v>
       </c>
       <c r="B3" t="n">
-        <v>1210</v>
+        <v>1187</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0CIMZOOqj8GukY8gSKgU97</t>
+          <t>2P3Mbts9P06BZqiOxGDRsK</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1125,11 +1125,11 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>LUF:342961</t>
+          <t>LUF:343164</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1216</v>
+        <v>1192</v>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
@@ -1157,11 +1157,11 @@
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>OG1</t>
+          <t>OG2</t>
         </is>
       </c>
       <c r="AD3" t="n">
-        <v>2.998</v>
+        <v>7.94</v>
       </c>
       <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="inlineStr"/>
@@ -1268,11 +1268,11 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>0b93QOWH141xpbKCpGErNs</t>
+          <t>0b93QOWH141xpbKCpGEr8x</t>
         </is>
       </c>
       <c r="CE3" t="n">
-        <v>4.941</v>
+        <v>4.008</v>
       </c>
       <c r="CF3" t="n">
         <v>7.38232192035912</v>
@@ -1281,7 +1281,7 @@
         <v>2.3140405</v>
       </c>
       <c r="CH3" t="n">
-        <v>11.4336741105</v>
+        <v>9.274674323999999</v>
       </c>
       <c r="CI3" t="inlineStr"/>
       <c r="CJ3" t="inlineStr"/>
@@ -1294,14 +1294,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1217</v>
+        <v>1193</v>
       </c>
       <c r="B4" t="n">
-        <v>1211</v>
+        <v>1188</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>18j2PWjBz3nhKzSkJrvM7d</t>
+          <t>39ETwZKMDAou$vKVot7pYG</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1321,11 +1321,11 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>LUF:343164</t>
+          <t>LUF:343294</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1217</v>
+        <v>1193</v>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
@@ -1353,11 +1353,11 @@
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>OG2</t>
+          <t>OG3</t>
         </is>
       </c>
       <c r="AD4" t="n">
-        <v>7.939</v>
+        <v>11.948</v>
       </c>
       <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="inlineStr"/>
@@ -1464,20 +1464,20 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>0b93QOWH141xpbKCpGEr8x</t>
+          <t>3ol_0stLL7q8pSNseENpkb</t>
         </is>
       </c>
       <c r="CE4" t="n">
-        <v>4.008</v>
+        <v>2.522</v>
       </c>
       <c r="CF4" t="n">
-        <v>7.38232192035912</v>
+        <v>7.49144557435166</v>
       </c>
       <c r="CG4" t="n">
-        <v>2.3140405</v>
+        <v>2.357719</v>
       </c>
       <c r="CH4" t="n">
-        <v>9.274674323999999</v>
+        <v>5.946167318</v>
       </c>
       <c r="CI4" t="inlineStr"/>
       <c r="CJ4" t="inlineStr"/>
@@ -1490,14 +1490,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1218</v>
+        <v>1194</v>
       </c>
       <c r="B5" t="n">
-        <v>1212</v>
+        <v>1183</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0wtQ7wfjD5FPd24jrI75yq</t>
+          <t>0flQ6A_KT1au1P6tc3jqMc</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1517,11 +1517,11 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>LUF:343294</t>
+          <t>TRH:341682</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1218</v>
+        <v>1194</v>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
@@ -1549,11 +1549,11 @@
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>OG3</t>
+          <t>UG2</t>
         </is>
       </c>
       <c r="AD5" t="n">
-        <v>11.947</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="inlineStr"/>
@@ -1609,7 +1609,7 @@
       <c r="BR5" t="inlineStr"/>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>LUF</t>
+          <t>TRH</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>Luftraum</t>
+          <t>Treppenhaus</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>LUF  -  Luftraum</t>
+          <t>TRH  -  Treppenhaus</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
@@ -1643,7 +1643,7 @@
         </is>
       </c>
       <c r="BZ5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CA5" t="n">
         <v>1</v>
@@ -1660,22 +1660,26 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>3ol_0stLL7q8pSNseENpkb</t>
+          <t>3VbCMl1_928hbAKPG5Knl1</t>
         </is>
       </c>
       <c r="CE5" t="n">
-        <v>2.523</v>
+        <v>4.12</v>
       </c>
       <c r="CF5" t="n">
-        <v>7.49144557435166</v>
+        <v>11.5222748736684</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.357719</v>
+        <v>10.428806</v>
       </c>
       <c r="CH5" t="n">
-        <v>5.948525037</v>
-      </c>
-      <c r="CI5" t="inlineStr"/>
+        <v>42.96668072</v>
+      </c>
+      <c r="CI5" t="inlineStr">
+        <is>
+          <t>VF</t>
+        </is>
+      </c>
       <c r="CJ5" t="inlineStr"/>
       <c r="CK5" t="inlineStr"/>
       <c r="CL5" t="inlineStr"/>
@@ -1686,14 +1690,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1219</v>
+        <v>1195</v>
       </c>
       <c r="B6" t="n">
-        <v>1212</v>
+        <v>1183</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2Ru4iRmYDDDfo5eLHGZ8RE</t>
+          <t>2F6s1tVBjDqQjhbB3E6WYb</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1713,11 +1717,11 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>KOR:343282</t>
+          <t>TRH:341685</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1219</v>
+        <v>1195</v>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
@@ -1745,11 +1749,11 @@
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>OG3</t>
+          <t>UG2</t>
         </is>
       </c>
       <c r="AD6" t="n">
-        <v>11.947</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1805,7 +1809,7 @@
       <c r="BR6" t="inlineStr"/>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>KOR</t>
+          <t>TRH</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -1820,7 +1824,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>Korridor</t>
+          <t>Treppenhaus</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -1830,7 +1834,7 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>KOR  -  Korridor</t>
+          <t>TRH  -  Treppenhaus</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
@@ -1856,20 +1860,20 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>3ol_0stLL7q8pSNseENpkf</t>
+          <t>3VbCMl1_928hbAKPG5Knl6</t>
         </is>
       </c>
       <c r="CE6" t="n">
-        <v>2.522</v>
+        <v>4.12</v>
       </c>
       <c r="CF6" t="n">
-        <v>24.6411125862649</v>
+        <v>30.3639272858965</v>
       </c>
       <c r="CG6" t="n">
-        <v>13.547317</v>
+        <v>32.464858</v>
       </c>
       <c r="CH6" t="n">
-        <v>34.166333474</v>
+        <v>133.75521496</v>
       </c>
       <c r="CI6" t="inlineStr">
         <is>
@@ -1886,14 +1890,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1220</v>
+        <v>1196</v>
       </c>
       <c r="B7" t="n">
-        <v>1207</v>
+        <v>1184</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3Q30KcAwrFjgFId43DWY8P</t>
+          <t>1ob0Dr3Tb3me5ixnzVhldr</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1913,11 +1917,11 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>TRH:341682</t>
+          <t>TRH:342381</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1220</v>
+        <v>1196</v>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
@@ -1945,11 +1949,11 @@
       <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>UG2</t>
+          <t>UG1</t>
         </is>
       </c>
       <c r="AD7" t="n">
-        <v>-8.199999999999999</v>
+        <v>-3.78</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -2056,20 +2060,20 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>3VbCMl1_928hbAKPG5Knl1</t>
+          <t>1QH5Axl111J9SJj2E3W4w1</t>
         </is>
       </c>
       <c r="CE7" t="n">
-        <v>4.121</v>
+        <v>3.42</v>
       </c>
       <c r="CF7" t="n">
-        <v>10.4407453756904</v>
+        <v>30.8626322671356</v>
       </c>
       <c r="CG7" t="n">
-        <v>6.8130725</v>
+        <v>58.794787</v>
       </c>
       <c r="CH7" t="n">
-        <v>28.0766717725</v>
+        <v>201.07817154</v>
       </c>
       <c r="CI7" t="inlineStr">
         <is>
@@ -2086,14 +2090,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1221</v>
+        <v>1197</v>
       </c>
       <c r="B8" t="n">
-        <v>1207</v>
+        <v>1183</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>34G_SBUtD7Bx_aSDXbyBOH</t>
+          <t>0WugxlnUz8xx2oGJ_ePbye</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2113,11 +2117,11 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>TRH:341685</t>
+          <t>LUF:340252</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1221</v>
+        <v>1197</v>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
@@ -2205,7 +2209,7 @@
       <c r="BR8" t="inlineStr"/>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>TRH</t>
+          <t>LUF</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -2220,7 +2224,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>Treppenhaus</t>
+          <t>Luftraum</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -2230,7 +2234,7 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>TRH  -  Treppenhaus</t>
+          <t>LUF  -  Luftraum</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
@@ -2239,7 +2243,7 @@
         </is>
       </c>
       <c r="BZ8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CA8" t="n">
         <v>1</v>
@@ -2256,26 +2260,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>3VbCMl1_928hbAKPG5Knl6</t>
+          <t>3VbCMl1_928hbAKPG5Knnl</t>
         </is>
       </c>
       <c r="CE8" t="n">
-        <v>4.121</v>
+        <v>4.42</v>
       </c>
       <c r="CF8" t="n">
-        <v>30.404276140697</v>
+        <v>7.38232192035912</v>
       </c>
       <c r="CG8" t="n">
-        <v>32.270022</v>
+        <v>2.3140405</v>
       </c>
       <c r="CH8" t="n">
-        <v>132.984760662</v>
-      </c>
-      <c r="CI8" t="inlineStr">
-        <is>
-          <t>VF</t>
-        </is>
-      </c>
+        <v>10.22805901</v>
+      </c>
+      <c r="CI8" t="inlineStr"/>
       <c r="CJ8" t="inlineStr"/>
       <c r="CK8" t="inlineStr"/>
       <c r="CL8" t="inlineStr"/>
@@ -2286,14 +2286,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1222</v>
+        <v>1198</v>
       </c>
       <c r="B9" t="n">
-        <v>1208</v>
+        <v>1184</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>11GLlly7bCgPkVa3553rnS</t>
+          <t>1TuiyJHazFPP354k0XGOop</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2313,11 +2313,11 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>TRH:342381</t>
+          <t>LUF:342420</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>1222</v>
+        <v>1198</v>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
@@ -2405,7 +2405,7 @@
       <c r="BR9" t="inlineStr"/>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>TRH</t>
+          <t>LUF</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -2420,7 +2420,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>Treppenhaus</t>
+          <t>Luftraum</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -2430,7 +2430,7 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>TRH  -  Treppenhaus</t>
+          <t>LUF  -  Luftraum</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
@@ -2439,7 +2439,7 @@
         </is>
       </c>
       <c r="BZ9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CA9" t="n">
         <v>1</v>
@@ -2456,26 +2456,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>1QH5Axl111J9SJj2E3W4w1</t>
+          <t>1QH5Axl111J9SJj2E3W4vu</t>
         </is>
       </c>
       <c r="CE9" t="n">
-        <v>3.421</v>
+        <v>3.42</v>
       </c>
       <c r="CF9" t="n">
-        <v>30.8427134126076</v>
+        <v>7.38098313865425</v>
       </c>
       <c r="CG9" t="n">
-        <v>58.7912815</v>
+        <v>2.312567</v>
       </c>
       <c r="CH9" t="n">
-        <v>201.1249740115</v>
-      </c>
-      <c r="CI9" t="inlineStr">
-        <is>
-          <t>VF</t>
-        </is>
-      </c>
+        <v>7.90897914</v>
+      </c>
+      <c r="CI9" t="inlineStr"/>
       <c r="CJ9" t="inlineStr"/>
       <c r="CK9" t="inlineStr"/>
       <c r="CL9" t="inlineStr"/>
@@ -2486,14 +2482,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1223</v>
+        <v>1199</v>
       </c>
       <c r="B10" t="n">
-        <v>1207</v>
+        <v>1185</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>13LOp07jD0lfjp1Ds2xiaX</t>
+          <t>049y1zqcb029syIWXEZkws</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2513,11 +2509,11 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>LUF:340252</t>
+          <t>LUF:342799</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1223</v>
+        <v>1199</v>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
@@ -2545,11 +2541,11 @@
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>UG2</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="AD10" t="n">
-        <v>-8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="inlineStr"/>
       <c r="AF10" t="inlineStr"/>
@@ -2656,20 +2652,20 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>3VbCMl1_928hbAKPG5Knnl</t>
+          <t>3$FY_ljDfBsweJfZwnfjOk</t>
         </is>
       </c>
       <c r="CE10" t="n">
-        <v>4.42</v>
+        <v>3</v>
       </c>
       <c r="CF10" t="n">
-        <v>7.38232192035912</v>
+        <v>58.6046173021893</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.3140405</v>
+        <v>29.7644175</v>
       </c>
       <c r="CH10" t="n">
-        <v>10.22805901</v>
+        <v>89.29325249999999</v>
       </c>
       <c r="CI10" t="inlineStr"/>
       <c r="CJ10" t="inlineStr"/>
@@ -2682,14 +2678,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1224</v>
+        <v>1200</v>
       </c>
       <c r="B11" t="n">
-        <v>1208</v>
+        <v>1185</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>3BN76u7jD8SONfck_e054E</t>
+          <t>3lSeJHANz4JwuuWWVWxbUH</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2709,11 +2705,11 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>LUF:342420</t>
+          <t>VRF:342787</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1224</v>
+        <v>1200</v>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
@@ -2741,11 +2737,11 @@
       <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>UG1</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="AD11" t="n">
-        <v>-3.78</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="inlineStr"/>
       <c r="AF11" t="inlineStr"/>
@@ -2801,7 +2797,7 @@
       <c r="BR11" t="inlineStr"/>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>LUF</t>
+          <t>VRF</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -2816,7 +2812,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>Luftraum</t>
+          <t>Verkehrsfläche</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -2826,7 +2822,7 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>LUF  -  Luftraum</t>
+          <t>VRF  -  Verkehrsfläche</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
@@ -2835,7 +2831,7 @@
         </is>
       </c>
       <c r="BZ11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CA11" t="n">
         <v>1</v>
@@ -2852,22 +2848,26 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>1QH5Axl111J9SJj2E3W4vu</t>
+          <t>3$FY_ljDfBsweJfZwnfjOY</t>
         </is>
       </c>
       <c r="CE11" t="n">
-        <v>3.421</v>
+        <v>3</v>
       </c>
       <c r="CF11" t="n">
-        <v>7.38098313865425</v>
+        <v>7.99949280466301</v>
       </c>
       <c r="CG11" t="n">
-        <v>2.312567</v>
+        <v>3.4365005</v>
       </c>
       <c r="CH11" t="n">
-        <v>7.911291707</v>
-      </c>
-      <c r="CI11" t="inlineStr"/>
+        <v>10.3095015</v>
+      </c>
+      <c r="CI11" t="inlineStr">
+        <is>
+          <t>VF</t>
+        </is>
+      </c>
       <c r="CJ11" t="inlineStr"/>
       <c r="CK11" t="inlineStr"/>
       <c r="CL11" t="inlineStr"/>
@@ -2878,14 +2878,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1225</v>
+        <v>1201</v>
       </c>
       <c r="B12" t="n">
-        <v>1209</v>
+        <v>1185</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0jRMZ$SnH9ouX0ZQEwstxo</t>
+          <t>1s_RuZ0k90YAlXWhJ4lnX8</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2905,11 +2905,11 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>VRF:342787</t>
+          <t>VRF:342790</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1225</v>
+        <v>1201</v>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
@@ -3048,20 +3048,20 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>3$FY_ljDfBsweJfZwnfjOY</t>
+          <t>3$FY_ljDfBsweJfZwnfjOd</t>
         </is>
       </c>
       <c r="CE12" t="n">
         <v>3</v>
       </c>
       <c r="CF12" t="n">
-        <v>7.99949280466301</v>
+        <v>8.511555999555499</v>
       </c>
       <c r="CG12" t="n">
-        <v>3.4365005</v>
+        <v>4.141197</v>
       </c>
       <c r="CH12" t="n">
-        <v>10.3095015</v>
+        <v>12.423591</v>
       </c>
       <c r="CI12" t="inlineStr">
         <is>
@@ -3078,14 +3078,14 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1226</v>
+        <v>1202</v>
       </c>
       <c r="B13" t="n">
-        <v>1209</v>
+        <v>1183</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1830E3dHD5f9qhMIKx9HB6</t>
+          <t>24xm6C08LB6PmPlweCGB8I</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -3105,11 +3105,11 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>VRF:342790</t>
+          <t>KOR:340508</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>1226</v>
+        <v>1202</v>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
@@ -3137,11 +3137,11 @@
       <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>UG2</t>
         </is>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="AE13" t="inlineStr"/>
       <c r="AF13" t="inlineStr"/>
@@ -3197,7 +3197,7 @@
       <c r="BR13" t="inlineStr"/>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>VRF</t>
+          <t>KOR</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -3212,7 +3212,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>Verkehrsfläche</t>
+          <t>Korridor</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -3222,7 +3222,7 @@
       </c>
       <c r="BX13" t="inlineStr">
         <is>
-          <t>VRF  -  Verkehrsfläche</t>
+          <t>KOR  -  Korridor</t>
         </is>
       </c>
       <c r="BY13" t="inlineStr">
@@ -3248,20 +3248,20 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>3$FY_ljDfBsweJfZwnfjOd</t>
+          <t>3VbCMl1_928hbAKPG5Knzl</t>
         </is>
       </c>
       <c r="CE13" t="n">
-        <v>3</v>
+        <v>4.12</v>
       </c>
       <c r="CF13" t="n">
-        <v>8.511555999555499</v>
+        <v>20.2968268134622</v>
       </c>
       <c r="CG13" t="n">
-        <v>4.141197</v>
+        <v>10.7493655</v>
       </c>
       <c r="CH13" t="n">
-        <v>12.423591</v>
+        <v>44.28738586</v>
       </c>
       <c r="CI13" t="inlineStr">
         <is>
@@ -3278,14 +3278,14 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1227</v>
+        <v>1203</v>
       </c>
       <c r="B14" t="n">
-        <v>1207</v>
+        <v>1184</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0emPRSOwnDOOTgYleM3B_A</t>
+          <t>0zR70dM_L5hgHRsQfW3Yo7</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3305,11 +3305,11 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>KOR:340508</t>
+          <t>KOR:342423</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1227</v>
+        <v>1203</v>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
@@ -3337,11 +3337,11 @@
       <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>UG2</t>
+          <t>UG1</t>
         </is>
       </c>
       <c r="AD14" t="n">
-        <v>-8.199999999999999</v>
+        <v>-3.78</v>
       </c>
       <c r="AE14" t="inlineStr"/>
       <c r="AF14" t="inlineStr"/>
@@ -3448,20 +3448,20 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>3VbCMl1_928hbAKPG5Knzl</t>
+          <t>1QH5Axl111J9SJj2E3W4vx</t>
         </is>
       </c>
       <c r="CE14" t="n">
-        <v>4.121</v>
+        <v>3.42000304025274</v>
       </c>
       <c r="CF14" t="n">
-        <v>20.2968268134622</v>
+        <v>26.887076979177</v>
       </c>
       <c r="CG14" t="n">
-        <v>10.7493655</v>
+        <v>18.0784765</v>
       </c>
       <c r="CH14" t="n">
-        <v>44.2981352255</v>
+        <v>61.8284445931377</v>
       </c>
       <c r="CI14" t="inlineStr">
         <is>
@@ -3478,14 +3478,14 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1228</v>
+        <v>1204</v>
       </c>
       <c r="B15" t="n">
-        <v>1208</v>
+        <v>1187</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2g6H0ojnvDdueYpZ_5Zux8</t>
+          <t>1jaqyoTjT5Bhtkj1U9RyUu</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3505,11 +3505,11 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>KOR:342423</t>
+          <t>KOR:343102</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>1228</v>
+        <v>1204</v>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
@@ -3537,11 +3537,11 @@
       <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>UG1</t>
+          <t>OG2</t>
         </is>
       </c>
       <c r="AD15" t="n">
-        <v>-3.78</v>
+        <v>7.94</v>
       </c>
       <c r="AE15" t="inlineStr"/>
       <c r="AF15" t="inlineStr"/>
@@ -3648,20 +3648,20 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>1QH5Axl111J9SJj2E3W4vx</t>
+          <t>0b93QOWH141xpbKCpGEr9v</t>
         </is>
       </c>
       <c r="CE15" t="n">
-        <v>3.421</v>
+        <v>3.57800180084113</v>
       </c>
       <c r="CF15" t="n">
-        <v>26.887076979177</v>
+        <v>22.2995095258837</v>
       </c>
       <c r="CG15" t="n">
-        <v>18.0784765</v>
+        <v>13.6486625</v>
       </c>
       <c r="CH15" t="n">
-        <v>61.8464681065</v>
+        <v>48.8349390040728</v>
       </c>
       <c r="CI15" t="inlineStr">
         <is>
@@ -3678,14 +3678,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1229</v>
+        <v>1205</v>
       </c>
       <c r="B16" t="n">
-        <v>1211</v>
+        <v>1188</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1rOBySJhH5b9YWwDU_guK1</t>
+          <t>3yI4yvxYX9aBv$Jk3GB$dy</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3705,11 +3705,11 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>KOR:343102</t>
+          <t>KOR:343282</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>1229</v>
+        <v>1205</v>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
@@ -3737,11 +3737,11 @@
       <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>OG2</t>
+          <t>OG3</t>
         </is>
       </c>
       <c r="AD16" t="n">
-        <v>7.939</v>
+        <v>11.948</v>
       </c>
       <c r="AE16" t="inlineStr"/>
       <c r="AF16" t="inlineStr"/>
@@ -3848,20 +3848,20 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>0b93QOWH141xpbKCpGEr9v</t>
+          <t>3ol_0stLL7q8pSNseENpkf</t>
         </is>
       </c>
       <c r="CE16" t="n">
-        <v>3.579</v>
+        <v>2.522</v>
       </c>
       <c r="CF16" t="n">
-        <v>22.2995095258837</v>
+        <v>24.6411125862649</v>
       </c>
       <c r="CG16" t="n">
-        <v>13.6486625</v>
+        <v>13.547317</v>
       </c>
       <c r="CH16" t="n">
-        <v>48.8485630875</v>
+        <v>34.166333474</v>
       </c>
       <c r="CI16" t="inlineStr">
         <is>
@@ -3878,14 +3878,14 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1230</v>
+        <v>1206</v>
       </c>
       <c r="B17" t="n">
-        <v>1209</v>
+        <v>1185</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>3vSADXkCf9CehgpLlu0Bds</t>
+          <t>367VhQ1U19B8v9mWQKmOzz</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3905,11 +3905,11 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>UUF:343913</t>
+          <t>UUF:343919</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>1230</v>
+        <v>1206</v>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
@@ -4048,20 +4048,20 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>3qJ9B5zvT7$hh913fcAFEG</t>
+          <t>3qJ9B5zvT7$hh913fcAFEM</t>
         </is>
       </c>
       <c r="CE17" t="n">
         <v>1</v>
       </c>
       <c r="CF17" t="n">
-        <v>28.3650362774305</v>
+        <v>27.1053636632595</v>
       </c>
       <c r="CG17" t="n">
-        <v>13.032036</v>
+        <v>35.456544</v>
       </c>
       <c r="CH17" t="n">
-        <v>13.032036</v>
+        <v>35.456544</v>
       </c>
       <c r="CI17" t="inlineStr">
         <is>
@@ -4082,14 +4082,14 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1231</v>
+        <v>1207</v>
       </c>
       <c r="B18" t="n">
-        <v>1209</v>
+        <v>1185</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2vZ$D3URf34vJnBMMHx9xX</t>
+          <t>2Hxz6DXsT92vehhFG6_ShJ</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -4109,11 +4109,11 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>UUF:343919</t>
+          <t>UUF:344049</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>1231</v>
+        <v>1207</v>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
@@ -4252,20 +4252,20 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>3qJ9B5zvT7$hh913fcAFEM</t>
+          <t>3qJ9B5zvT7$hh913fcAFC8</t>
         </is>
       </c>
       <c r="CE18" t="n">
         <v>1</v>
       </c>
       <c r="CF18" t="n">
-        <v>27.1971243796257</v>
+        <v>164.979919618776</v>
       </c>
       <c r="CG18" t="n">
-        <v>35.7954435</v>
+        <v>259.062335</v>
       </c>
       <c r="CH18" t="n">
-        <v>35.7954435</v>
+        <v>259.062335</v>
       </c>
       <c r="CI18" t="inlineStr">
         <is>
@@ -4286,14 +4286,14 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1232</v>
+        <v>1208</v>
       </c>
       <c r="B19" t="n">
-        <v>1209</v>
+        <v>1185</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1D6v$lAcHDiAsIdGYCYrg4</t>
+          <t>38tAZDumv6$hnRXN0FwtYj</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4313,11 +4313,11 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>UUF:344049</t>
+          <t>UUF:344052</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>1232</v>
+        <v>1208</v>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
@@ -4456,20 +4456,20 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>3qJ9B5zvT7$hh913fcAFC8</t>
+          <t>3qJ9B5zvT7$hh913fcAFCD</t>
         </is>
       </c>
       <c r="CE19" t="n">
         <v>1</v>
       </c>
       <c r="CF19" t="n">
-        <v>165.175783539062</v>
+        <v>32.1979140750708</v>
       </c>
       <c r="CG19" t="n">
-        <v>258.794827</v>
+        <v>56.537983</v>
       </c>
       <c r="CH19" t="n">
-        <v>258.794827</v>
+        <v>56.537983</v>
       </c>
       <c r="CI19" t="inlineStr">
         <is>
@@ -4490,38 +4490,38 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>1233</v>
+        <v>1209</v>
       </c>
       <c r="B20" t="n">
+        <v>1184</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>3W2HgVPjj8sgJOb9kc$BUn</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>IfcSpace</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>VRF:342387</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
         <v>1209</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>14Y66SGP5Fm8iYaOLsp2V8</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>IfcSpace</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>UUF:344052</t>
-        </is>
-      </c>
-      <c r="H20" t="n">
-        <v>1233</v>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
@@ -4536,7 +4536,7 @@
       <c r="S20" t="inlineStr"/>
       <c r="T20" t="inlineStr">
         <is>
-          <t>EXTERNAL</t>
+          <t>INTERNAL</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
@@ -4549,11 +4549,11 @@
       <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>UG1</t>
         </is>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>-3.78</v>
       </c>
       <c r="AE20" t="inlineStr"/>
       <c r="AF20" t="inlineStr"/>
@@ -4609,41 +4609,41 @@
       <c r="BR20" t="inlineStr"/>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>UUF</t>
+          <t>VRF</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>Aussenbereich</t>
+          <t>Allgemein</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>Aussenanlagen</t>
+          <t>Allgemein</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>Unbearbeitete Umgebungsflächen</t>
+          <t>Verkehrsfläche</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
         <is>
-          <t>Alle restlichen unbearbeiteten Aussenanlagenflächen bis zur Grundstücksgrenze</t>
+          <t>nach Bedarf</t>
         </is>
       </c>
       <c r="BX20" t="inlineStr">
         <is>
-          <t>UUF  -  Unbearbeitete Umgebungsflächen</t>
+          <t>VRF  -  Verkehrsfläche</t>
         </is>
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>EXTERNAL</t>
+          <t>INTERNAL</t>
         </is>
       </c>
       <c r="BZ20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CA20" t="n">
         <v>1</v>
@@ -4660,31 +4660,27 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>3qJ9B5zvT7$hh913fcAFCD</t>
+          <t>1QH5Axl111J9SJj2E3W4wV</t>
         </is>
       </c>
       <c r="CE20" t="n">
-        <v>1</v>
+        <v>3.42</v>
       </c>
       <c r="CF20" t="n">
-        <v>32.1979140750708</v>
+        <v>63.7340745259235</v>
       </c>
       <c r="CG20" t="n">
-        <v>56.537983</v>
+        <v>49.7657485</v>
       </c>
       <c r="CH20" t="n">
-        <v>56.537983</v>
+        <v>170.19885987</v>
       </c>
       <c r="CI20" t="inlineStr">
         <is>
-          <t>BUF</t>
-        </is>
-      </c>
-      <c r="CJ20" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
+          <t>VF</t>
+        </is>
+      </c>
+      <c r="CJ20" t="inlineStr"/>
       <c r="CK20" t="inlineStr"/>
       <c r="CL20" t="inlineStr"/>
       <c r="CM20" t="inlineStr"/>
@@ -4694,14 +4690,14 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>1234</v>
+        <v>1210</v>
       </c>
       <c r="B21" t="n">
-        <v>1208</v>
+        <v>1184</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>14zTAK7eDFxu25AGckILdY</t>
+          <t>3W8P9$rMX2_fA9sfb6fwqp</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4721,11 +4717,11 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>VRF:342387</t>
+          <t>VRF:342402</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>1234</v>
+        <v>1210</v>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
@@ -4864,20 +4860,20 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>1QH5Axl111J9SJj2E3W4wV</t>
+          <t>1QH5Axl111J9SJj2E3W4vk</t>
         </is>
       </c>
       <c r="CE21" t="n">
-        <v>3.421</v>
+        <v>3.42</v>
       </c>
       <c r="CF21" t="n">
-        <v>64.01776445924619</v>
+        <v>8.247282695482101</v>
       </c>
       <c r="CG21" t="n">
-        <v>50.4801045</v>
+        <v>4.2125125</v>
       </c>
       <c r="CH21" t="n">
-        <v>172.6924374945</v>
+        <v>14.40679275</v>
       </c>
       <c r="CI21" t="inlineStr">
         <is>
@@ -4894,14 +4890,14 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>1235</v>
+        <v>1211</v>
       </c>
       <c r="B22" t="n">
-        <v>1208</v>
+        <v>1185</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>3_49$ldkHAGOZei44e_8FY</t>
+          <t>0HX_qt1yzF3xKWplASPhYe</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4921,11 +4917,11 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>VRF:342402</t>
+          <t>BUF:345808</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>1235</v>
+        <v>1211</v>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
@@ -4940,7 +4936,7 @@
       <c r="S22" t="inlineStr"/>
       <c r="T22" t="inlineStr">
         <is>
-          <t>INTERNAL</t>
+          <t>EXTERNAL</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
@@ -4953,11 +4949,11 @@
       <c r="AB22" t="inlineStr"/>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>UG1</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="AD22" t="n">
-        <v>-3.78</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="inlineStr"/>
       <c r="AF22" t="inlineStr"/>
@@ -5013,41 +5009,41 @@
       <c r="BR22" t="inlineStr"/>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>VRF</t>
+          <t>BUF</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>Allgemein</t>
+          <t>Aussenbereich</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>Allgemein</t>
+          <t>Aussenanlagen</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>Verkehrsfläche</t>
+          <t>Bearbeitet Umgebungsflächen</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
         <is>
-          <t>nach Bedarf</t>
+          <t>Alle restlichen bearbeiteten Aussenanlagenflächen bis zur Grundstücksgrenze</t>
         </is>
       </c>
       <c r="BX22" t="inlineStr">
         <is>
-          <t>VRF  -  Verkehrsfläche</t>
+          <t>BUF  -  Bearbeitet Umgebungsflächen</t>
         </is>
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>INTERNAL</t>
+          <t>EXTERNAL</t>
         </is>
       </c>
       <c r="BZ22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CA22" t="n">
         <v>1</v>
@@ -5064,27 +5060,31 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>1QH5Axl111J9SJj2E3W4vk</t>
+          <t>3EjVH2xK16fxVS2$WCt57y</t>
         </is>
       </c>
       <c r="CE22" t="n">
-        <v>3.421</v>
+        <v>1</v>
       </c>
       <c r="CF22" t="n">
-        <v>8.247282695482101</v>
+        <v>93.1053783306551</v>
       </c>
       <c r="CG22" t="n">
-        <v>4.2125125</v>
+        <v>330.8825295</v>
       </c>
       <c r="CH22" t="n">
-        <v>14.4110052625</v>
+        <v>330.8825295</v>
       </c>
       <c r="CI22" t="inlineStr">
         <is>
-          <t>VF</t>
-        </is>
-      </c>
-      <c r="CJ22" t="inlineStr"/>
+          <t>BUF</t>
+        </is>
+      </c>
+      <c r="CJ22" t="inlineStr">
+        <is>
+          <t>???</t>
+        </is>
+      </c>
       <c r="CK22" t="inlineStr"/>
       <c r="CL22" t="inlineStr"/>
       <c r="CM22" t="inlineStr"/>
@@ -5094,14 +5094,14 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>1236</v>
+        <v>1212</v>
       </c>
       <c r="B23" t="n">
-        <v>1209</v>
+        <v>1188</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2smUqi2i10zRE_diOVjJhu</t>
+          <t>2qXFUIy2T3SBxq9lBM4xHo</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -5121,11 +5121,11 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>BUF:345808</t>
+          <t>BUF:345410</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>1236</v>
+        <v>1212</v>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
@@ -5153,11 +5153,11 @@
       <c r="AB23" t="inlineStr"/>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>OG3</t>
         </is>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>11.948</v>
       </c>
       <c r="AE23" t="inlineStr"/>
       <c r="AF23" t="inlineStr"/>
@@ -5264,20 +5264,20 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>3EjVH2xK16fxVS2$WCt57y</t>
+          <t>2VFBkNPLX5hxPkFzLFhskz</t>
         </is>
       </c>
       <c r="CE23" t="n">
         <v>1</v>
       </c>
       <c r="CF23" t="n">
-        <v>93.1053783306551</v>
+        <v>26.6601989972909</v>
       </c>
       <c r="CG23" t="n">
-        <v>330.8825295</v>
+        <v>29.3330605</v>
       </c>
       <c r="CH23" t="n">
-        <v>330.8825295</v>
+        <v>29.3330605</v>
       </c>
       <c r="CI23" t="inlineStr">
         <is>
@@ -5298,14 +5298,14 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>1237</v>
+        <v>1213</v>
       </c>
       <c r="B24" t="n">
-        <v>1212</v>
+        <v>1188</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2VPJztHKzE5eU2jmaJhVnb</t>
+          <t>2RrGEvz4H6O8oYwW_ERzQ6</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5325,11 +5325,11 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>BUF:345410</t>
+          <t>BUF:345413</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>1237</v>
+        <v>1213</v>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
@@ -5361,7 +5361,7 @@
         </is>
       </c>
       <c r="AD24" t="n">
-        <v>11.947</v>
+        <v>11.948</v>
       </c>
       <c r="AE24" t="inlineStr"/>
       <c r="AF24" t="inlineStr"/>
@@ -5468,20 +5468,20 @@
       </c>
       <c r="CD24" t="inlineStr">
         <is>
-          <t>2VFBkNPLX5hxPkFzLFhskz</t>
+          <t>2VFBkNPLX5hxPkFzLFhskw</t>
         </is>
       </c>
       <c r="CE24" t="n">
-        <v>1.001</v>
+        <v>1</v>
       </c>
       <c r="CF24" t="n">
-        <v>26.6148846931745</v>
+        <v>25.0995479191626</v>
       </c>
       <c r="CG24" t="n">
-        <v>29.418831</v>
+        <v>49.998075</v>
       </c>
       <c r="CH24" t="n">
-        <v>29.448249831</v>
+        <v>49.998075</v>
       </c>
       <c r="CI24" t="inlineStr">
         <is>
@@ -5502,14 +5502,14 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>1238</v>
+        <v>1214</v>
       </c>
       <c r="B25" t="n">
-        <v>1212</v>
+        <v>1188</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>360G1aSpvFCuurfPO7oVVK</t>
+          <t>1AENlAVbf0FPNqAceD_OOg</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5529,11 +5529,11 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>BUF:345413</t>
+          <t>BUF:345445</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>1238</v>
+        <v>1214</v>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
@@ -5565,7 +5565,7 @@
         </is>
       </c>
       <c r="AD25" t="n">
-        <v>11.947</v>
+        <v>11.948</v>
       </c>
       <c r="AE25" t="inlineStr"/>
       <c r="AF25" t="inlineStr"/>
@@ -5672,20 +5672,20 @@
       </c>
       <c r="CD25" t="inlineStr">
         <is>
-          <t>2VFBkNPLX5hxPkFzLFhskw</t>
+          <t>2VFBkNPLX5hxPkFzLFhskQ</t>
         </is>
       </c>
       <c r="CE25" t="n">
-        <v>1.001</v>
+        <v>0.9980058549395801</v>
       </c>
       <c r="CF25" t="n">
-        <v>22.6274169979695</v>
+        <v>26.6595601224005</v>
       </c>
       <c r="CG25" t="n">
-        <v>32</v>
+        <v>29.3323215</v>
       </c>
       <c r="CH25" t="n">
-        <v>32.032</v>
+        <v>29.2738285959701</v>
       </c>
       <c r="CI25" t="inlineStr">
         <is>
@@ -5706,14 +5706,14 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>1239</v>
+        <v>1215</v>
       </c>
       <c r="B26" t="n">
-        <v>1212</v>
+        <v>1185</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2gK95MKEPE$O83dwER37Qp</t>
+          <t>2vghzoGT51TxNQvOAAv0j4</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5733,11 +5733,11 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>BUF:345445</t>
+          <t>UUF:343895</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>1239</v>
+        <v>1215</v>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
@@ -5765,11 +5765,11 @@
       <c r="AB26" t="inlineStr"/>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>OG3</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="AD26" t="n">
-        <v>11.947</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="inlineStr"/>
       <c r="AF26" t="inlineStr"/>
@@ -5825,7 +5825,7 @@
       <c r="BR26" t="inlineStr"/>
       <c r="BS26" t="inlineStr">
         <is>
-          <t>BUF</t>
+          <t>UUF</t>
         </is>
       </c>
       <c r="BT26" t="inlineStr">
@@ -5840,17 +5840,17 @@
       </c>
       <c r="BV26" t="inlineStr">
         <is>
-          <t>Bearbeitet Umgebungsflächen</t>
+          <t>Unbearbeitete Umgebungsflächen</t>
         </is>
       </c>
       <c r="BW26" t="inlineStr">
         <is>
-          <t>Alle restlichen bearbeiteten Aussenanlagenflächen bis zur Grundstücksgrenze</t>
+          <t>Alle restlichen unbearbeiteten Aussenanlagenflächen bis zur Grundstücksgrenze</t>
         </is>
       </c>
       <c r="BX26" t="inlineStr">
         <is>
-          <t>BUF  -  Bearbeitet Umgebungsflächen</t>
+          <t>UUF  -  Unbearbeitete Umgebungsflächen</t>
         </is>
       </c>
       <c r="BY26" t="inlineStr">
@@ -5876,20 +5876,20 @@
       </c>
       <c r="CD26" t="inlineStr">
         <is>
-          <t>2VFBkNPLX5hxPkFzLFhskQ</t>
+          <t>3qJ9B5zvT7$hh913fcAFEk</t>
         </is>
       </c>
       <c r="CE26" t="n">
-        <v>1.001</v>
+        <v>1.00001926331646</v>
       </c>
       <c r="CF26" t="n">
-        <v>26.6132231953422</v>
+        <v>71.8572432719856</v>
       </c>
       <c r="CG26" t="n">
-        <v>29.4185435</v>
+        <v>24.9312215</v>
       </c>
       <c r="CH26" t="n">
-        <v>29.4479620435</v>
+        <v>24.9317017580095</v>
       </c>
       <c r="CI26" t="inlineStr">
         <is>
@@ -5898,7 +5898,7 @@
       </c>
       <c r="CJ26" t="inlineStr">
         <is>
-          <t>???</t>
+          <t>true</t>
         </is>
       </c>
       <c r="CK26" t="inlineStr"/>
@@ -5910,14 +5910,14 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>1240</v>
+        <v>1216</v>
       </c>
       <c r="B27" t="n">
-        <v>1209</v>
+        <v>1185</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>0XbzWrb4P70RH_r69FZvNC</t>
+          <t>2rIGmJBcz82eOKIU2HIoRF</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5937,11 +5937,11 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>UUF:343895</t>
+          <t>UUF:343913</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>1240</v>
+        <v>1216</v>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
@@ -6080,20 +6080,20 @@
       </c>
       <c r="CD27" t="inlineStr">
         <is>
-          <t>3qJ9B5zvT7$hh913fcAFEk</t>
+          <t>3qJ9B5zvT7$hh913fcAFEG</t>
         </is>
       </c>
       <c r="CE27" t="n">
         <v>1</v>
       </c>
       <c r="CF27" t="n">
-        <v>71.8572432719856</v>
+        <v>28.8364393051884</v>
       </c>
       <c r="CG27" t="n">
-        <v>24.9312215</v>
+        <v>13.119374</v>
       </c>
       <c r="CH27" t="n">
-        <v>24.9312215</v>
+        <v>13.119374</v>
       </c>
       <c r="CI27" t="inlineStr">
         <is>
@@ -6114,14 +6114,14 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>1241</v>
+        <v>1217</v>
       </c>
       <c r="B28" t="n">
-        <v>1209</v>
+        <v>1185</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>0WtOOP9cn9MBUnf0AHUQfJ</t>
+          <t>0eDs_7T5r34RBessIb8ALy</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -6145,7 +6145,7 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>1241</v>
+        <v>1217</v>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
@@ -6318,14 +6318,14 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>1242</v>
+        <v>1218</v>
       </c>
       <c r="B29" t="n">
-        <v>1209</v>
+        <v>1185</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2u0jNhx4PBahQiA_Mn0fAT</t>
+          <t>2KTKdUnXz3EAT3eZQsBIVW</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6349,7 +6349,7 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>1242</v>
+        <v>1218</v>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
@@ -6522,14 +6522,14 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>1243</v>
+        <v>1219</v>
       </c>
       <c r="B30" t="n">
-        <v>1209</v>
+        <v>1185</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1XvgrEk2L7Sf0_v9d5iT66</t>
+          <t>1dm6hXA1TAHxySfbOH_SuE</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6553,7 +6553,7 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>1243</v>
+        <v>1219</v>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
@@ -6726,14 +6726,14 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>1244</v>
+        <v>1220</v>
       </c>
       <c r="B31" t="n">
-        <v>1209</v>
+        <v>1185</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>02z0dETOLCdvSjB6spGLDD</t>
+          <t>3Ko5GwjxPFa8wWHDHgsYet</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6757,7 +6757,7 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>1244</v>
+        <v>1220</v>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
@@ -6930,14 +6930,14 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>1245</v>
+        <v>1221</v>
       </c>
       <c r="B32" t="n">
-        <v>1209</v>
+        <v>1185</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2dWGfk8A5FP9hGnKCxZb2t</t>
+          <t>0bj3cexLz16A$8LPJ5vRgB</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6961,7 +6961,7 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>1245</v>
+        <v>1221</v>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
@@ -7134,14 +7134,14 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>1246</v>
+        <v>1222</v>
       </c>
       <c r="B33" t="n">
-        <v>1209</v>
+        <v>1185</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1MqvEZmU539xzlBdmFG0Gt</t>
+          <t>3Zzx4L78nBqBHz3ZA4ivSQ</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -7161,11 +7161,11 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>VEL_L:343934</t>
+          <t>VEL_S:343931</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>1246</v>
+        <v>1222</v>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
@@ -7253,7 +7253,7 @@
       <c r="BR33" t="inlineStr"/>
       <c r="BS33" t="inlineStr">
         <is>
-          <t>VEL_L</t>
+          <t>VEL_S</t>
         </is>
       </c>
       <c r="BT33" t="inlineStr">
@@ -7268,17 +7268,17 @@
       </c>
       <c r="BV33" t="inlineStr">
         <is>
-          <t>Velo- Abstellplätze Schulpersonal</t>
+          <t>Velo- Abstellplätze Schulkinder</t>
         </is>
       </c>
       <c r="BW33" t="inlineStr">
         <is>
-          <t>8 Stück, Gedeckt und gegen Diebstahl und Vanalismus geschützt</t>
+          <t>13 Stück, davon mind 1/3 überdacht, idealerweise alle</t>
         </is>
       </c>
       <c r="BX33" t="inlineStr">
         <is>
-          <t>VEL_L  -  Velo- Abstellplätze Schulpersonal</t>
+          <t>VEL_S  -  Velo- Abstellplätze Schulkinder</t>
         </is>
       </c>
       <c r="BY33" t="inlineStr">
@@ -7304,20 +7304,20 @@
       </c>
       <c r="CD33" t="inlineStr">
         <is>
-          <t>3qJ9B5zvT7$hh913fcAFE7</t>
+          <t>3qJ9B5zvT7$hh913fcAFE2</t>
         </is>
       </c>
       <c r="CE33" t="n">
-        <v>1</v>
+        <v>0.999999999999999</v>
       </c>
       <c r="CF33" t="n">
-        <v>9.201563573455161</v>
+        <v>22.2049630491981</v>
       </c>
       <c r="CG33" t="n">
-        <v>5.20168</v>
+        <v>18.206341</v>
       </c>
       <c r="CH33" t="n">
-        <v>5.20168</v>
+        <v>18.206341</v>
       </c>
       <c r="CI33" t="inlineStr">
         <is>
@@ -7340,14 +7340,14 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>1247</v>
+        <v>1223</v>
       </c>
       <c r="B34" t="n">
-        <v>1209</v>
+        <v>1185</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>3eJReeN3j08hoB6uk90Meh</t>
+          <t>0wQhe8bif1LOoZtbl2gXny</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7367,11 +7367,11 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>VEL_S:343931</t>
+          <t>AVF:343904</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>1247</v>
+        <v>1223</v>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
@@ -7459,7 +7459,7 @@
       <c r="BR34" t="inlineStr"/>
       <c r="BS34" t="inlineStr">
         <is>
-          <t>VEL_S</t>
+          <t>AVF</t>
         </is>
       </c>
       <c r="BT34" t="inlineStr">
@@ -7474,17 +7474,17 @@
       </c>
       <c r="BV34" t="inlineStr">
         <is>
-          <t>Velo- Abstellplätze Schulkinder</t>
+          <t>Zufahrt, Abstandsfläche, Umschwung</t>
         </is>
       </c>
       <c r="BW34" t="inlineStr">
         <is>
-          <t>13 Stück, davon mind 1/3 überdacht, idealerweise alle</t>
+          <t>nach Bedarf</t>
         </is>
       </c>
       <c r="BX34" t="inlineStr">
         <is>
-          <t>VEL_S  -  Velo- Abstellplätze Schulkinder</t>
+          <t>AVF  -  Zufahrt, Abstandsfläche, Umschwung</t>
         </is>
       </c>
       <c r="BY34" t="inlineStr">
@@ -7510,20 +7510,20 @@
       </c>
       <c r="CD34" t="inlineStr">
         <is>
-          <t>3qJ9B5zvT7$hh913fcAFE2</t>
+          <t>3qJ9B5zvT7$hh913fcAFEP</t>
         </is>
       </c>
       <c r="CE34" t="n">
-        <v>0.999999999999999</v>
+        <v>1</v>
       </c>
       <c r="CF34" t="n">
-        <v>22.2049630491981</v>
+        <v>14.5215458021443</v>
       </c>
       <c r="CG34" t="n">
-        <v>18.206341</v>
+        <v>12.9937485</v>
       </c>
       <c r="CH34" t="n">
-        <v>18.206341</v>
+        <v>12.9937485</v>
       </c>
       <c r="CI34" t="inlineStr">
         <is>
@@ -7535,9 +7535,7 @@
           <t>false</t>
         </is>
       </c>
-      <c r="CK34" t="n">
-        <v>10.1</v>
-      </c>
+      <c r="CK34" t="inlineStr"/>
       <c r="CL34" t="inlineStr"/>
       <c r="CM34" t="inlineStr"/>
       <c r="CN34" t="inlineStr"/>
@@ -7546,14 +7544,14 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>1248</v>
+        <v>1224</v>
       </c>
       <c r="B35" t="n">
-        <v>1209</v>
+        <v>1185</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>3OwC$bqnH8HPMox51VeeVy</t>
+          <t>2CKlKmb3L8if01dRSHZkQk</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7573,11 +7571,11 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>AVF:343904</t>
+          <t>BUF:343892</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>1248</v>
+        <v>1224</v>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
@@ -7665,7 +7663,7 @@
       <c r="BR35" t="inlineStr"/>
       <c r="BS35" t="inlineStr">
         <is>
-          <t>AVF</t>
+          <t>BUF</t>
         </is>
       </c>
       <c r="BT35" t="inlineStr">
@@ -7680,17 +7678,17 @@
       </c>
       <c r="BV35" t="inlineStr">
         <is>
-          <t>Zufahrt, Abstandsfläche, Umschwung</t>
+          <t>Bearbeitet Umgebungsflächen</t>
         </is>
       </c>
       <c r="BW35" t="inlineStr">
         <is>
-          <t>nach Bedarf</t>
+          <t>Alle restlichen bearbeiteten Aussenanlagenflächen bis zur Grundstücksgrenze</t>
         </is>
       </c>
       <c r="BX35" t="inlineStr">
         <is>
-          <t>AVF  -  Zufahrt, Abstandsfläche, Umschwung</t>
+          <t>BUF  -  Bearbeitet Umgebungsflächen</t>
         </is>
       </c>
       <c r="BY35" t="inlineStr">
@@ -7716,20 +7714,20 @@
       </c>
       <c r="CD35" t="inlineStr">
         <is>
-          <t>3qJ9B5zvT7$hh913fcAFEP</t>
+          <t>3qJ9B5zvT7$hh913fcAFEj</t>
         </is>
       </c>
       <c r="CE35" t="n">
-        <v>1</v>
+        <v>1.00002454702819</v>
       </c>
       <c r="CF35" t="n">
-        <v>14.5215458021443</v>
+        <v>118.873554291617</v>
       </c>
       <c r="CG35" t="n">
-        <v>12.9937485</v>
+        <v>162.490801</v>
       </c>
       <c r="CH35" t="n">
-        <v>12.9937485</v>
+        <v>162.494789666272</v>
       </c>
       <c r="CI35" t="inlineStr">
         <is>
@@ -7738,7 +7736,7 @@
       </c>
       <c r="CJ35" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>???</t>
         </is>
       </c>
       <c r="CK35" t="inlineStr"/>
@@ -7750,14 +7748,14 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>1249</v>
+        <v>1225</v>
       </c>
       <c r="B36" t="n">
-        <v>1209</v>
+        <v>1185</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>3Dk2HhiCr35RYXuSaVOvs6</t>
+          <t>3VSDX0a6j5R9Sc3ExLWrsf</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7777,11 +7775,11 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>BUF:343892</t>
+          <t>BUF:343901</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>1249</v>
+        <v>1225</v>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
@@ -7920,20 +7918,20 @@
       </c>
       <c r="CD36" t="inlineStr">
         <is>
-          <t>3qJ9B5zvT7$hh913fcAFEj</t>
+          <t>3qJ9B5zvT7$hh913fcAFEa</t>
         </is>
       </c>
       <c r="CE36" t="n">
         <v>1</v>
       </c>
       <c r="CF36" t="n">
-        <v>118.876854433513</v>
+        <v>36.0606998520392</v>
       </c>
       <c r="CG36" t="n">
-        <v>162.444519</v>
+        <v>25.4851555</v>
       </c>
       <c r="CH36" t="n">
-        <v>162.444519</v>
+        <v>25.4851555</v>
       </c>
       <c r="CI36" t="inlineStr">
         <is>
@@ -7954,14 +7952,14 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>1250</v>
+        <v>1226</v>
       </c>
       <c r="B37" t="n">
-        <v>1209</v>
+        <v>1185</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>3AGSwy4Cv9YOBE5MpdNLQt</t>
+          <t>1DAsWzcd53mxYOR7lJYiHX</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7981,11 +7979,11 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>BUF:343901</t>
+          <t>BUF:343907</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>1250</v>
+        <v>1226</v>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
@@ -8124,20 +8122,20 @@
       </c>
       <c r="CD37" t="inlineStr">
         <is>
-          <t>3qJ9B5zvT7$hh913fcAFEa</t>
+          <t>3qJ9B5zvT7$hh913fcAFEQ</t>
         </is>
       </c>
       <c r="CE37" t="n">
         <v>1</v>
       </c>
       <c r="CF37" t="n">
-        <v>36.0606998520392</v>
+        <v>12.0248764381316</v>
       </c>
       <c r="CG37" t="n">
-        <v>25.4851555</v>
+        <v>4.922164</v>
       </c>
       <c r="CH37" t="n">
-        <v>25.4851555</v>
+        <v>4.922164</v>
       </c>
       <c r="CI37" t="inlineStr">
         <is>
@@ -8158,14 +8156,14 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>1251</v>
+        <v>1227</v>
       </c>
       <c r="B38" t="n">
-        <v>1209</v>
+        <v>1188</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>0E4QXUam15QfaVaTAymHn2</t>
+          <t>2jDi0spfj5xugCuK32MU8B</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -8185,11 +8183,11 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>BUF:343907</t>
+          <t>PAA:345416</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>1251</v>
+        <v>1227</v>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
@@ -8217,11 +8215,11 @@
       <c r="AB38" t="inlineStr"/>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>OG3</t>
         </is>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>11.948</v>
       </c>
       <c r="AE38" t="inlineStr"/>
       <c r="AF38" t="inlineStr"/>
@@ -8277,7 +8275,7 @@
       <c r="BR38" t="inlineStr"/>
       <c r="BS38" t="inlineStr">
         <is>
-          <t>BUF</t>
+          <t>PAA</t>
         </is>
       </c>
       <c r="BT38" t="inlineStr">
@@ -8292,17 +8290,17 @@
       </c>
       <c r="BV38" t="inlineStr">
         <is>
-          <t>Bearbeitet Umgebungsflächen</t>
+          <t>Pausenfläche PS</t>
         </is>
       </c>
       <c r="BW38" t="inlineStr">
         <is>
-          <t>Alle restlichen bearbeiteten Aussenanlagenflächen bis zur Grundstücksgrenze</t>
+          <t>Pausenfläche (Hartplatz) für ges.Schulanlage. Auf Erweiterungsbau sollen auch Dachflächen als Pausenplatz nutzbar sein</t>
         </is>
       </c>
       <c r="BX38" t="inlineStr">
         <is>
-          <t>BUF  -  Bearbeitet Umgebungsflächen</t>
+          <t>PAA  -  Pausenfläche PS</t>
         </is>
       </c>
       <c r="BY38" t="inlineStr">
@@ -8328,20 +8326,20 @@
       </c>
       <c r="CD38" t="inlineStr">
         <is>
-          <t>3qJ9B5zvT7$hh913fcAFEQ</t>
+          <t>2VFBkNPLX5hxPkFzLFhskt</t>
         </is>
       </c>
       <c r="CE38" t="n">
         <v>1</v>
       </c>
       <c r="CF38" t="n">
-        <v>12.0248764381316</v>
+        <v>61.8686530336046</v>
       </c>
       <c r="CG38" t="n">
-        <v>4.922164</v>
+        <v>125.579465</v>
       </c>
       <c r="CH38" t="n">
-        <v>4.922164</v>
+        <v>125.579465</v>
       </c>
       <c r="CI38" t="inlineStr">
         <is>
@@ -8350,11 +8348,15 @@
       </c>
       <c r="CJ38" t="inlineStr">
         <is>
-          <t>???</t>
-        </is>
-      </c>
-      <c r="CK38" t="inlineStr"/>
-      <c r="CL38" t="inlineStr"/>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="CK38" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="CL38" t="n">
+        <v>400</v>
+      </c>
       <c r="CM38" t="inlineStr"/>
       <c r="CN38" t="inlineStr"/>
       <c r="CO38" t="inlineStr"/>
@@ -8362,14 +8364,14 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>1252</v>
+        <v>1228</v>
       </c>
       <c r="B39" t="n">
-        <v>1212</v>
+        <v>1188</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2MZESDDfb379fB261rIbnR</t>
+          <t>1JP2teRZzAKhVlWoAk44Gi</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8393,7 +8395,7 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>1252</v>
+        <v>1228</v>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
@@ -8425,7 +8427,7 @@
         </is>
       </c>
       <c r="AD39" t="n">
-        <v>11.947</v>
+        <v>11.948</v>
       </c>
       <c r="AE39" t="inlineStr"/>
       <c r="AF39" t="inlineStr"/>
@@ -8536,16 +8538,16 @@
         </is>
       </c>
       <c r="CE39" t="n">
-        <v>1.001</v>
+        <v>1</v>
       </c>
       <c r="CF39" t="n">
-        <v>61.8367587494543</v>
+        <v>61.8746072005705</v>
       </c>
       <c r="CG39" t="n">
-        <v>126.1984585</v>
+        <v>125.616293</v>
       </c>
       <c r="CH39" t="n">
-        <v>126.3246569585</v>
+        <v>125.616293</v>
       </c>
       <c r="CI39" t="inlineStr">
         <is>
@@ -8570,14 +8572,14 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>1253</v>
+        <v>1229</v>
       </c>
       <c r="B40" t="n">
-        <v>1212</v>
+        <v>1185</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2VPSmwn8f80wlwsZLQwj7f</t>
+          <t>2pH4Wqvuf1bu8FEuNmVz7e</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8597,11 +8599,11 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>PAA:345416</t>
+          <t>ALL:343925</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>1253</v>
+        <v>1229</v>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
@@ -8629,11 +8631,11 @@
       <c r="AB40" t="inlineStr"/>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>OG3</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="AD40" t="n">
-        <v>11.947</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="inlineStr"/>
       <c r="AF40" t="inlineStr"/>
@@ -8689,7 +8691,7 @@
       <c r="BR40" t="inlineStr"/>
       <c r="BS40" t="inlineStr">
         <is>
-          <t>PAA</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="BT40" t="inlineStr">
@@ -8704,17 +8706,17 @@
       </c>
       <c r="BV40" t="inlineStr">
         <is>
-          <t>Pausenfläche PS</t>
+          <t>Allwetterplatz mit Sportbelag</t>
         </is>
       </c>
       <c r="BW40" t="inlineStr">
         <is>
-          <t>Pausenfläche (Hartplatz) für ges.Schulanlage. Auf Erweiterungsbau sollen auch Dachflächen als Pausenplatz nutzbar sein</t>
+          <t>idealerweise 26 x 40m - ebenerdiger sportfunktionaler Allwetterplatz (EPDM-Belag, Ballfang) mit minimalen Spielfeld-Abmessungen 24 x 13m plus Sicherheitsraum umlaufend b=1m zwingend nachzuweisen</t>
         </is>
       </c>
       <c r="BX40" t="inlineStr">
         <is>
-          <t>PAA  -  Pausenfläche PS</t>
+          <t>ALL  -  Allwetterplatz mit Sportbelag</t>
         </is>
       </c>
       <c r="BY40" t="inlineStr">
@@ -8740,20 +8742,20 @@
       </c>
       <c r="CD40" t="inlineStr">
         <is>
-          <t>2VFBkNPLX5hxPkFzLFhskt</t>
+          <t>3qJ9B5zvT7$hh913fcAFEC</t>
         </is>
       </c>
       <c r="CE40" t="n">
-        <v>1.001</v>
+        <v>1</v>
       </c>
       <c r="CF40" t="n">
-        <v>61.8374883969868</v>
+        <v>82.51586312796729</v>
       </c>
       <c r="CG40" t="n">
-        <v>126.246645</v>
+        <v>396.6236325</v>
       </c>
       <c r="CH40" t="n">
-        <v>126.372891645</v>
+        <v>396.6236325</v>
       </c>
       <c r="CI40" t="inlineStr">
         <is>
@@ -8766,10 +8768,10 @@
         </is>
       </c>
       <c r="CK40" t="n">
-        <v>10.8</v>
+        <v>10.4</v>
       </c>
       <c r="CL40" t="n">
-        <v>400</v>
+        <v>390</v>
       </c>
       <c r="CM40" t="inlineStr"/>
       <c r="CN40" t="inlineStr"/>
@@ -8778,14 +8780,14 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>1254</v>
+        <v>1230</v>
       </c>
       <c r="B41" t="n">
-        <v>1209</v>
+        <v>1185</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2VcirkfBf6ahuppLqfjuCo</t>
+          <t>1y6$NkJCn2eRH9vQ05Vfth</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8805,11 +8807,11 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>ALL:343925</t>
+          <t>PPA:343898</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>1254</v>
+        <v>1230</v>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
@@ -8897,7 +8899,7 @@
       <c r="BR41" t="inlineStr"/>
       <c r="BS41" t="inlineStr">
         <is>
-          <t>ALL</t>
+          <t>PPA</t>
         </is>
       </c>
       <c r="BT41" t="inlineStr">
@@ -8912,17 +8914,17 @@
       </c>
       <c r="BV41" t="inlineStr">
         <is>
-          <t>Allwetterplatz mit Sportbelag</t>
+          <t>Parkplätze PW (Normbedarf)</t>
         </is>
       </c>
       <c r="BW41" t="inlineStr">
         <is>
-          <t>idealerweise 26 x 40m - ebenerdiger sportfunktionaler Allwetterplatz (EPDM-Belag, Ballfang) mit minimalen Spielfeld-Abmessungen 24 x 13m plus Sicherheitsraum umlaufend b=1m zwingend nachzuweisen</t>
+          <t>Gesamtangebot für Schulpersonal, Besuchende, Anlieferung, IV-Transport usw. Reduktionsfaktor nicht berücksichtigt&amp;#10;1 PP-IV auf Anlage, 5 PP ausgelagert in TG vom GFA Wildbach, Wildbachstr. 11</t>
         </is>
       </c>
       <c r="BX41" t="inlineStr">
         <is>
-          <t>ALL  -  Allwetterplatz mit Sportbelag</t>
+          <t>PPA  -  Parkplätze PW (Normbedarf)</t>
         </is>
       </c>
       <c r="BY41" t="inlineStr">
@@ -8948,20 +8950,20 @@
       </c>
       <c r="CD41" t="inlineStr">
         <is>
-          <t>3qJ9B5zvT7$hh913fcAFEC</t>
+          <t>3qJ9B5zvT7$hh913fcAFEZ</t>
         </is>
       </c>
       <c r="CE41" t="n">
         <v>1</v>
       </c>
       <c r="CF41" t="n">
-        <v>82.51586312796729</v>
+        <v>20.3229188998477</v>
       </c>
       <c r="CG41" t="n">
-        <v>396.6236325</v>
+        <v>17.289957</v>
       </c>
       <c r="CH41" t="n">
-        <v>396.6236325</v>
+        <v>17.289957</v>
       </c>
       <c r="CI41" t="inlineStr">
         <is>
@@ -8974,10 +8976,10 @@
         </is>
       </c>
       <c r="CK41" t="n">
-        <v>10.4</v>
+        <v>10.1</v>
       </c>
       <c r="CL41" t="n">
-        <v>390</v>
+        <v>12</v>
       </c>
       <c r="CM41" t="inlineStr"/>
       <c r="CN41" t="inlineStr"/>
@@ -8986,14 +8988,14 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>1255</v>
+        <v>1231</v>
       </c>
       <c r="B42" t="n">
-        <v>1209</v>
+        <v>1185</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>07p_i19HfFMxUYszLXHx0R</t>
+          <t>0a48Ih65rFx8QfDnXMMhEl</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -9013,11 +9015,11 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>PPA:343898</t>
+          <t>VEL_L:343934</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>1255</v>
+        <v>1231</v>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
@@ -9105,7 +9107,7 @@
       <c r="BR42" t="inlineStr"/>
       <c r="BS42" t="inlineStr">
         <is>
-          <t>PPA</t>
+          <t>VEL_L</t>
         </is>
       </c>
       <c r="BT42" t="inlineStr">
@@ -9120,17 +9122,17 @@
       </c>
       <c r="BV42" t="inlineStr">
         <is>
-          <t>Parkplätze PW (Normbedarf)</t>
+          <t>Velo- Abstellplätze Schulpersonal</t>
         </is>
       </c>
       <c r="BW42" t="inlineStr">
         <is>
-          <t>Gesamtangebot für Schulpersonal, Besuchende, Anlieferung, IV-Transport usw. Reduktionsfaktor nicht berücksichtigt&amp;#10;1 PP-IV auf Anlage, 5 PP ausgelagert in TG vom GFA Wildbach, Wildbachstr. 11</t>
+          <t>8 Stück, Gedeckt und gegen Diebstahl und Vanalismus geschützt</t>
         </is>
       </c>
       <c r="BX42" t="inlineStr">
         <is>
-          <t>PPA  -  Parkplätze PW (Normbedarf)</t>
+          <t>VEL_L  -  Velo- Abstellplätze Schulpersonal</t>
         </is>
       </c>
       <c r="BY42" t="inlineStr">
@@ -9156,20 +9158,20 @@
       </c>
       <c r="CD42" t="inlineStr">
         <is>
-          <t>3qJ9B5zvT7$hh913fcAFEZ</t>
+          <t>3qJ9B5zvT7$hh913fcAFE7</t>
         </is>
       </c>
       <c r="CE42" t="n">
         <v>1</v>
       </c>
       <c r="CF42" t="n">
-        <v>20.3229188998477</v>
+        <v>9.201563573455161</v>
       </c>
       <c r="CG42" t="n">
-        <v>17.289957</v>
+        <v>5.20168</v>
       </c>
       <c r="CH42" t="n">
-        <v>17.289957</v>
+        <v>5.20168</v>
       </c>
       <c r="CI42" t="inlineStr">
         <is>
@@ -9178,15 +9180,13 @@
       </c>
       <c r="CJ42" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="CK42" t="n">
         <v>10.1</v>
       </c>
-      <c r="CL42" t="n">
-        <v>12</v>
-      </c>
+      <c r="CL42" t="inlineStr"/>
       <c r="CM42" t="inlineStr"/>
       <c r="CN42" t="inlineStr"/>
       <c r="CO42" t="inlineStr"/>
@@ -9194,14 +9194,14 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>1256</v>
+        <v>1232</v>
       </c>
       <c r="B43" t="n">
-        <v>1209</v>
+        <v>1185</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>3dUr5q39zEXBCsj4PLV405</t>
+          <t>3sBsqaQPb0euZE5Csd1V40</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -9225,7 +9225,7 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>1256</v>
+        <v>1232</v>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
@@ -9368,16 +9368,16 @@
         </is>
       </c>
       <c r="CE43" t="n">
-        <v>1</v>
+        <v>1.00000564844451</v>
       </c>
       <c r="CF43" t="n">
-        <v>36.5379660958738</v>
+        <v>36.5380755997099</v>
       </c>
       <c r="CG43" t="n">
-        <v>73.566976</v>
+        <v>73.5662785</v>
       </c>
       <c r="CH43" t="n">
-        <v>73.566976</v>
+        <v>73.5666940350422</v>
       </c>
       <c r="CI43" t="inlineStr">
         <is>
@@ -9400,14 +9400,14 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>1257</v>
+        <v>1233</v>
       </c>
       <c r="B44" t="n">
-        <v>1209</v>
+        <v>1185</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>3WAjbS9Tz63fT8SRxhsEgW</t>
+          <t>2jZ_u9g6bC0gnFdRULl6Ao</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9431,7 +9431,7 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>1257</v>
+        <v>1233</v>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
@@ -9608,14 +9608,14 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>1258</v>
+        <v>1234</v>
       </c>
       <c r="B45" t="n">
-        <v>1209</v>
+        <v>1185</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2F9RWBhUfEZ8$cJ_kTeVpx</t>
+          <t>0owNcgsrLCORAeZymoLxMZ</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9639,7 +9639,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>1258</v>
+        <v>1234</v>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
@@ -9778,16 +9778,16 @@
         </is>
       </c>
       <c r="CE45" t="n">
-        <v>1</v>
+        <v>1.00001430884626</v>
       </c>
       <c r="CF45" t="n">
-        <v>70.7275988525333</v>
+        <v>70.7243967332807</v>
       </c>
       <c r="CG45" t="n">
-        <v>295.86007</v>
+        <v>295.8120275</v>
       </c>
       <c r="CH45" t="n">
-        <v>295.86007</v>
+        <v>295.816260228824</v>
       </c>
       <c r="CI45" t="inlineStr">
         <is>
@@ -9812,14 +9812,14 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>1259</v>
+        <v>1235</v>
       </c>
       <c r="B46" t="n">
-        <v>1209</v>
+        <v>1185</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>3vBeHUwhfB5OcVQruWBfzN</t>
+          <t>0cuCI57f5FDx6c5xjTH_wt</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9843,7 +9843,7 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>1259</v>
+        <v>1235</v>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
@@ -9989,13 +9989,13 @@
         <v>1</v>
       </c>
       <c r="CF46" t="n">
-        <v>228.018781084836</v>
+        <v>228.018850694891</v>
       </c>
       <c r="CG46" t="n">
-        <v>627.669683</v>
+        <v>627.6705645</v>
       </c>
       <c r="CH46" t="n">
-        <v>627.669683</v>
+        <v>627.6705645</v>
       </c>
       <c r="CI46" t="inlineStr">
         <is>
@@ -10020,14 +10020,14 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>1260</v>
+        <v>1236</v>
       </c>
       <c r="B47" t="n">
-        <v>1207</v>
+        <v>1183</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>3LuW9jHbHBBAyJit_$Yn3$</t>
+          <t>3EFA13Ox1F58pYx6_i5NyU</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -10051,7 +10051,7 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>1260</v>
+        <v>1236</v>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
@@ -10194,7 +10194,7 @@
         </is>
       </c>
       <c r="CE47" t="n">
-        <v>4.121</v>
+        <v>4.12</v>
       </c>
       <c r="CF47" t="n">
         <v>57.8747961939876</v>
@@ -10203,7 +10203,7 @@
         <v>130.4597315</v>
       </c>
       <c r="CH47" t="n">
-        <v>537.6245535115</v>
+        <v>537.49409378</v>
       </c>
       <c r="CI47" t="inlineStr">
         <is>
@@ -10226,14 +10226,14 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>1261</v>
+        <v>1237</v>
       </c>
       <c r="B48" t="n">
-        <v>1207</v>
+        <v>1183</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>0ZrdVUR4b0zxBrw6VrPmpy</t>
+          <t>0VzQ2RIZnBkuyXmMpvbN9_</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -10257,7 +10257,7 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>1261</v>
+        <v>1237</v>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
@@ -10400,7 +10400,7 @@
         </is>
       </c>
       <c r="CE48" t="n">
-        <v>4.121</v>
+        <v>4.12</v>
       </c>
       <c r="CF48" t="n">
         <v>29.2296306506672</v>
@@ -10409,7 +10409,7 @@
         <v>38.861445</v>
       </c>
       <c r="CH48" t="n">
-        <v>160.148014845</v>
+        <v>160.1091534</v>
       </c>
       <c r="CI48" t="inlineStr">
         <is>
@@ -10432,14 +10432,14 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>1262</v>
+        <v>1238</v>
       </c>
       <c r="B49" t="n">
-        <v>1208</v>
+        <v>1184</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>1R9Imo_5167B$XHbYy7aZ6</t>
+          <t>0bebBo2BjBix6YQ7lpTjg5</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10463,7 +10463,7 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>1262</v>
+        <v>1238</v>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
@@ -10606,7 +10606,7 @@
         </is>
       </c>
       <c r="CE49" t="n">
-        <v>3.421</v>
+        <v>3.42</v>
       </c>
       <c r="CF49" t="n">
         <v>21.5722949304711</v>
@@ -10615,7 +10615,7 @@
         <v>25.280915</v>
       </c>
       <c r="CH49" t="n">
-        <v>86.48601021499999</v>
+        <v>86.4607293</v>
       </c>
       <c r="CI49" t="inlineStr">
         <is>
@@ -10638,14 +10638,14 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>1263</v>
+        <v>1239</v>
       </c>
       <c r="B50" t="n">
-        <v>1209</v>
+        <v>1185</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>0teRCO0lj5OQYpPkvQztRq</t>
+          <t>0p4XPibzXDmfYuHdDNQKoi</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10669,7 +10669,7 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>1263</v>
+        <v>1239</v>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
@@ -10811,13 +10811,13 @@
         <v>1</v>
       </c>
       <c r="CF50" t="n">
-        <v>32.1201520903664</v>
+        <v>32.1152224910364</v>
       </c>
       <c r="CG50" t="n">
-        <v>34.123994</v>
+        <v>34.1596555</v>
       </c>
       <c r="CH50" t="n">
-        <v>34.123994</v>
+        <v>34.1596555</v>
       </c>
       <c r="CI50" t="inlineStr">
         <is>
@@ -10838,14 +10838,14 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>1264</v>
+        <v>1240</v>
       </c>
       <c r="B51" t="n">
-        <v>1209</v>
+        <v>1185</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>3O5OUxbKP5_PZAUUrtfSgZ</t>
+          <t>3vzyyhvhTCCxHI3Ujz_Pdk</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10869,7 +10869,7 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>1264</v>
+        <v>1240</v>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
@@ -11015,13 +11015,13 @@
         <v>3</v>
       </c>
       <c r="CF51" t="n">
-        <v>13.0853052853127</v>
+        <v>13.1107742818786</v>
       </c>
       <c r="CG51" t="n">
-        <v>13.396027</v>
+        <v>13.502395</v>
       </c>
       <c r="CH51" t="n">
-        <v>40.188081</v>
+        <v>40.507185</v>
       </c>
       <c r="CI51" t="inlineStr">
         <is>
@@ -11042,14 +11042,14 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>1265</v>
+        <v>1241</v>
       </c>
       <c r="B52" t="n">
-        <v>1207</v>
+        <v>1183</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2v3d7GGqDEd8IyrTdRXWWY</t>
+          <t>3P24pHOeX7huTaoUa46vgT</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -11073,7 +11073,7 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>1265</v>
+        <v>1241</v>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr"/>
@@ -11216,7 +11216,7 @@
         </is>
       </c>
       <c r="CE52" t="n">
-        <v>4.121</v>
+        <v>4.11999999999999</v>
       </c>
       <c r="CF52" t="n">
         <v>33.6781770938313</v>
@@ -11225,7 +11225,7 @@
         <v>68.07347249999999</v>
       </c>
       <c r="CH52" t="n">
-        <v>280.5307801725</v>
+        <v>280.462706699999</v>
       </c>
       <c r="CI52" t="inlineStr">
         <is>
@@ -11248,14 +11248,14 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>1266</v>
+        <v>1242</v>
       </c>
       <c r="B53" t="n">
-        <v>1208</v>
+        <v>1184</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2_kl8xFAvE_Oi0Djmy1jeA</t>
+          <t>0OAGNaNgv3wwzf3ckQ_KTm</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -11279,7 +11279,7 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>1266</v>
+        <v>1242</v>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
@@ -11422,7 +11422,7 @@
         </is>
       </c>
       <c r="CE53" t="n">
-        <v>3.421</v>
+        <v>3.42</v>
       </c>
       <c r="CF53" t="n">
         <v>15.2440637556325</v>
@@ -11431,7 +11431,7 @@
         <v>13.790366</v>
       </c>
       <c r="CH53" t="n">
-        <v>47.176842086</v>
+        <v>47.16305172</v>
       </c>
       <c r="CI53" t="inlineStr">
         <is>
@@ -11454,14 +11454,14 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>1267</v>
+        <v>1243</v>
       </c>
       <c r="B54" t="n">
-        <v>1208</v>
+        <v>1184</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>1wnl70Hcf4J91aH6kWoQ5w</t>
+          <t>2pxOd96v91mxlwof2bdwwu</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11485,7 +11485,7 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>1267</v>
+        <v>1243</v>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
@@ -11628,7 +11628,7 @@
         </is>
       </c>
       <c r="CE54" t="n">
-        <v>3.421</v>
+        <v>3.42</v>
       </c>
       <c r="CF54" t="n">
         <v>7.93463321095369</v>
@@ -11637,7 +11637,7 @@
         <v>3.934619</v>
       </c>
       <c r="CH54" t="n">
-        <v>13.460331599</v>
+        <v>13.45639698</v>
       </c>
       <c r="CI54" t="inlineStr">
         <is>
@@ -11658,14 +11658,14 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>1268</v>
+        <v>1244</v>
       </c>
       <c r="B55" t="n">
-        <v>1210</v>
+        <v>1186</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>1MPw1r9hv6$h6AZYdCPJK4</t>
+          <t>2lK1NiaZXE9g_b2KyM_qzf</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11689,7 +11689,7 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>1268</v>
+        <v>1244</v>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr"/>
@@ -11862,14 +11862,14 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>1269</v>
+        <v>1245</v>
       </c>
       <c r="B56" t="n">
-        <v>1208</v>
+        <v>1184</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>1F3Fkq$vj7GQErmS_ow7lc</t>
+          <t>2DRzef4hn3IgIiLgkhkHE9</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11893,7 +11893,7 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>1269</v>
+        <v>1245</v>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr"/>
@@ -12036,7 +12036,7 @@
         </is>
       </c>
       <c r="CE56" t="n">
-        <v>3.421</v>
+        <v>3.42</v>
       </c>
       <c r="CF56" t="n">
         <v>16.0088117114571</v>
@@ -12045,7 +12045,7 @@
         <v>15.551871</v>
       </c>
       <c r="CH56" t="n">
-        <v>53.202950691</v>
+        <v>53.18739882</v>
       </c>
       <c r="CI56" t="inlineStr">
         <is>
@@ -12066,14 +12066,14 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>1270</v>
+        <v>1246</v>
       </c>
       <c r="B57" t="n">
-        <v>1208</v>
+        <v>1184</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>1acftYr2jDufGYUUZLoAmB</t>
+          <t>2EaietiEbAIPhvSO2Cvy$b</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -12097,7 +12097,7 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>1270</v>
+        <v>1246</v>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr"/>
@@ -12240,7 +12240,7 @@
         </is>
       </c>
       <c r="CE57" t="n">
-        <v>3.421</v>
+        <v>3.42</v>
       </c>
       <c r="CF57" t="n">
         <v>16.1179353577298</v>
@@ -12249,7 +12249,7 @@
         <v>15.807475</v>
       </c>
       <c r="CH57" t="n">
-        <v>54.077371975</v>
+        <v>54.0615645</v>
       </c>
       <c r="CI57" t="inlineStr">
         <is>
@@ -12270,14 +12270,14 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>1271</v>
+        <v>1247</v>
       </c>
       <c r="B58" t="n">
-        <v>1208</v>
+        <v>1184</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>1vDbowLhr7nx5SdmnF8FXc</t>
+          <t>2_ozTiGP19wxfIiizV$YDP</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -12301,7 +12301,7 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>1271</v>
+        <v>1247</v>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
@@ -12444,16 +12444,16 @@
         </is>
       </c>
       <c r="CE58" t="n">
-        <v>3.421</v>
+        <v>3.42</v>
       </c>
       <c r="CF58" t="n">
-        <v>38.5924363426088</v>
+        <v>38.4721477169385</v>
       </c>
       <c r="CG58" t="n">
-        <v>42.344828</v>
+        <v>42.594047</v>
       </c>
       <c r="CH58" t="n">
-        <v>144.861656588</v>
+        <v>145.67164074</v>
       </c>
       <c r="CI58" t="inlineStr">
         <is>
@@ -12474,14 +12474,14 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>1272</v>
+        <v>1248</v>
       </c>
       <c r="B59" t="n">
-        <v>1208</v>
+        <v>1184</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2oV52czXD7zAOL8XOUSL78</t>
+          <t>1hrw6SBSX5_xz0kjcf$lQq</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -12505,7 +12505,7 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>1272</v>
+        <v>1248</v>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
@@ -12648,16 +12648,16 @@
         </is>
       </c>
       <c r="CE59" t="n">
-        <v>3.421</v>
+        <v>3.4200048337541</v>
       </c>
       <c r="CF59" t="n">
-        <v>38.5665051072028</v>
+        <v>38.4494075508202</v>
       </c>
       <c r="CG59" t="n">
-        <v>42.0894875</v>
+        <v>42.33211</v>
       </c>
       <c r="CH59" t="n">
-        <v>143.9881367375</v>
+        <v>144.77602082301</v>
       </c>
       <c r="CI59" t="inlineStr">
         <is>
@@ -12678,14 +12678,14 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>1273</v>
+        <v>1249</v>
       </c>
       <c r="B60" t="n">
-        <v>1210</v>
+        <v>1185</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>1FDFHpwUH4NB1tapjSpmKb</t>
+          <t>1KAZImcajE19VMZ2urkS9A</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12705,11 +12705,11 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>SGR:342955</t>
+          <t>AGS:343922</t>
         </is>
       </c>
       <c r="H60" t="n">
-        <v>1273</v>
+        <v>1249</v>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr"/>
@@ -12724,7 +12724,7 @@
       <c r="S60" t="inlineStr"/>
       <c r="T60" t="inlineStr">
         <is>
-          <t>INTERNAL</t>
+          <t>EXTERNAL</t>
         </is>
       </c>
       <c r="U60" t="inlineStr"/>
@@ -12737,11 +12737,11 @@
       <c r="AB60" t="inlineStr"/>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>OG1</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="AD60" t="n">
-        <v>2.998</v>
+        <v>0</v>
       </c>
       <c r="AE60" t="inlineStr"/>
       <c r="AF60" t="inlineStr"/>
@@ -12797,7 +12797,7 @@
       <c r="BR60" t="inlineStr"/>
       <c r="BS60" t="inlineStr">
         <is>
-          <t>SGR</t>
+          <t>AGS</t>
         </is>
       </c>
       <c r="BT60" t="inlineStr">
@@ -12812,17 +12812,17 @@
       </c>
       <c r="BV60" t="inlineStr">
         <is>
-          <t>Geräteraum</t>
+          <t>Aussengeräteraum Sport</t>
         </is>
       </c>
       <c r="BW60" t="inlineStr">
         <is>
-          <t>Diekt aus der zugehörigen Sporthalle, stufenlos zugänglich. Inkl. abschliessbarem Kleingeräteraum. Zu beachten: Mind. 6m Raumtiefe und 2.5m Höhe im Licht.</t>
+          <t>Direkter Zugang von Aussen,mit Beleuchtung und Ballkompressor</t>
         </is>
       </c>
       <c r="BX60" t="inlineStr">
         <is>
-          <t>SGR  -  Geräteraum</t>
+          <t>AGS  -  Aussengeräteraum Sport</t>
         </is>
       </c>
       <c r="BY60" t="inlineStr">
@@ -12834,7 +12834,7 @@
         <v>1</v>
       </c>
       <c r="CA60" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CB60" t="inlineStr">
         <is>
@@ -12848,20 +12848,20 @@
       </c>
       <c r="CD60" t="inlineStr">
         <is>
-          <t>0b93QOWH141xpbKCpGErNi</t>
+          <t>3qJ9B5zvT7$hh913fcAFEB</t>
         </is>
       </c>
       <c r="CE60" t="n">
-        <v>3.982</v>
+        <v>1</v>
       </c>
       <c r="CF60" t="n">
-        <v>41.7997852969898</v>
+        <v>15.9988743322313</v>
       </c>
       <c r="CG60" t="n">
-        <v>89.581008</v>
+        <v>14.9977755</v>
       </c>
       <c r="CH60" t="n">
-        <v>356.711573856</v>
+        <v>14.9977755</v>
       </c>
       <c r="CI60" t="inlineStr">
         <is>
@@ -12873,7 +12873,7 @@
         <v>4.1</v>
       </c>
       <c r="CL60" t="n">
-        <v>90</v>
+        <v>15</v>
       </c>
       <c r="CM60" t="inlineStr"/>
       <c r="CN60" t="inlineStr"/>
@@ -12882,14 +12882,14 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>1274</v>
+        <v>1250</v>
       </c>
       <c r="B61" t="n">
-        <v>1209</v>
+        <v>1184</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>0qoMVDV8fAzBp8ww__y4Tz</t>
+          <t>3MbScePwXCG951Z0r4L0yN</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12909,11 +12909,11 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>AGS:343922</t>
+          <t>GSA:342369</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>1274</v>
+        <v>1250</v>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr"/>
@@ -12928,7 +12928,7 @@
       <c r="S61" t="inlineStr"/>
       <c r="T61" t="inlineStr">
         <is>
-          <t>EXTERNAL</t>
+          <t>INTERNAL</t>
         </is>
       </c>
       <c r="U61" t="inlineStr"/>
@@ -12941,11 +12941,11 @@
       <c r="AB61" t="inlineStr"/>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>UG1</t>
         </is>
       </c>
       <c r="AD61" t="n">
-        <v>0</v>
+        <v>-3.78</v>
       </c>
       <c r="AE61" t="inlineStr"/>
       <c r="AF61" t="inlineStr"/>
@@ -13001,7 +13001,7 @@
       <c r="BR61" t="inlineStr"/>
       <c r="BS61" t="inlineStr">
         <is>
-          <t>AGS</t>
+          <t>GSA</t>
         </is>
       </c>
       <c r="BT61" t="inlineStr">
@@ -13016,17 +13016,17 @@
       </c>
       <c r="BV61" t="inlineStr">
         <is>
-          <t>Aussengeräteraum Sport</t>
+          <t>Garderobe inkl. Dusche</t>
         </is>
       </c>
       <c r="BW61" t="inlineStr">
         <is>
-          <t>Direkter Zugang von Aussen,mit Beleuchtung und Ballkompressor</t>
+          <t>Garderoben gem. BASPO 201. Jede Umkleide schliesst direkt an einen Duschraum an. &amp;#10;Inkl. Abtrockungszone, Garderoben gem. BASPO 201. Pro Duschraum ist 1 gehbehindertengerechter Duschplatz vorhanden.</t>
         </is>
       </c>
       <c r="BX61" t="inlineStr">
         <is>
-          <t>AGS  -  Aussengeräteraum Sport</t>
+          <t>GSA  -  Garderobe inkl. Dusche</t>
         </is>
       </c>
       <c r="BY61" t="inlineStr">
@@ -13038,7 +13038,7 @@
         <v>1</v>
       </c>
       <c r="CA61" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="CB61" t="inlineStr">
         <is>
@@ -13052,32 +13052,32 @@
       </c>
       <c r="CD61" t="inlineStr">
         <is>
-          <t>3qJ9B5zvT7$hh913fcAFEB</t>
+          <t>1QH5Axl111J9SJj2E3W4wD</t>
         </is>
       </c>
       <c r="CE61" t="n">
-        <v>1</v>
+        <v>3.4200029159233</v>
       </c>
       <c r="CF61" t="n">
-        <v>15.9988743322313</v>
+        <v>38.4766189708997</v>
       </c>
       <c r="CG61" t="n">
-        <v>14.9977755</v>
+        <v>42.543861</v>
       </c>
       <c r="CH61" t="n">
-        <v>14.9977755</v>
+        <v>145.500128674635</v>
       </c>
       <c r="CI61" t="inlineStr">
         <is>
-          <t>HNF</t>
+          <t>NNF</t>
         </is>
       </c>
       <c r="CJ61" t="inlineStr"/>
       <c r="CK61" t="n">
-        <v>4.1</v>
+        <v>7.2</v>
       </c>
       <c r="CL61" t="n">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="CM61" t="inlineStr"/>
       <c r="CN61" t="inlineStr"/>
@@ -13086,14 +13086,14 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>1275</v>
+        <v>1251</v>
       </c>
       <c r="B62" t="n">
-        <v>1208</v>
+        <v>1184</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>1d_UGp1UD2pfCq6QCu1odj</t>
+          <t>3YWB1QD45A0ffgE_grSlSK</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -13113,11 +13113,11 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>GSA:342369</t>
+          <t>GSA:342372</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>1275</v>
+        <v>1251</v>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
@@ -13256,20 +13256,20 @@
       </c>
       <c r="CD62" t="inlineStr">
         <is>
-          <t>1QH5Axl111J9SJj2E3W4wD</t>
+          <t>1QH5Axl111J9SJj2E3W4w8</t>
         </is>
       </c>
       <c r="CE62" t="n">
-        <v>3.421</v>
+        <v>3.42</v>
       </c>
       <c r="CF62" t="n">
-        <v>38.597841235775</v>
+        <v>38.3845491226873</v>
       </c>
       <c r="CG62" t="n">
-        <v>42.293608</v>
+        <v>42.138849</v>
       </c>
       <c r="CH62" t="n">
-        <v>144.686432968</v>
+        <v>144.11486358</v>
       </c>
       <c r="CI62" t="inlineStr">
         <is>
@@ -13290,14 +13290,14 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>1276</v>
+        <v>1252</v>
       </c>
       <c r="B63" t="n">
-        <v>1208</v>
+        <v>1183</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>1DjBk084n8gfRcElXcnhlR</t>
+          <t>0fphzOn3z3ffzYnIZDfkRZ</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -13317,11 +13317,11 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>GSA:342372</t>
+          <t>SGR:340482</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>1276</v>
+        <v>1252</v>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr"/>
@@ -13349,11 +13349,11 @@
       <c r="AB63" t="inlineStr"/>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>UG1</t>
+          <t>UG2</t>
         </is>
       </c>
       <c r="AD63" t="n">
-        <v>-3.78</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="AE63" t="inlineStr"/>
       <c r="AF63" t="inlineStr"/>
@@ -13409,7 +13409,7 @@
       <c r="BR63" t="inlineStr"/>
       <c r="BS63" t="inlineStr">
         <is>
-          <t>GSA</t>
+          <t>SGR</t>
         </is>
       </c>
       <c r="BT63" t="inlineStr">
@@ -13424,17 +13424,17 @@
       </c>
       <c r="BV63" t="inlineStr">
         <is>
-          <t>Garderobe inkl. Dusche</t>
+          <t>Geräteraum</t>
         </is>
       </c>
       <c r="BW63" t="inlineStr">
         <is>
-          <t>Garderoben gem. BASPO 201. Jede Umkleide schliesst direkt an einen Duschraum an. &amp;#10;Inkl. Abtrockungszone, Garderoben gem. BASPO 201. Pro Duschraum ist 1 gehbehindertengerechter Duschplatz vorhanden.</t>
+          <t>Diekt aus der zugehörigen Sporthalle, stufenlos zugänglich. Inkl. abschliessbarem Kleingeräteraum. Zu beachten: Mind. 6m Raumtiefe und 2.5m Höhe im Licht.</t>
         </is>
       </c>
       <c r="BX63" t="inlineStr">
         <is>
-          <t>GSA  -  Garderobe inkl. Dusche</t>
+          <t>SGR  -  Geräteraum</t>
         </is>
       </c>
       <c r="BY63" t="inlineStr">
@@ -13446,7 +13446,7 @@
         <v>1</v>
       </c>
       <c r="CA63" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="CB63" t="inlineStr">
         <is>
@@ -13460,32 +13460,32 @@
       </c>
       <c r="CD63" t="inlineStr">
         <is>
-          <t>1QH5Axl111J9SJj2E3W4w8</t>
+          <t>3VbCMl1_928hbAKPG5Knzn</t>
         </is>
       </c>
       <c r="CE63" t="n">
-        <v>3.421</v>
+        <v>4.12</v>
       </c>
       <c r="CF63" t="n">
-        <v>38.5011315279237</v>
+        <v>37.9925325891083</v>
       </c>
       <c r="CG63" t="n">
-        <v>41.894542</v>
+        <v>89.857005</v>
       </c>
       <c r="CH63" t="n">
-        <v>143.321228182</v>
+        <v>370.2108606</v>
       </c>
       <c r="CI63" t="inlineStr">
         <is>
-          <t>NNF</t>
+          <t>HNF</t>
         </is>
       </c>
       <c r="CJ63" t="inlineStr"/>
       <c r="CK63" t="n">
-        <v>7.2</v>
+        <v>4.1</v>
       </c>
       <c r="CL63" t="n">
-        <v>45</v>
+        <v>90</v>
       </c>
       <c r="CM63" t="inlineStr"/>
       <c r="CN63" t="inlineStr"/>
@@ -13494,14 +13494,14 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>1277</v>
+        <v>1253</v>
       </c>
       <c r="B64" t="n">
-        <v>1210</v>
+        <v>1186</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2qwEpCHpPBQhWqR0aH8a_c</t>
+          <t>3$MWY95kL37xnSaojxj3cW</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -13521,11 +13521,11 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>SPH:342964</t>
+          <t>SGR:342955</t>
         </is>
       </c>
       <c r="H64" t="n">
-        <v>1277</v>
+        <v>1253</v>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
@@ -13613,7 +13613,7 @@
       <c r="BR64" t="inlineStr"/>
       <c r="BS64" t="inlineStr">
         <is>
-          <t>SPH</t>
+          <t>SGR</t>
         </is>
       </c>
       <c r="BT64" t="inlineStr">
@@ -13628,17 +13628,17 @@
       </c>
       <c r="BV64" t="inlineStr">
         <is>
-          <t>Sporthalle</t>
+          <t>Geräteraum</t>
         </is>
       </c>
       <c r="BW64" t="inlineStr">
         <is>
-          <t>Einfachhalle 28 x 16 x 7m (frei bespielbare Höhe= 7m, Stauraum für Technik, Tragstruktur, Sportgeräte + ca. 1m)&amp;#10;</t>
+          <t>Diekt aus der zugehörigen Sporthalle, stufenlos zugänglich. Inkl. abschliessbarem Kleingeräteraum. Zu beachten: Mind. 6m Raumtiefe und 2.5m Höhe im Licht.</t>
         </is>
       </c>
       <c r="BX64" t="inlineStr">
         <is>
-          <t>SPH  -  Sporthalle</t>
+          <t>SGR  -  Geräteraum</t>
         </is>
       </c>
       <c r="BY64" t="inlineStr">
@@ -13664,20 +13664,20 @@
       </c>
       <c r="CD64" t="inlineStr">
         <is>
-          <t>0b93QOWH141xpbKCpGErNp</t>
+          <t>0b93QOWH141xpbKCpGErNi</t>
         </is>
       </c>
       <c r="CE64" t="n">
-        <v>7.85999999999999</v>
+        <v>3.982</v>
       </c>
       <c r="CF64" t="n">
-        <v>89.09855519173711</v>
+        <v>41.7997852969898</v>
       </c>
       <c r="CG64" t="n">
-        <v>463.384951</v>
+        <v>89.581008</v>
       </c>
       <c r="CH64" t="n">
-        <v>3642.20571486</v>
+        <v>356.711573856</v>
       </c>
       <c r="CI64" t="inlineStr">
         <is>
@@ -13686,34 +13686,26 @@
       </c>
       <c r="CJ64" t="inlineStr"/>
       <c r="CK64" t="n">
-        <v>5.5</v>
+        <v>4.1</v>
       </c>
       <c r="CL64" t="n">
-        <v>448</v>
-      </c>
-      <c r="CM64" t="n">
-        <v>7</v>
-      </c>
-      <c r="CN64" t="n">
-        <v>8</v>
-      </c>
-      <c r="CO64" t="n">
-        <v>28</v>
-      </c>
-      <c r="CP64" t="n">
-        <v>16</v>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="CM64" t="inlineStr"/>
+      <c r="CN64" t="inlineStr"/>
+      <c r="CO64" t="inlineStr"/>
+      <c r="CP64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>1278</v>
+        <v>1254</v>
       </c>
       <c r="B65" t="n">
-        <v>1207</v>
+        <v>1183</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>1OOeb7pNP5YhVqjcacSVQj</t>
+          <t>0SfLsfaY1DQQexHNkqpPq8</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13733,11 +13725,11 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>SGR:340482</t>
+          <t>HRR:340470</t>
         </is>
       </c>
       <c r="H65" t="n">
-        <v>1278</v>
+        <v>1254</v>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
@@ -13825,32 +13817,32 @@
       <c r="BR65" t="inlineStr"/>
       <c r="BS65" t="inlineStr">
         <is>
-          <t>SGR</t>
+          <t>HRR</t>
         </is>
       </c>
       <c r="BT65" t="inlineStr">
         <is>
-          <t>Sportbereich</t>
+          <t>Hausdienst</t>
         </is>
       </c>
       <c r="BU65" t="inlineStr">
         <is>
-          <t>Sporthallen</t>
+          <t>Hausdienst</t>
         </is>
       </c>
       <c r="BV65" t="inlineStr">
         <is>
-          <t>Geräteraum</t>
+          <t>Hauptreinigungsraum</t>
         </is>
       </c>
       <c r="BW65" t="inlineStr">
         <is>
-          <t>Diekt aus der zugehörigen Sporthalle, stufenlos zugänglich. Inkl. abschliessbarem Kleingeräteraum. Zu beachten: Mind. 6m Raumtiefe und 2.5m Höhe im Licht.</t>
+          <t>1 pro Gebäude/Trakt, im UG, Lager, Kaltwasseranschluss und Ausgusslavabo, Bodenablauf (Im Geschoss des HRR kein RRG)&amp;#10;</t>
         </is>
       </c>
       <c r="BX65" t="inlineStr">
         <is>
-          <t>SGR  -  Geräteraum</t>
+          <t>HRR  -  Hauptreinigungsraum</t>
         </is>
       </c>
       <c r="BY65" t="inlineStr">
@@ -13862,7 +13854,7 @@
         <v>1</v>
       </c>
       <c r="CA65" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CB65" t="inlineStr">
         <is>
@@ -13876,32 +13868,32 @@
       </c>
       <c r="CD65" t="inlineStr">
         <is>
-          <t>3VbCMl1_928hbAKPG5Knzn</t>
+          <t>3VbCMl1_928hbAKPG5Kno5</t>
         </is>
       </c>
       <c r="CE65" t="n">
-        <v>4.121</v>
+        <v>4.12000209952917</v>
       </c>
       <c r="CF65" t="n">
-        <v>37.9925325891083</v>
+        <v>25.4721434358016</v>
       </c>
       <c r="CG65" t="n">
-        <v>89.857005</v>
+        <v>24.251362</v>
       </c>
       <c r="CH65" t="n">
-        <v>370.300717605</v>
+        <v>99.9156623564419</v>
       </c>
       <c r="CI65" t="inlineStr">
         <is>
-          <t>HNF</t>
+          <t>NNF</t>
         </is>
       </c>
       <c r="CJ65" t="inlineStr"/>
       <c r="CK65" t="n">
-        <v>4.1</v>
+        <v>7.1</v>
       </c>
       <c r="CL65" t="n">
-        <v>90</v>
+        <v>25</v>
       </c>
       <c r="CM65" t="inlineStr"/>
       <c r="CN65" t="inlineStr"/>
@@ -13910,14 +13902,14 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>1279</v>
+        <v>1255</v>
       </c>
       <c r="B66" t="n">
-        <v>1207</v>
+        <v>1183</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>0kB0A2S5z5auQg3$i3qAjO</t>
+          <t>2jQqxIN7D0G9XrN3psKCHB</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13937,11 +13929,11 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>HRR:340470</t>
+          <t>GRP:340476</t>
         </is>
       </c>
       <c r="H66" t="n">
-        <v>1279</v>
+        <v>1255</v>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
@@ -14029,7 +14021,7 @@
       <c r="BR66" t="inlineStr"/>
       <c r="BS66" t="inlineStr">
         <is>
-          <t>HRR</t>
+          <t>GRP</t>
         </is>
       </c>
       <c r="BT66" t="inlineStr">
@@ -14044,17 +14036,17 @@
       </c>
       <c r="BV66" t="inlineStr">
         <is>
-          <t>Hauptreinigungsraum</t>
+          <t>Garderobe / Personalraum</t>
         </is>
       </c>
       <c r="BW66" t="inlineStr">
         <is>
-          <t>1 pro Gebäude/Trakt, im UG, Lager, Kaltwasseranschluss und Ausgusslavabo, Bodenablauf (Im Geschoss des HRR kein RRG)&amp;#10;</t>
+          <t>Spinden + Umkleidekabinen</t>
         </is>
       </c>
       <c r="BX66" t="inlineStr">
         <is>
-          <t>HRR  -  Hauptreinigungsraum</t>
+          <t>GRP  -  Garderobe / Personalraum</t>
         </is>
       </c>
       <c r="BY66" t="inlineStr">
@@ -14080,20 +14072,20 @@
       </c>
       <c r="CD66" t="inlineStr">
         <is>
-          <t>3VbCMl1_928hbAKPG5Kno5</t>
+          <t>3VbCMl1_928hbAKPG5KnoF</t>
         </is>
       </c>
       <c r="CE66" t="n">
-        <v>4.121</v>
+        <v>4.12</v>
       </c>
       <c r="CF66" t="n">
-        <v>25.4703597146799</v>
+        <v>13.5853049126557</v>
       </c>
       <c r="CG66" t="n">
-        <v>24.194584</v>
+        <v>11.5049595</v>
       </c>
       <c r="CH66" t="n">
-        <v>99.70588066400001</v>
+        <v>47.40043314</v>
       </c>
       <c r="CI66" t="inlineStr">
         <is>
@@ -14102,10 +14094,10 @@
       </c>
       <c r="CJ66" t="inlineStr"/>
       <c r="CK66" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="CL66" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="CM66" t="inlineStr"/>
       <c r="CN66" t="inlineStr"/>
@@ -14114,14 +14106,14 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>1280</v>
+        <v>1256</v>
       </c>
       <c r="B67" t="n">
-        <v>1207</v>
+        <v>1185</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>21ftMaN2H3x9V_1Iuv7_Lz</t>
+          <t>1elxkk8h12l8VI66SES48s</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -14141,11 +14133,11 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>GRP:340476</t>
+          <t>CON:342808</t>
         </is>
       </c>
       <c r="H67" t="n">
-        <v>1280</v>
+        <v>1256</v>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr"/>
@@ -14173,11 +14165,11 @@
       <c r="AB67" t="inlineStr"/>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>UG2</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="AD67" t="n">
-        <v>-8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AE67" t="inlineStr"/>
       <c r="AF67" t="inlineStr"/>
@@ -14233,7 +14225,7 @@
       <c r="BR67" t="inlineStr"/>
       <c r="BS67" t="inlineStr">
         <is>
-          <t>GRP</t>
+          <t>CON</t>
         </is>
       </c>
       <c r="BT67" t="inlineStr">
@@ -14248,17 +14240,17 @@
       </c>
       <c r="BV67" t="inlineStr">
         <is>
-          <t>Garderobe / Personalraum</t>
+          <t xml:space="preserve">Containerraum </t>
         </is>
       </c>
       <c r="BW67" t="inlineStr">
         <is>
-          <t>Spinden + Umkleidekabinen</t>
+          <t>Container: 0.8 x 1.25 m, 800L Inhalt, Zugang direkt von Aussen</t>
         </is>
       </c>
       <c r="BX67" t="inlineStr">
         <is>
-          <t>GRP  -  Garderobe / Personalraum</t>
+          <t xml:space="preserve">CON  -  Containerraum </t>
         </is>
       </c>
       <c r="BY67" t="inlineStr">
@@ -14284,20 +14276,20 @@
       </c>
       <c r="CD67" t="inlineStr">
         <is>
-          <t>3VbCMl1_928hbAKPG5KnoF</t>
+          <t>3$FY_ljDfBsweJfZwnfjOv</t>
         </is>
       </c>
       <c r="CE67" t="n">
-        <v>4.121</v>
+        <v>3</v>
       </c>
       <c r="CF67" t="n">
-        <v>13.5853049126557</v>
+        <v>13.3093771618808</v>
       </c>
       <c r="CG67" t="n">
-        <v>11.5049595</v>
+        <v>11.070615</v>
       </c>
       <c r="CH67" t="n">
-        <v>47.4119380995</v>
+        <v>33.211845</v>
       </c>
       <c r="CI67" t="inlineStr">
         <is>
@@ -14306,7 +14298,7 @@
       </c>
       <c r="CJ67" t="inlineStr"/>
       <c r="CK67" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="CL67" t="n">
         <v>12</v>
@@ -14318,14 +14310,14 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>1281</v>
+        <v>1257</v>
       </c>
       <c r="B68" t="n">
-        <v>1209</v>
+        <v>1183</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2rnYpcA2j5ORd2uupGEvG0</t>
+          <t>1mK10My2H1Jf6TH2FFyNJl</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -14345,11 +14337,11 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>CON:342808</t>
+          <t>SPH:340222</t>
         </is>
       </c>
       <c r="H68" t="n">
-        <v>1281</v>
+        <v>1257</v>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr"/>
@@ -14377,11 +14369,11 @@
       <c r="AB68" t="inlineStr"/>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>UG2</t>
         </is>
       </c>
       <c r="AD68" t="n">
-        <v>0</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="AE68" t="inlineStr"/>
       <c r="AF68" t="inlineStr"/>
@@ -14437,32 +14429,32 @@
       <c r="BR68" t="inlineStr"/>
       <c r="BS68" t="inlineStr">
         <is>
-          <t>CON</t>
+          <t>SPH</t>
         </is>
       </c>
       <c r="BT68" t="inlineStr">
         <is>
-          <t>Hausdienst</t>
+          <t>Sportbereich</t>
         </is>
       </c>
       <c r="BU68" t="inlineStr">
         <is>
-          <t>Hausdienst</t>
+          <t>Sporthallen</t>
         </is>
       </c>
       <c r="BV68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Containerraum </t>
+          <t>Sporthalle</t>
         </is>
       </c>
       <c r="BW68" t="inlineStr">
         <is>
-          <t>Container: 0.8 x 1.25 m, 800L Inhalt, Zugang direkt von Aussen</t>
+          <t>Einfachhalle 28 x 16 x 7m (frei bespielbare Höhe= 7m, Stauraum für Technik, Tragstruktur, Sportgeräte + ca. 1m)&amp;#10;</t>
         </is>
       </c>
       <c r="BX68" t="inlineStr">
         <is>
-          <t xml:space="preserve">CON  -  Containerraum </t>
+          <t>SPH  -  Sporthalle</t>
         </is>
       </c>
       <c r="BY68" t="inlineStr">
@@ -14474,7 +14466,7 @@
         <v>1</v>
       </c>
       <c r="CA68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CB68" t="inlineStr">
         <is>
@@ -14488,48 +14480,56 @@
       </c>
       <c r="CD68" t="inlineStr">
         <is>
-          <t>3$FY_ljDfBsweJfZwnfjOv</t>
+          <t>27eKs3mJf3tucFrDswOcPu</t>
         </is>
       </c>
       <c r="CE68" t="n">
-        <v>3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CF68" t="n">
-        <v>13.3093771618808</v>
+        <v>89.0980990398666</v>
       </c>
       <c r="CG68" t="n">
-        <v>11.070615</v>
+        <v>463.376039</v>
       </c>
       <c r="CH68" t="n">
-        <v>33.211845</v>
+        <v>3799.6835198</v>
       </c>
       <c r="CI68" t="inlineStr">
         <is>
-          <t>NNF</t>
+          <t>HNF</t>
         </is>
       </c>
       <c r="CJ68" t="inlineStr"/>
       <c r="CK68" t="n">
-        <v>7.3</v>
+        <v>5.5</v>
       </c>
       <c r="CL68" t="n">
-        <v>12</v>
-      </c>
-      <c r="CM68" t="inlineStr"/>
-      <c r="CN68" t="inlineStr"/>
-      <c r="CO68" t="inlineStr"/>
-      <c r="CP68" t="inlineStr"/>
+        <v>448</v>
+      </c>
+      <c r="CM68" t="n">
+        <v>7</v>
+      </c>
+      <c r="CN68" t="n">
+        <v>8</v>
+      </c>
+      <c r="CO68" t="n">
+        <v>28</v>
+      </c>
+      <c r="CP68" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>1282</v>
+        <v>1258</v>
       </c>
       <c r="B69" t="n">
-        <v>1207</v>
+        <v>1186</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>3fqw08GKT8VB$WT6lvspWB</t>
+          <t>0v8vKsFUHEhuGCI94TqyuL</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -14549,11 +14549,11 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>SPH:340222</t>
+          <t>SPH:342964</t>
         </is>
       </c>
       <c r="H69" t="n">
-        <v>1282</v>
+        <v>1258</v>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr"/>
@@ -14581,11 +14581,11 @@
       <c r="AB69" t="inlineStr"/>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>UG2</t>
+          <t>OG1</t>
         </is>
       </c>
       <c r="AD69" t="n">
-        <v>-8.199999999999999</v>
+        <v>2.998</v>
       </c>
       <c r="AE69" t="inlineStr"/>
       <c r="AF69" t="inlineStr"/>
@@ -14692,20 +14692,20 @@
       </c>
       <c r="CD69" t="inlineStr">
         <is>
-          <t>27eKs3mJf3tucFrDswOcPu</t>
+          <t>0b93QOWH141xpbKCpGErNp</t>
         </is>
       </c>
       <c r="CE69" t="n">
-        <v>8.199999999999999</v>
+        <v>7.85999999999999</v>
       </c>
       <c r="CF69" t="n">
-        <v>89.0980990398666</v>
+        <v>89.09855519173711</v>
       </c>
       <c r="CG69" t="n">
-        <v>463.376039</v>
+        <v>463.384951</v>
       </c>
       <c r="CH69" t="n">
-        <v>3799.6835198</v>
+        <v>3642.20571486</v>
       </c>
       <c r="CI69" t="inlineStr">
         <is>
@@ -14734,14 +14734,14 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>1283</v>
+        <v>1259</v>
       </c>
       <c r="B70" t="n">
-        <v>1208</v>
+        <v>1184</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>3fS1w73ELCBRUIqHWvP3$z</t>
+          <t>25qvKAslv4su4AGnfPnQAy</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14765,7 +14765,7 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>1283</v>
+        <v>1259</v>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr"/>
@@ -14908,16 +14908,16 @@
         </is>
       </c>
       <c r="CE70" t="n">
-        <v>3.421</v>
+        <v>3.42000189301365</v>
       </c>
       <c r="CF70" t="n">
-        <v>9.480715967371051</v>
+        <v>9.600782029985609</v>
       </c>
       <c r="CG70" t="n">
-        <v>3.582502</v>
+        <v>3.639574</v>
       </c>
       <c r="CH70" t="n">
-        <v>12.255739342</v>
+        <v>12.4473499697633</v>
       </c>
       <c r="CI70" t="inlineStr">
         <is>
@@ -14938,14 +14938,14 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>1284</v>
+        <v>1260</v>
       </c>
       <c r="B71" t="n">
-        <v>1211</v>
+        <v>1187</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2FQ8B6_JP08wqgDmUUSwZn</t>
+          <t>0$R0qHln98kepMxkmwzDXO</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14969,7 +14969,7 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>1284</v>
+        <v>1260</v>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr"/>
@@ -15001,7 +15001,7 @@
         </is>
       </c>
       <c r="AD71" t="n">
-        <v>7.939</v>
+        <v>7.94</v>
       </c>
       <c r="AE71" t="inlineStr"/>
       <c r="AF71" t="inlineStr"/>
@@ -15112,7 +15112,7 @@
         </is>
       </c>
       <c r="CE71" t="n">
-        <v>3.579</v>
+        <v>3.578</v>
       </c>
       <c r="CF71" t="n">
         <v>8.46504079502658</v>
@@ -15121,7 +15121,7 @@
         <v>4.3787245</v>
       </c>
       <c r="CH71" t="n">
-        <v>15.6714549855</v>
+        <v>15.667076261</v>
       </c>
       <c r="CI71" t="inlineStr">
         <is>
@@ -15142,14 +15142,14 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>1285</v>
+        <v>1261</v>
       </c>
       <c r="B72" t="n">
-        <v>1209</v>
+        <v>1185</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>1PXOCrKLD2ohK81bqcw5L8</t>
+          <t>1nHVq1BLj3N83VoxI$QAiV</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -15173,7 +15173,7 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>1285</v>
+        <v>1261</v>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr"/>
@@ -15342,14 +15342,14 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>1286</v>
+        <v>1262</v>
       </c>
       <c r="B73" t="n">
-        <v>1212</v>
+        <v>1188</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>3gQV9bpHv7NfVbjzlui7Lj</t>
+          <t>3865N6dr5D2QZmKnsV5UjA</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -15373,7 +15373,7 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>1286</v>
+        <v>1262</v>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr"/>
@@ -15405,7 +15405,7 @@
         </is>
       </c>
       <c r="AD73" t="n">
-        <v>11.947</v>
+        <v>11.948</v>
       </c>
       <c r="AE73" t="inlineStr"/>
       <c r="AF73" t="inlineStr"/>
@@ -15542,14 +15542,14 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>1287</v>
+        <v>1263</v>
       </c>
       <c r="B74" t="n">
-        <v>1212</v>
+        <v>1188</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>0x5OAt7GXB6Rq0gRG_tICL</t>
+          <t>2dCF9Z2NrCiPs79T_2XETx</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -15573,7 +15573,7 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>1287</v>
+        <v>1263</v>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr"/>
@@ -15605,7 +15605,7 @@
         </is>
       </c>
       <c r="AD74" t="n">
-        <v>11.947</v>
+        <v>11.948</v>
       </c>
       <c r="AE74" t="inlineStr"/>
       <c r="AF74" t="inlineStr"/>
@@ -15742,14 +15742,14 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>1288</v>
+        <v>1264</v>
       </c>
       <c r="B75" t="n">
-        <v>1211</v>
+        <v>1187</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>0CmilJIZr6B8RyG4QW7HcZ</t>
+          <t>2V_TDJQGX5u9IXI55MWQFM</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15773,7 +15773,7 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>1288</v>
+        <v>1264</v>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr"/>
@@ -15805,7 +15805,7 @@
         </is>
       </c>
       <c r="AD75" t="n">
-        <v>7.939</v>
+        <v>7.94</v>
       </c>
       <c r="AE75" t="inlineStr"/>
       <c r="AF75" t="inlineStr"/>
@@ -15912,7 +15912,7 @@
         </is>
       </c>
       <c r="CE75" t="n">
-        <v>3.579</v>
+        <v>3.578</v>
       </c>
       <c r="CF75" t="n">
         <v>29.9183857421605</v>
@@ -15921,7 +15921,7 @@
         <v>51.768942</v>
       </c>
       <c r="CH75" t="n">
-        <v>185.281043418</v>
+        <v>185.229274476</v>
       </c>
       <c r="CI75" t="inlineStr">
         <is>
@@ -15942,14 +15942,14 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>1289</v>
+        <v>1265</v>
       </c>
       <c r="B76" t="n">
-        <v>1211</v>
+        <v>1187</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>0mgHCA5Bj2q8PGPshAJwdu</t>
+          <t>2EdAa2vnvDwv$K313aI9nH</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15973,7 +15973,7 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>1289</v>
+        <v>1265</v>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr"/>
@@ -16005,7 +16005,7 @@
         </is>
       </c>
       <c r="AD76" t="n">
-        <v>7.939</v>
+        <v>7.94</v>
       </c>
       <c r="AE76" t="inlineStr"/>
       <c r="AF76" t="inlineStr"/>
@@ -16112,7 +16112,7 @@
         </is>
       </c>
       <c r="CE76" t="n">
-        <v>3.579</v>
+        <v>3.578</v>
       </c>
       <c r="CF76" t="n">
         <v>16.922049437983</v>
@@ -16121,7 +16121,7 @@
         <v>17.5731125</v>
       </c>
       <c r="CH76" t="n">
-        <v>62.8941696375</v>
+        <v>62.876596525</v>
       </c>
       <c r="CI76" t="inlineStr">
         <is>
@@ -16142,14 +16142,14 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>1290</v>
+        <v>1266</v>
       </c>
       <c r="B77" t="n">
-        <v>1212</v>
+        <v>1188</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>3542EqJCz3j9Eu7i7LwKQI</t>
+          <t>2RQb_YuIX0cupTG8njrqa5</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -16173,7 +16173,7 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>1290</v>
+        <v>1266</v>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr"/>
@@ -16205,7 +16205,7 @@
         </is>
       </c>
       <c r="AD77" t="n">
-        <v>11.947</v>
+        <v>11.948</v>
       </c>
       <c r="AE77" t="inlineStr"/>
       <c r="AF77" t="inlineStr"/>
@@ -16342,14 +16342,14 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>1291</v>
+        <v>1267</v>
       </c>
       <c r="B78" t="n">
-        <v>1209</v>
+        <v>1185</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>37pvr1fmPFoPR8VqDaFSaH</t>
+          <t>1xAkayK$92b8rEYvsI7ddA</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -16373,7 +16373,7 @@
         </is>
       </c>
       <c r="H78" t="n">
-        <v>1291</v>
+        <v>1267</v>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr"/>
@@ -16548,14 +16548,14 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>1292</v>
+        <v>1268</v>
       </c>
       <c r="B79" t="n">
-        <v>1209</v>
+        <v>1185</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2q$FhMpurDpQLxyHcG7QMH</t>
+          <t>0snplPWT179OZgXqJkFdam</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -16579,7 +16579,7 @@
         </is>
       </c>
       <c r="H79" t="n">
-        <v>1292</v>
+        <v>1268</v>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr"/>
@@ -16752,14 +16752,14 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>1293</v>
+        <v>1269</v>
       </c>
       <c r="B80" t="n">
-        <v>1209</v>
+        <v>1185</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>15q5B8t2H1jOLW$YLJTSCd</t>
+          <t>3QuKuIVNvEDebBjhENRHdp</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16783,7 +16783,7 @@
         </is>
       </c>
       <c r="H80" t="n">
-        <v>1293</v>
+        <v>1269</v>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr"/>
@@ -16956,14 +16956,14 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>1294</v>
+        <v>1270</v>
       </c>
       <c r="B81" t="n">
-        <v>1209</v>
+        <v>1185</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>0lrhQ1hBL3UB9wu$bziAIW</t>
+          <t>1PFX2sV$1EtwB4cgbdYiiR</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16987,7 +16987,7 @@
         </is>
       </c>
       <c r="H81" t="n">
-        <v>1294</v>
+        <v>1270</v>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr"/>
@@ -17156,14 +17156,14 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>1295</v>
+        <v>1271</v>
       </c>
       <c r="B82" t="n">
-        <v>1208</v>
+        <v>1184</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>1K1FlaQx1EExBCUKfCbQFS</t>
+          <t>2TkX3v9lLDHfNhAwV_173q</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -17187,7 +17187,7 @@
         </is>
       </c>
       <c r="H82" t="n">
-        <v>1295</v>
+        <v>1271</v>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr"/>
@@ -17330,7 +17330,7 @@
         </is>
       </c>
       <c r="CE82" t="n">
-        <v>3.421</v>
+        <v>3.42</v>
       </c>
       <c r="CF82" t="n">
         <v>7.37292153872654</v>
@@ -17339,7 +17339,7 @@
         <v>2.719245</v>
       </c>
       <c r="CH82" t="n">
-        <v>9.302537145000001</v>
+        <v>9.299817900000001</v>
       </c>
       <c r="CI82" t="inlineStr">
         <is>
@@ -17360,14 +17360,14 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>1296</v>
+        <v>1272</v>
       </c>
       <c r="B83" t="n">
-        <v>1208</v>
+        <v>1184</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2VOStX3MjEzAywBgrc2Ymz</t>
+          <t>2b761ZbMf7OQyYTjBYwlqS</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -17391,7 +17391,7 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>1296</v>
+        <v>1272</v>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr"/>
@@ -17534,7 +17534,7 @@
         </is>
       </c>
       <c r="CE83" t="n">
-        <v>3.421</v>
+        <v>3.42</v>
       </c>
       <c r="CF83" t="n">
         <v>7.50486180797826</v>
@@ -17543,7 +17543,7 @@
         <v>2.8944635</v>
       </c>
       <c r="CH83" t="n">
-        <v>9.901959633500001</v>
+        <v>9.89906517</v>
       </c>
       <c r="CI83" t="inlineStr">
         <is>
@@ -17564,14 +17564,14 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>1297</v>
+        <v>1273</v>
       </c>
       <c r="B84" t="n">
-        <v>1209</v>
+        <v>1185</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>1nbtU4bcH2MeFbv04K7ZN2</t>
+          <t>3th3YBjLPEbgeAFO8BnVLM</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -17595,7 +17595,7 @@
         </is>
       </c>
       <c r="H84" t="n">
-        <v>1297</v>
+        <v>1273</v>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr"/>
@@ -17770,14 +17770,14 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>1298</v>
+        <v>1274</v>
       </c>
       <c r="B85" t="n">
-        <v>1209</v>
+        <v>1185</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>1H1NJxt1P4dhBGOFdbv$N4</t>
+          <t>3V04x_Gn9CsOd3mf5kjSS7</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17801,7 +17801,7 @@
         </is>
       </c>
       <c r="H85" t="n">
-        <v>1298</v>
+        <v>1274</v>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr"/>
@@ -17974,14 +17974,14 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>1299</v>
+        <v>1275</v>
       </c>
       <c r="B86" t="n">
-        <v>1212</v>
+        <v>1188</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>1xCUaRipzEBRjcRGOUa__w</t>
+          <t>0ydbChVXH5YeiOECwP0lP5</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -18005,7 +18005,7 @@
         </is>
       </c>
       <c r="H86" t="n">
-        <v>1299</v>
+        <v>1275</v>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr"/>
@@ -18037,7 +18037,7 @@
         </is>
       </c>
       <c r="AD86" t="n">
-        <v>11.947</v>
+        <v>11.948</v>
       </c>
       <c r="AE86" t="inlineStr"/>
       <c r="AF86" t="inlineStr"/>
@@ -18178,14 +18178,14 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>1300</v>
+        <v>1276</v>
       </c>
       <c r="B87" t="n">
-        <v>1209</v>
+        <v>1185</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>0x9I5spTf0W8z7GhPCk1ky</t>
+          <t>3tE0xz5ivFbule77FUWYT7</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -18209,7 +18209,7 @@
         </is>
       </c>
       <c r="H87" t="n">
-        <v>1300</v>
+        <v>1276</v>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr"/>
@@ -18351,13 +18351,13 @@
         <v>3</v>
       </c>
       <c r="CF87" t="n">
-        <v>70.77332838583099</v>
+        <v>70.7806751860665</v>
       </c>
       <c r="CG87" t="n">
-        <v>123.877062</v>
+        <v>123.8381265</v>
       </c>
       <c r="CH87" t="n">
-        <v>371.631186</v>
+        <v>371.5143795</v>
       </c>
       <c r="CI87" t="inlineStr">
         <is>
@@ -18378,14 +18378,14 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>1301</v>
+        <v>1277</v>
       </c>
       <c r="B88" t="n">
-        <v>1208</v>
+        <v>1184</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2goFLwB6DCTwDTgbAWEEIH</t>
+          <t>2gsiWFr2TB1AHTbv7ojX6m</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -18409,7 +18409,7 @@
         </is>
       </c>
       <c r="H88" t="n">
-        <v>1301</v>
+        <v>1277</v>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr"/>
@@ -18552,7 +18552,7 @@
         </is>
       </c>
       <c r="CE88" t="n">
-        <v>3.421</v>
+        <v>3.42</v>
       </c>
       <c r="CF88" t="n">
         <v>14.8495146387802</v>
@@ -18561,7 +18561,7 @@
         <v>9.246236</v>
       </c>
       <c r="CH88" t="n">
-        <v>31.631373356</v>
+        <v>31.62212712</v>
       </c>
       <c r="CI88" t="inlineStr">
         <is>
@@ -18582,14 +18582,14 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>1302</v>
+        <v>1278</v>
       </c>
       <c r="B89" t="n">
-        <v>1211</v>
+        <v>1187</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>0d65XwDRr8KPZICzeqHSW5</t>
+          <t>3jgApaggT6VOj2drGLqhV$</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -18613,7 +18613,7 @@
         </is>
       </c>
       <c r="H89" t="n">
-        <v>1302</v>
+        <v>1278</v>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr"/>
@@ -18645,7 +18645,7 @@
         </is>
       </c>
       <c r="AD89" t="n">
-        <v>7.939</v>
+        <v>7.94</v>
       </c>
       <c r="AE89" t="inlineStr"/>
       <c r="AF89" t="inlineStr"/>
@@ -18756,7 +18756,7 @@
         </is>
       </c>
       <c r="CE89" t="n">
-        <v>3.579</v>
+        <v>3.578</v>
       </c>
       <c r="CF89" t="n">
         <v>10.1779200252527</v>
@@ -18765,7 +18765,7 @@
         <v>6.381486</v>
       </c>
       <c r="CH89" t="n">
-        <v>22.839338394</v>
+        <v>22.832956908</v>
       </c>
       <c r="CI89" t="inlineStr">
         <is>
@@ -18786,14 +18786,14 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>1303</v>
+        <v>1279</v>
       </c>
       <c r="B90" t="n">
-        <v>1208</v>
+        <v>1184</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>0WJ65NDaH54RWZcOZo2hFz</t>
+          <t>0L$CPopvL2ng78uaCkxmd2</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18817,7 +18817,7 @@
         </is>
       </c>
       <c r="H90" t="n">
-        <v>1303</v>
+        <v>1279</v>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr"/>
@@ -18960,7 +18960,7 @@
         </is>
       </c>
       <c r="CE90" t="n">
-        <v>3.421</v>
+        <v>3.42</v>
       </c>
       <c r="CF90" t="n">
         <v>16.1398401474132</v>
@@ -18969,7 +18969,7 @@
         <v>11.0386675</v>
       </c>
       <c r="CH90" t="n">
-        <v>37.7632815175</v>
+        <v>37.75224285</v>
       </c>
       <c r="CI90" t="inlineStr">
         <is>
@@ -18990,14 +18990,14 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>1304</v>
+        <v>1280</v>
       </c>
       <c r="B91" t="n">
-        <v>1211</v>
+        <v>1187</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>0DQARhKmnCX83BGrsfeEgq</t>
+          <t>2R0Ko1_rT45gQWRWnSw8Rh</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -19021,7 +19021,7 @@
         </is>
       </c>
       <c r="H91" t="n">
-        <v>1304</v>
+        <v>1280</v>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr"/>
@@ -19053,7 +19053,7 @@
         </is>
       </c>
       <c r="AD91" t="n">
-        <v>7.939</v>
+        <v>7.94</v>
       </c>
       <c r="AE91" t="inlineStr"/>
       <c r="AF91" t="inlineStr"/>
@@ -19164,7 +19164,7 @@
         </is>
       </c>
       <c r="CE91" t="n">
-        <v>3.579</v>
+        <v>3.578</v>
       </c>
       <c r="CF91" t="n">
         <v>8.90153516286427</v>
@@ -19173,7 +19173,7 @@
         <v>4.561436</v>
       </c>
       <c r="CH91" t="n">
-        <v>16.325379444</v>
+        <v>16.320818008</v>
       </c>
       <c r="CI91" t="inlineStr">
         <is>
@@ -19194,14 +19194,14 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>1305</v>
+        <v>1281</v>
       </c>
       <c r="B92" t="n">
-        <v>1209</v>
+        <v>1185</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2jn0CO4WT6agpI_e3theVz</t>
+          <t>30_jhjUID1lOEnoZkbwPlR</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -19225,7 +19225,7 @@
         </is>
       </c>
       <c r="H92" t="n">
-        <v>1305</v>
+        <v>1281</v>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr"/>
@@ -19398,14 +19398,14 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>1306</v>
+        <v>1282</v>
       </c>
       <c r="B93" t="n">
-        <v>1209</v>
+        <v>1185</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>0R6CzIVUf9Xg$xY9ZGMPOI</t>
+          <t>3v_If9$uz3fwzdtVKMHQ8o</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -19429,7 +19429,7 @@
         </is>
       </c>
       <c r="H93" t="n">
-        <v>1306</v>
+        <v>1282</v>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr"/>
@@ -19598,14 +19598,14 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>1307</v>
+        <v>1283</v>
       </c>
       <c r="B94" t="n">
-        <v>1207</v>
+        <v>1183</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2h61zMFo5AJAPRusVng_Xn</t>
+          <t>2g7lHgM9fCfeWFLbqCROTN</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -19629,7 +19629,7 @@
         </is>
       </c>
       <c r="H94" t="n">
-        <v>1307</v>
+        <v>1283</v>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="J94" t="inlineStr"/>
@@ -19739,13 +19739,13 @@
         <v>4.42</v>
       </c>
       <c r="CF94" t="n">
-        <v>123.779783200545</v>
+        <v>123.77898440477</v>
       </c>
       <c r="CG94" t="n">
-        <v>946.7568455000001</v>
+        <v>946.7966155</v>
       </c>
       <c r="CH94" t="n">
-        <v>4184.66525711</v>
+        <v>4184.84104051</v>
       </c>
       <c r="CI94" t="inlineStr"/>
       <c r="CJ94" t="inlineStr"/>
@@ -19758,14 +19758,14 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>1308</v>
+        <v>1284</v>
       </c>
       <c r="B95" t="n">
-        <v>1207</v>
+        <v>1183</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>1ocReKPMH6yQHek4DHBHWe</t>
+          <t>2TjpIVE3fEjf2yeWwF5tbt</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19789,7 +19789,7 @@
         </is>
       </c>
       <c r="H95" t="n">
-        <v>1308</v>
+        <v>1284</v>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="J95" t="inlineStr"/>
@@ -19899,13 +19899,13 @@
         <v>0.5</v>
       </c>
       <c r="CF95" t="n">
-        <v>96.22017162882391</v>
+        <v>96.1953347530367</v>
       </c>
       <c r="CG95" t="n">
-        <v>946.748385</v>
+        <v>946.779711</v>
       </c>
       <c r="CH95" t="n">
-        <v>473.3741925</v>
+        <v>473.3898555</v>
       </c>
       <c r="CI95" t="inlineStr"/>
       <c r="CJ95" t="inlineStr"/>
@@ -19918,14 +19918,14 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>1309</v>
+        <v>1285</v>
       </c>
       <c r="B96" t="n">
-        <v>1207</v>
+        <v>1183</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>220mi7GG59YuA9V0nhWv8f</t>
+          <t>11rtg$OHHCQgjPenPfbWHc</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19949,7 +19949,7 @@
         </is>
       </c>
       <c r="H96" t="n">
-        <v>1309</v>
+        <v>1285</v>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="J96" t="inlineStr"/>
@@ -20059,13 +20059,13 @@
         <v>1</v>
       </c>
       <c r="CF96" t="n">
-        <v>123.779783200545</v>
+        <v>123.77898440477</v>
       </c>
       <c r="CG96" t="n">
-        <v>946.7568455000001</v>
+        <v>946.7966155</v>
       </c>
       <c r="CH96" t="n">
-        <v>946.7568455000001</v>
+        <v>946.7966155</v>
       </c>
       <c r="CI96" t="inlineStr"/>
       <c r="CJ96" t="inlineStr"/>
@@ -20078,14 +20078,14 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>1310</v>
+        <v>1286</v>
       </c>
       <c r="B97" t="n">
-        <v>1208</v>
+        <v>1184</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>1WVo1W$JrFBwJk1Ud33P2_</t>
+          <t>37U7QqRiD3K8YpI0EDvqEG</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -20109,7 +20109,7 @@
         </is>
       </c>
       <c r="H97" t="n">
-        <v>1310</v>
+        <v>1286</v>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="J97" t="inlineStr"/>
@@ -20219,13 +20219,13 @@
         <v>3.78</v>
       </c>
       <c r="CF97" t="n">
-        <v>126.058990957543</v>
+        <v>126.05717405587</v>
       </c>
       <c r="CG97" t="n">
-        <v>944.3010395</v>
+        <v>944.3288025000001</v>
       </c>
       <c r="CH97" t="n">
-        <v>3569.45792931</v>
+        <v>3569.56287345</v>
       </c>
       <c r="CI97" t="inlineStr"/>
       <c r="CJ97" t="inlineStr"/>
@@ -20238,14 +20238,14 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>1311</v>
+        <v>1287</v>
       </c>
       <c r="B98" t="n">
-        <v>1208</v>
+        <v>1184</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>1CV6oaRyn1HQP8tN4myNln</t>
+          <t>1IKxMLTg96xBLZwOLJkOep</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -20269,7 +20269,7 @@
         </is>
       </c>
       <c r="H98" t="n">
-        <v>1311</v>
+        <v>1287</v>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="J98" t="inlineStr"/>
@@ -20379,13 +20379,13 @@
         <v>1</v>
       </c>
       <c r="CF98" t="n">
-        <v>126.058990957543</v>
+        <v>126.05717405587</v>
       </c>
       <c r="CG98" t="n">
-        <v>944.3010395</v>
+        <v>944.3288025000001</v>
       </c>
       <c r="CH98" t="n">
-        <v>944.3010395</v>
+        <v>944.3288025000001</v>
       </c>
       <c r="CI98" t="inlineStr"/>
       <c r="CJ98" t="inlineStr"/>
@@ -20398,14 +20398,14 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>1312</v>
+        <v>1288</v>
       </c>
       <c r="B99" t="n">
-        <v>1209</v>
+        <v>1185</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>3S19U$d1v2EAwMe1MFmPkg</t>
+          <t>1CcwMqeXT8UesKx8nLd6OD</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -20429,7 +20429,7 @@
         </is>
       </c>
       <c r="H99" t="n">
-        <v>1312</v>
+        <v>1288</v>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="J99" t="inlineStr"/>
@@ -20547,13 +20547,13 @@
         <v>1</v>
       </c>
       <c r="CF99" t="n">
-        <v>10.4510384173057</v>
+        <v>11.5343811888718</v>
       </c>
       <c r="CG99" t="n">
-        <v>6.8265125</v>
+        <v>10.45073</v>
       </c>
       <c r="CH99" t="n">
-        <v>6.8265125</v>
+        <v>10.45073</v>
       </c>
       <c r="CI99" t="inlineStr"/>
       <c r="CJ99" t="inlineStr"/>
@@ -20566,14 +20566,14 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>1313</v>
+        <v>1289</v>
       </c>
       <c r="B100" t="n">
-        <v>1209</v>
+        <v>1185</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>1dO_bQkdz9nwDyTkTE7ib2</t>
+          <t>0XnoVHZ5b7YeZWNQ2bXPFm</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20597,7 +20597,7 @@
         </is>
       </c>
       <c r="H100" t="n">
-        <v>1313</v>
+        <v>1289</v>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="J100" t="inlineStr"/>
@@ -20715,13 +20715,13 @@
         <v>1</v>
       </c>
       <c r="CF100" t="n">
-        <v>22.0715375602572</v>
+        <v>22.1434378257397</v>
       </c>
       <c r="CG100" t="n">
-        <v>16.361301</v>
+        <v>17.082447</v>
       </c>
       <c r="CH100" t="n">
-        <v>16.361301</v>
+        <v>17.082447</v>
       </c>
       <c r="CI100" t="inlineStr"/>
       <c r="CJ100" t="inlineStr"/>
@@ -20734,14 +20734,14 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>1314</v>
+        <v>1290</v>
       </c>
       <c r="B101" t="n">
-        <v>1209</v>
+        <v>1185</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2tu7qWjqT2KwS8C7vq8SbN</t>
+          <t>3Phqv9RFv0aPLT5D_Im9QT</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20765,7 +20765,7 @@
         </is>
       </c>
       <c r="H101" t="n">
-        <v>1314</v>
+        <v>1290</v>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="J101" t="inlineStr"/>
@@ -20875,13 +20875,13 @@
         <v>2.998</v>
       </c>
       <c r="CF101" t="n">
-        <v>110.604319237956</v>
+        <v>110.601345096434</v>
       </c>
       <c r="CG101" t="n">
-        <v>633.053385</v>
+        <v>633.1125025</v>
       </c>
       <c r="CH101" t="n">
-        <v>1897.89404823</v>
+        <v>1898.071282495</v>
       </c>
       <c r="CI101" t="inlineStr"/>
       <c r="CJ101" t="inlineStr"/>
@@ -20894,14 +20894,14 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>1315</v>
+        <v>1291</v>
       </c>
       <c r="B102" t="n">
-        <v>1209</v>
+        <v>1185</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2rXFWc8jX9X9uAiF4mg4_c</t>
+          <t>2CTrriW1D4XfbevcRhL0D$</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20925,7 +20925,7 @@
         </is>
       </c>
       <c r="H102" t="n">
-        <v>1315</v>
+        <v>1291</v>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="J102" t="inlineStr"/>
@@ -21035,13 +21035,13 @@
         <v>0.66</v>
       </c>
       <c r="CF102" t="n">
-        <v>108.708999464787</v>
+        <v>108.706025323265</v>
       </c>
       <c r="CG102" t="n">
-        <v>635.4141235</v>
+        <v>635.473241</v>
       </c>
       <c r="CH102" t="n">
-        <v>419.37332151</v>
+        <v>419.41233906</v>
       </c>
       <c r="CI102" t="inlineStr"/>
       <c r="CJ102" t="inlineStr"/>
@@ -21054,14 +21054,14 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>1316</v>
+        <v>1292</v>
       </c>
       <c r="B103" t="n">
-        <v>1209</v>
+        <v>1185</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>1xVbGem8z8Yw7KMlDD7tyl</t>
+          <t>3ue0$unPz0uux7AwL1STF3</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -21085,7 +21085,7 @@
         </is>
       </c>
       <c r="H103" t="n">
-        <v>1316</v>
+        <v>1292</v>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="J103" t="inlineStr"/>
@@ -21214,14 +21214,14 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>1317</v>
+        <v>1293</v>
       </c>
       <c r="B104" t="n">
-        <v>1209</v>
+        <v>1185</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2JYUQcEU93zwiGeMtni83Z</t>
+          <t>2lJbeNWPr69PR6Bv8eHLx5</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -21245,7 +21245,7 @@
         </is>
       </c>
       <c r="H104" t="n">
-        <v>1317</v>
+        <v>1293</v>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr"/>
@@ -21355,13 +21355,13 @@
         <v>1</v>
       </c>
       <c r="CF104" t="n">
-        <v>108.708999464787</v>
+        <v>108.706025323265</v>
       </c>
       <c r="CG104" t="n">
-        <v>635.4141235</v>
+        <v>635.473241</v>
       </c>
       <c r="CH104" t="n">
-        <v>635.4141235</v>
+        <v>635.473241</v>
       </c>
       <c r="CI104" t="inlineStr"/>
       <c r="CJ104" t="inlineStr"/>
@@ -21374,14 +21374,14 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>1318</v>
+        <v>1294</v>
       </c>
       <c r="B105" t="n">
-        <v>1210</v>
+        <v>1186</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>0cZezKqu94ovlQgVTxGUP9</t>
+          <t>1MQDEFDcX439MvQ3uigCM$</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21405,7 +21405,7 @@
         </is>
       </c>
       <c r="H105" t="n">
-        <v>1318</v>
+        <v>1294</v>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="J105" t="inlineStr"/>
@@ -21520,16 +21520,16 @@
         </is>
       </c>
       <c r="CE105" t="n">
-        <v>1.158</v>
+        <v>0.999999999999999</v>
       </c>
       <c r="CF105" t="n">
-        <v>10.4510384173057</v>
+        <v>11.5343811888718</v>
       </c>
       <c r="CG105" t="n">
-        <v>6.8265125</v>
+        <v>10.45073</v>
       </c>
       <c r="CH105" t="n">
-        <v>7.90510147499999</v>
+        <v>10.45073</v>
       </c>
       <c r="CI105" t="inlineStr"/>
       <c r="CJ105" t="inlineStr"/>
@@ -21542,14 +21542,14 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>1319</v>
+        <v>1295</v>
       </c>
       <c r="B106" t="n">
-        <v>1210</v>
+        <v>1186</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>1Bex$LLBz14RGCBVd_3SHQ</t>
+          <t>3aH$lMb654_u$4SW_WvFAN</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21573,7 +21573,7 @@
         </is>
       </c>
       <c r="H106" t="n">
-        <v>1319</v>
+        <v>1295</v>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr"/>
@@ -21688,16 +21688,16 @@
         </is>
       </c>
       <c r="CE106" t="n">
-        <v>1.158</v>
+        <v>0.999999999999999</v>
       </c>
       <c r="CF106" t="n">
-        <v>27.2953812739153</v>
+        <v>27.4536844116549</v>
       </c>
       <c r="CG106" t="n">
-        <v>25.18441</v>
+        <v>25.384223</v>
       </c>
       <c r="CH106" t="n">
-        <v>29.16354678</v>
+        <v>25.384223</v>
       </c>
       <c r="CI106" t="inlineStr"/>
       <c r="CJ106" t="inlineStr"/>
@@ -21710,14 +21710,14 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>1320</v>
+        <v>1296</v>
       </c>
       <c r="B107" t="n">
-        <v>1210</v>
+        <v>1186</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>0s4lbBN6v2wQ56baFu8aCK</t>
+          <t>14l9pM3sL8xfYz1mvXCNWG</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21741,7 +21741,7 @@
         </is>
       </c>
       <c r="H107" t="n">
-        <v>1320</v>
+        <v>1296</v>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="J107" t="inlineStr"/>
@@ -21856,16 +21856,16 @@
         </is>
       </c>
       <c r="CE107" t="n">
-        <v>1.158</v>
+        <v>0.999999999999999</v>
       </c>
       <c r="CF107" t="n">
-        <v>27.3237702962066</v>
+        <v>27.6473031566045</v>
       </c>
       <c r="CG107" t="n">
-        <v>25.3495095</v>
+        <v>25.882478</v>
       </c>
       <c r="CH107" t="n">
-        <v>29.354732001</v>
+        <v>25.882478</v>
       </c>
       <c r="CI107" t="inlineStr"/>
       <c r="CJ107" t="inlineStr"/>
@@ -21878,14 +21878,14 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>1321</v>
+        <v>1297</v>
       </c>
       <c r="B108" t="n">
-        <v>1210</v>
+        <v>1186</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>29mRuo3Gj2kAoruOaOpQPk</t>
+          <t>0BPV577Cv2qOXbm$_0BLlX</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21909,7 +21909,7 @@
         </is>
       </c>
       <c r="H108" t="n">
-        <v>1321</v>
+        <v>1297</v>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="J108" t="inlineStr"/>
@@ -22016,7 +22016,7 @@
       </c>
       <c r="CD108" t="inlineStr"/>
       <c r="CE108" t="n">
-        <v>4.281</v>
+        <v>4.282</v>
       </c>
       <c r="CF108" t="n">
         <v>104.920885573921</v>
@@ -22025,7 +22025,7 @@
         <v>607.3553475</v>
       </c>
       <c r="CH108" t="n">
-        <v>2600.0882426475</v>
+        <v>2600.695597995</v>
       </c>
       <c r="CI108" t="inlineStr"/>
       <c r="CJ108" t="inlineStr"/>
@@ -22038,14 +22038,14 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>1322</v>
+        <v>1298</v>
       </c>
       <c r="B109" t="n">
-        <v>1210</v>
+        <v>1186</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2UYbzXfWX4jeekEZZounLu</t>
+          <t>0D49X8G8b21vMvV9fI6DYy</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -22069,7 +22069,7 @@
         </is>
       </c>
       <c r="H109" t="n">
-        <v>1322</v>
+        <v>1298</v>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr"/>
@@ -22198,14 +22198,14 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>1323</v>
+        <v>1299</v>
       </c>
       <c r="B110" t="n">
-        <v>1210</v>
+        <v>1186</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2iqV3awXnFaPEu0T7HAtp4</t>
+          <t>3QbhoocVL16heqVtso3nIe</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22229,7 +22229,7 @@
         </is>
       </c>
       <c r="H110" t="n">
-        <v>1323</v>
+        <v>1299</v>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr"/>
@@ -22358,14 +22358,14 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>1324</v>
+        <v>1300</v>
       </c>
       <c r="B111" t="n">
-        <v>1210</v>
+        <v>1186</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2O9cNxLZXB48ei75HpXuVM</t>
+          <t>0sM00mZHr6DOEYTFqh$IrG</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22389,7 +22389,7 @@
         </is>
       </c>
       <c r="H111" t="n">
-        <v>1324</v>
+        <v>1300</v>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr"/>
@@ -22518,14 +22518,14 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>1325</v>
+        <v>1301</v>
       </c>
       <c r="B112" t="n">
-        <v>1211</v>
+        <v>1187</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>19fOi9h4H1XBR85Agg_fkE</t>
+          <t>0hYc3lmMH2T91sw96db3JM</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22549,7 +22549,7 @@
         </is>
       </c>
       <c r="H112" t="n">
-        <v>1325</v>
+        <v>1301</v>
       </c>
       <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr"/>
@@ -22581,7 +22581,7 @@
         </is>
       </c>
       <c r="AD112" t="n">
-        <v>7.939</v>
+        <v>7.94</v>
       </c>
       <c r="AE112" t="inlineStr"/>
       <c r="AF112" t="inlineStr"/>
@@ -22664,16 +22664,16 @@
         </is>
       </c>
       <c r="CE112" t="n">
-        <v>1.001</v>
+        <v>1</v>
       </c>
       <c r="CF112" t="n">
-        <v>28.2538110740109</v>
+        <v>28.3136803768729</v>
       </c>
       <c r="CG112" t="n">
-        <v>28.464383</v>
+        <v>28.4057145</v>
       </c>
       <c r="CH112" t="n">
-        <v>28.4928473830001</v>
+        <v>28.4057145000001</v>
       </c>
       <c r="CI112" t="inlineStr"/>
       <c r="CJ112" t="inlineStr"/>
@@ -22686,14 +22686,14 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>1326</v>
+        <v>1302</v>
       </c>
       <c r="B113" t="n">
-        <v>1211</v>
+        <v>1187</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>1YjQd29ADBdhHAaWT8IdQR</t>
+          <t>0pnXM2gsT77R5nDFj8mzSx</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22717,7 +22717,7 @@
         </is>
       </c>
       <c r="H113" t="n">
-        <v>1326</v>
+        <v>1302</v>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="J113" t="inlineStr"/>
@@ -22749,7 +22749,7 @@
         </is>
       </c>
       <c r="AD113" t="n">
-        <v>7.939</v>
+        <v>7.94</v>
       </c>
       <c r="AE113" t="inlineStr"/>
       <c r="AF113" t="inlineStr"/>
@@ -22832,16 +22832,16 @@
         </is>
       </c>
       <c r="CE113" t="n">
-        <v>1.001</v>
+        <v>1</v>
       </c>
       <c r="CF113" t="n">
-        <v>28.2852454986017</v>
+        <v>28.4471992015421</v>
       </c>
       <c r="CG113" t="n">
-        <v>28.6278645</v>
+        <v>29.2135305</v>
       </c>
       <c r="CH113" t="n">
-        <v>28.6564923645001</v>
+        <v>29.2135305000001</v>
       </c>
       <c r="CI113" t="inlineStr"/>
       <c r="CJ113" t="inlineStr"/>
@@ -22854,14 +22854,14 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>1327</v>
+        <v>1303</v>
       </c>
       <c r="B114" t="n">
-        <v>1211</v>
+        <v>1187</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>0Dg5sNnYTBWwyKrJUXkFTO</t>
+          <t>2$k1ahqBDFJPjWMBdR8WtC</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22885,7 +22885,7 @@
         </is>
       </c>
       <c r="H114" t="n">
-        <v>1327</v>
+        <v>1303</v>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr"/>
@@ -22917,7 +22917,7 @@
         </is>
       </c>
       <c r="AD114" t="n">
-        <v>7.939</v>
+        <v>7.94</v>
       </c>
       <c r="AE114" t="inlineStr"/>
       <c r="AF114" t="inlineStr"/>
@@ -23000,16 +23000,16 @@
         </is>
       </c>
       <c r="CE114" t="n">
-        <v>1.001</v>
+        <v>1</v>
       </c>
       <c r="CF114" t="n">
-        <v>10.4510384173057</v>
+        <v>11.5343811888718</v>
       </c>
       <c r="CG114" t="n">
-        <v>6.8265125</v>
+        <v>10.45073</v>
       </c>
       <c r="CH114" t="n">
-        <v>6.83333901250001</v>
+        <v>10.45073</v>
       </c>
       <c r="CI114" t="inlineStr"/>
       <c r="CJ114" t="inlineStr"/>
@@ -23022,14 +23022,14 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>1328</v>
+        <v>1304</v>
       </c>
       <c r="B115" t="n">
-        <v>1211</v>
+        <v>1187</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2HDdALzov8sOiati08LIYR</t>
+          <t>1vS9xL68j7QRd7X5GTAvLE</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23053,7 +23053,7 @@
         </is>
       </c>
       <c r="H115" t="n">
-        <v>1328</v>
+        <v>1304</v>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr"/>
@@ -23085,7 +23085,7 @@
         </is>
       </c>
       <c r="AD115" t="n">
-        <v>7.939</v>
+        <v>7.94</v>
       </c>
       <c r="AE115" t="inlineStr"/>
       <c r="AF115" t="inlineStr"/>
@@ -23160,7 +23160,7 @@
       </c>
       <c r="CD115" t="inlineStr"/>
       <c r="CE115" t="n">
-        <v>4.009</v>
+        <v>4.008</v>
       </c>
       <c r="CF115" t="n">
         <v>104.909626929904</v>
@@ -23169,7 +23169,7 @@
         <v>607.3728175</v>
       </c>
       <c r="CH115" t="n">
-        <v>2434.9576253575</v>
+        <v>2434.35025254</v>
       </c>
       <c r="CI115" t="inlineStr"/>
       <c r="CJ115" t="inlineStr"/>
@@ -23182,14 +23182,14 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>1329</v>
+        <v>1305</v>
       </c>
       <c r="B116" t="n">
-        <v>1211</v>
+        <v>1187</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2E_TZJZ7r4DgKH0p0YQJl8</t>
+          <t>0rjMKvNtzAnefNaYJ97j52</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23213,7 +23213,7 @@
         </is>
       </c>
       <c r="H116" t="n">
-        <v>1329</v>
+        <v>1305</v>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="J116" t="inlineStr"/>
@@ -23245,7 +23245,7 @@
         </is>
       </c>
       <c r="AD116" t="n">
-        <v>7.939</v>
+        <v>7.94</v>
       </c>
       <c r="AE116" t="inlineStr"/>
       <c r="AF116" t="inlineStr"/>
@@ -23342,14 +23342,14 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>1330</v>
+        <v>1306</v>
       </c>
       <c r="B117" t="n">
-        <v>1212</v>
+        <v>1188</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>3eXcdEMUX3XuwJXhU1bBiW</t>
+          <t>3r8c5tGbPC_fDRkxzKA81G</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23373,7 +23373,7 @@
         </is>
       </c>
       <c r="H117" t="n">
-        <v>1330</v>
+        <v>1306</v>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr"/>
@@ -23405,7 +23405,7 @@
         </is>
       </c>
       <c r="AD117" t="n">
-        <v>11.947</v>
+        <v>11.948</v>
       </c>
       <c r="AE117" t="inlineStr"/>
       <c r="AF117" t="inlineStr"/>
@@ -23488,16 +23488,16 @@
         </is>
       </c>
       <c r="CE117" t="n">
-        <v>1.001</v>
+        <v>1</v>
       </c>
       <c r="CF117" t="n">
-        <v>10.4510384173057</v>
+        <v>11.5343811888718</v>
       </c>
       <c r="CG117" t="n">
-        <v>6.8265125</v>
+        <v>10.45073</v>
       </c>
       <c r="CH117" t="n">
-        <v>6.8333390125</v>
+        <v>10.45073</v>
       </c>
       <c r="CI117" t="inlineStr"/>
       <c r="CJ117" t="inlineStr"/>
@@ -23510,14 +23510,14 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>1331</v>
+        <v>1307</v>
       </c>
       <c r="B118" t="n">
-        <v>1212</v>
+        <v>1188</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2yWWAdHcT0Ee9Cxo9n9g3E</t>
+          <t>3hhMFg80L1LfBHM_a3hr7A</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23541,7 +23541,7 @@
         </is>
       </c>
       <c r="H118" t="n">
-        <v>1331</v>
+        <v>1307</v>
       </c>
       <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr"/>
@@ -23573,7 +23573,7 @@
         </is>
       </c>
       <c r="AD118" t="n">
-        <v>11.947</v>
+        <v>11.948</v>
       </c>
       <c r="AE118" t="inlineStr"/>
       <c r="AF118" t="inlineStr"/>
@@ -23656,16 +23656,16 @@
         </is>
       </c>
       <c r="CE118" t="n">
-        <v>1.001</v>
+        <v>0.999999999999998</v>
       </c>
       <c r="CF118" t="n">
-        <v>29.8805721692127</v>
+        <v>29.8929803703454</v>
       </c>
       <c r="CG118" t="n">
-        <v>40.6284265</v>
+        <v>40.5779875</v>
       </c>
       <c r="CH118" t="n">
-        <v>40.6690549264999</v>
+        <v>40.5779874999999</v>
       </c>
       <c r="CI118" t="inlineStr"/>
       <c r="CJ118" t="inlineStr"/>
@@ -23678,14 +23678,14 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>1332</v>
+        <v>1308</v>
       </c>
       <c r="B119" t="n">
-        <v>1212</v>
+        <v>1188</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>191C_eUqLBjwUYQYjuyzbJ</t>
+          <t>1MeUygKbr5gwqhdLnI1$fr</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23709,7 +23709,7 @@
         </is>
       </c>
       <c r="H119" t="n">
-        <v>1332</v>
+        <v>1308</v>
       </c>
       <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr"/>
@@ -23741,7 +23741,7 @@
         </is>
       </c>
       <c r="AD119" t="n">
-        <v>11.947</v>
+        <v>11.948</v>
       </c>
       <c r="AE119" t="inlineStr"/>
       <c r="AF119" t="inlineStr"/>
@@ -23838,14 +23838,14 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>1333</v>
+        <v>1309</v>
       </c>
       <c r="B120" t="n">
-        <v>1212</v>
+        <v>1188</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>1AmWYBKrzAYQ$BPe2iH8In</t>
+          <t>0qFk07a55D6POPpcM5bCmf</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -23869,7 +23869,7 @@
         </is>
       </c>
       <c r="H120" t="n">
-        <v>1333</v>
+        <v>1309</v>
       </c>
       <c r="I120" t="inlineStr"/>
       <c r="J120" t="inlineStr"/>
@@ -23901,7 +23901,7 @@
         </is>
       </c>
       <c r="AD120" t="n">
-        <v>11.947</v>
+        <v>11.948</v>
       </c>
       <c r="AE120" t="inlineStr"/>
       <c r="AF120" t="inlineStr"/>
